--- a/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
+++ b/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
@@ -9,10 +9,11 @@
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Debt &amp; EF Plan" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Actuals" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Subscriptions" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Rules &amp; Legend" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Weekly Envelopes" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Debt &amp; EF Plan" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Actuals" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Subscriptions" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Rules &amp; Legend" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="395">
   <si>
     <t xml:space="preserve">Household Budget — October 2026 rebuild</t>
   </si>
@@ -122,10 +123,10 @@
     <t xml:space="preserve">Fixed $341.99/mo all year. Confirm what it is and when it ends.</t>
   </si>
   <si>
-    <t xml:space="preserve">Installment/promo/HELOC payments (Holyoke CU, Capital One, TD, OnePay/Sync)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holyoke CU ran $500–$1,400 (likely the HELOC at 3.5%, $500 min per your note). Hold it at the minimum while JetBlue is at 29.74%; Capital One $350 and TD ~$190 look like fixed plans. Verify balances/expiry.</t>
+    <t xml:space="preserve">HELOC (Holyoke CU) + installment/promo plans (Capital One, TD, OnePay/Sync)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELOC repriced 3.5% → 7% at the account anniversary; minimum now ≈ $1,100 (was $500) — per you. Target = Holyoke $1,100 + Capital One $350 + TD ~$190 + OnePay/Sync ~$160. Pay the HELOC minimum only while the 29.74%/17.49% cards exist. A single $450 Wells Fargo payment (9/22) is not included — what is it?</t>
   </si>
   <si>
     <t xml:space="preserve">GEICO auto</t>
@@ -170,10 +171,10 @@
     <t xml:space="preserve">Wireless ~$257 (down from $311) + $90 recurring on checking. Audit lines/plan.</t>
   </si>
   <si>
-    <t xml:space="preserve">WGBH + E-ZPass (SiriusXM cancelled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SiriusXM $72.97/mo removed — see Subscriptions.</t>
+    <t xml:space="preserve">SiriusXM + WGBH + E-ZPass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SiriusXM ($72.97) is staying. No change vs. Q3.</t>
   </si>
   <si>
     <t xml:space="preserve">Landscape, pest/tick, pet waste (Lynch, F&amp;W, Ohdeer, MetroWest)</t>
@@ -206,25 +207,34 @@
     <t xml:space="preserve">Joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Protected. Includes beach-week food in Jul/Aug.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery apps (DoorDash, Grubhub)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fees + tip premium. Use pickup or one planned delivery night/week.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household help (weekly $160 checks + Venmo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly checks ($150–$160) + Venmo (~$120/mo). Unlabeled in the statements — confirm what these are.</t>
+    <t xml:space="preserve">Protected. Q3 includes beach-week food. Dining + takeout together = $1,050/mo ($242/wk) vs $1,138 in Q3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takeout orders (DoorDash, Grubhub)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family takeout — protected, essentially held at Q3. Only lever: pickup instead of delivery when the fee/tip is the difference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaning help ($160/wk checks) + Venmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$160 × 52 ÷ 12 = $693/mo; Q3 checks averaged $698. Venmo ~$65/mo.</t>
   </si>
   <si>
     <t xml:space="preserve">Cleaning/laundry (FreshNClean, Galicia)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fuel + auto upkeep (gas, Sudbury Automotive, tolls/parking, RMV)</t>
+    <t xml:space="preserve">Gas (fuel stations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 $334/mo ≈ $77/wk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto upkeep, parking, tolls, RMV (Sudbury Automotive, Audi service)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumpy — monthly envelope, not weekly.</t>
   </si>
   <si>
     <t xml:space="preserve">Home improvement/garden (Lowe's, Home Depot, Mahoney's, Aubuchon)</t>
@@ -428,6 +438,69 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
+    <t xml:space="preserve">Weekly envelopes — Checking account (debit card)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly = monthly target × 12 ÷ 52. Targets come from the Budget sheet (green = link), so edit them there. 'Q3 /wk' = what you actually spent in Jul–Sep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envelope (spend-as-you-go)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEEKLY target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 actual /wk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δ /wk vs Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan–Sep avg /wk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groceries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takeout (DoorDash, Grubhub)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon + household orders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fun money (movies, hobbies, cash)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend-as-you-go total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned / lumpy — handle monthly, not weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per week equivalent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned / lumpy total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERYTHING in Checking, per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check: equals Budget Checking subtotal ÷ 52 × 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check vs Budget subtotal (should be 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months with a 5th Allison paycheck (2026: Apr, Jul, Sep, Dec) are paid 52/12 — the 5th check is NOT envelope money; it goes to card paydown.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Card payoff (avalanche) and emergency-fund timeline</t>
   </si>
   <si>
@@ -512,7 +585,7 @@
     <t xml:space="preserve">Your stated Mar-2027 SPAXX goal in memory.</t>
   </si>
   <si>
-    <t xml:space="preserve">Not modeled: new card charges (the plan assumes zero), HELOC/promo balances, EF interest (~4% on SPAXX), Oct payments.</t>
+    <t xml:space="preserve">Not modeled: new card charges (the plan assumes zero), promo-plan payoffs, HELOC principal paydown beyond the minimum, EF interest (~4% on SPAXX), Oct payments.</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 1 ends after</t>
@@ -716,9 +789,6 @@
     <t xml:space="preserve">Venmo payments</t>
   </si>
   <si>
-    <t xml:space="preserve">Groceries</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dining / coffee / treats</t>
   </si>
   <si>
@@ -821,13 +891,13 @@
     <t xml:space="preserve">Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Cut</t>
+    <t xml:space="preserve">Keep</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Paid from Bills account. $876/yr.</t>
+    <t xml:space="preserve">Keeping (your call). Paid from Bills account.</t>
   </si>
   <si>
     <t xml:space="preserve">YouTube TV</t>
@@ -845,9 +915,6 @@
     <t xml:space="preserve">Netflix</t>
   </si>
   <si>
-    <t xml:space="preserve">Keep</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-10-08</t>
   </si>
   <si>
@@ -1085,7 +1152,7 @@
     <t xml:space="preserve">Payoff mechanics</t>
   </si>
   <si>
-    <t xml:space="preserve">Autopay the minimum on every card. On each payday, send the Phase paydown amount to JetBlue (29.74%) until zero, then Fidelity (17.49%). Do not overpay the 3.5% HELOC (Holyoke) or 0% loans while a 29.74% balance exists.</t>
+    <t xml:space="preserve">Autopay the minimum on every card. On each payday, send the Phase paydown amount to JetBlue (29.74%) until zero, then Fidelity (17.49%). Pay only the minimum on the HELOC (Holyoke, now 7%, ~$1,100/mo) and the 0% loans while a 29.74% or 17.49% balance exists.</t>
   </si>
   <si>
     <t xml:space="preserve">5th-paycheck months</t>
@@ -1097,13 +1164,13 @@
     <t xml:space="preserve">Weekly 10-minute check (Sunday)</t>
   </si>
   <si>
-    <t xml:space="preserve">Three numbers: groceries left, fun left (dining + delivery + entertainment), Amazon left. Compare against the monthly target ÷ 4.33.</t>
+    <t xml:space="preserve">Four numbers against the Weekly Envelopes sheet: groceries, dining + takeout, gas, Amazon.</t>
   </si>
   <si>
     <t xml:space="preserve">Protected 'joy' lines</t>
   </si>
   <si>
-    <t xml:space="preserve">Thoreau Club, kids' activities, dining out, entertainment/hobbies, donations, family trips. These are funded first and not cut — the cuts come from app-store/gaming, Amazon, delivery fees, overlapping subscriptions, and insurance/phone/oil shopping.</t>
+    <t xml:space="preserve">Thoreau Club, kids' activities, dining out, entertainment/hobbies, donations, family trips. These are funded first and not cut — the cuts come from app-store/gaming, Amazon, overlapping subscriptions, and insurance/phone/oil shopping. Takeout and SiriusXM are kept.</t>
   </si>
   <si>
     <t xml:space="preserve">Investing</t>
@@ -1127,7 +1194,7 @@
     <t xml:space="preserve">Income: Sep 2026 payroll deposits across the three accounts (statements).</t>
   </si>
   <si>
-    <t xml:space="preserve">Debt balances: Kevin config debt tracker dated 2026-09-27 (JetBlue $9,800.78; Fidelity $5,341.52). APRs: 'Debt consolidation' note (JetBlue 29.74%, Fidelity 17.49%, HELOC 3.5%, Volvo 5.49%, Audi 5.25%, Petro AC loan 0%). That note's balances are older than the config.</t>
+    <t xml:space="preserve">Debt balances: Kevin config debt tracker dated 2026-09-27 (JetBlue $9,800.78; Fidelity $5,341.52). APRs: 'Debt consolidation' note (JetBlue 29.74%, Fidelity 17.49%, HELOC 3.5% in the note — now 7% with ~$1,100 minimum per you, Volvo 5.49%, Audi 5.25%, Petro AC loan 0%). That note's balances are older than the config.</t>
   </si>
   <si>
     <t xml:space="preserve">Emergency fund $12,081 (SPAXX $9,501 + lifestyle $2,580) is from config 9/27 — the CSVs contain no balances, so I could not verify it.</t>
@@ -1139,7 +1206,7 @@
     <t xml:space="preserve">Card charges are not in the statements — only payments are. The plan assumes zero new card charges.</t>
   </si>
   <si>
-    <t xml:space="preserve">Categories are keyword-based on merchant strings; unclassified items are shown on Actuals. Weekly $150–$160 checks are unlabeled.</t>
+    <t xml:space="preserve">Categories are keyword-based on merchant strings; unclassified items are shown on Actuals. Weekly checks = cleaning help ($160/wk); DoorDash/Grubhub = family takeout (per you). HELOC minimum of ~$1,100 is assumed to apply from Nov-26.</t>
   </si>
   <si>
     <t xml:space="preserve">Not financial, tax, or legal advice.</t>
@@ -1406,6 +1473,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1419,10 +1490,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1690,7 +1757,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1926,7 +1993,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
@@ -1943,11 +2010,11 @@
         <v>1275</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="G17" s="12" t="n">
         <f aca="false">F17-D17</f>
-        <v>-200</v>
+        <v>400</v>
       </c>
       <c r="H17" s="14" t="s">
         <v>33</v>
@@ -2157,11 +2224,11 @@
         <v>142</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="G25" s="12" t="n">
         <f aca="false">F25-D25</f>
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>49</v>
@@ -2210,11 +2277,11 @@
       </c>
       <c r="F27" s="17" t="n">
         <f aca="false">SUM(F13:F26)</f>
-        <v>14232</v>
+        <v>14892</v>
       </c>
       <c r="G27" s="17" t="n">
         <f aca="false">SUM(G13:G26)</f>
-        <v>-817</v>
+        <v>-157</v>
       </c>
       <c r="H27" s="18"/>
     </row>
@@ -2260,7 +2327,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>58</v>
       </c>
@@ -2277,17 +2344,17 @@
         <v>965</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="G31" s="12" t="n">
         <f aca="false">F31-D31</f>
-        <v>-128</v>
+        <v>-78</v>
       </c>
       <c r="H31" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>61</v>
       </c>
@@ -2295,7 +2362,7 @@
         <v>56</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D32" s="12" t="n">
         <v>310</v>
@@ -2304,11 +2371,11 @@
         <v>325</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G32" s="12" t="n">
         <f aca="false">F32-D32</f>
-        <v>-160</v>
+        <v>-10</v>
       </c>
       <c r="H32" s="14" t="s">
         <v>62</v>
@@ -2331,11 +2398,11 @@
         <v>952</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="G33" s="12" t="n">
         <f aca="false">F33-D33</f>
-        <v>89</v>
+        <v>-1</v>
       </c>
       <c r="H33" s="14" t="s">
         <v>64</v>
@@ -2377,23 +2444,25 @@
         <v>51</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>612</v>
+        <v>334</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>553</v>
+        <v>279</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>550</v>
+        <v>340</v>
       </c>
       <c r="G35" s="12" t="n">
         <f aca="false">F35-D35</f>
-        <v>-62</v>
-      </c>
-      <c r="H35" s="14"/>
+        <v>6</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>56</v>
@@ -2402,52 +2471,52 @@
         <v>51</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>363</v>
+        <v>278</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>464</v>
+        <v>274</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="G36" s="12" t="n">
         <f aca="false">F36-D36</f>
-        <v>-63</v>
+        <v>-68</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>498</v>
+        <v>363</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>498</v>
+        <v>300</v>
       </c>
       <c r="G37" s="12" t="n">
         <f aca="false">F37-D37</f>
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>56</v>
@@ -2456,52 +2525,52 @@
         <v>59</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="G38" s="12" t="n">
         <f aca="false">F38-D38</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>207</v>
+        <v>493</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>139</v>
+        <v>483</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>200</v>
+        <v>490</v>
       </c>
       <c r="G39" s="12" t="n">
         <f aca="false">F39-D39</f>
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>56</v>
@@ -2510,25 +2579,25 @@
         <v>51</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>870</v>
+        <v>207</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>478</v>
+        <v>139</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G40" s="12" t="n">
         <f aca="false">F40-D40</f>
-        <v>-520</v>
+        <v>-7</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>56</v>
@@ -2537,79 +2606,79 @@
         <v>51</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>93</v>
+        <v>870</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>70</v>
+        <v>478</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="G41" s="12" t="n">
         <f aca="false">F41-D41</f>
-        <v>-43</v>
+        <v>-520</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>296</v>
+        <v>93</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>293</v>
+        <v>70</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="G42" s="12" t="n">
         <f aca="false">F42-D42</f>
-        <v>4</v>
+        <v>-43</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>785</v>
+        <v>296</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>1022</v>
+        <v>293</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G43" s="12" t="n">
         <f aca="false">F43-D43</f>
-        <v>-285</v>
+        <v>4</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>56</v>
@@ -2618,23 +2687,25 @@
         <v>51</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>280</v>
+        <v>785</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>346</v>
+        <v>1022</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G44" s="12" t="n">
         <f aca="false">F44-D44</f>
-        <v>-30</v>
-      </c>
-      <c r="H44" s="14"/>
+        <v>-285</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>56</v>
@@ -2643,23 +2714,23 @@
         <v>51</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>144</v>
+        <v>346</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G45" s="12" t="n">
         <f aca="false">F45-D45</f>
-        <v>-1</v>
+        <v>-30</v>
       </c>
       <c r="H45" s="14"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>56</v>
@@ -2668,23 +2739,23 @@
         <v>51</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G46" s="12" t="n">
         <f aca="false">F46-D46</f>
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="14"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>56</v>
@@ -2693,25 +2764,23 @@
         <v>51</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>214</v>
+        <v>96</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="G47" s="12" t="n">
         <f aca="false">F47-D47</f>
-        <v>-82</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>86</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H47" s="14"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>56</v>
@@ -2720,25 +2789,25 @@
         <v>51</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>153</v>
+        <v>252</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="G48" s="12" t="n">
         <f aca="false">F48-D48</f>
-        <v>-63</v>
+        <v>-82</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>56</v>
@@ -2747,17 +2816,17 @@
         <v>51</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>298</v>
+        <v>176</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="G49" s="12" t="n">
         <f aca="false">F49-D49</f>
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="H49" s="14" t="s">
         <v>89</v>
@@ -2765,59 +2834,61 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>38</v>
+        <v>240</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>62</v>
+        <v>298</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="G50" s="12" t="n">
         <f aca="false">F50-D50</f>
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="G51" s="12" t="n">
         <f aca="false">F51-D51</f>
-        <v>-2</v>
-      </c>
-      <c r="H51" s="14"/>
+        <v>37</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>56</v>
@@ -2826,406 +2897,431 @@
         <v>51</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="G52" s="12" t="n">
         <f aca="false">F52-D52</f>
+        <v>-2</v>
+      </c>
+      <c r="H52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <f aca="false">F53-D53</f>
         <v>-9</v>
       </c>
-      <c r="H52" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="17" t="n">
-        <f aca="false">SUM(D30:D52)</f>
+      <c r="H53" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17" t="n">
+        <f aca="false">SUM(D30:D53)</f>
         <v>8421</v>
       </c>
-      <c r="E53" s="17" t="n">
-        <f aca="false">SUM(E30:E52)</f>
+      <c r="E54" s="17" t="n">
+        <f aca="false">SUM(E30:E53)</f>
         <v>8673</v>
       </c>
-      <c r="F53" s="17" t="n">
-        <f aca="false">SUM(F30:F52)</f>
-        <v>7328</v>
-      </c>
-      <c r="G53" s="17" t="n">
-        <f aca="false">SUM(G30:G52)</f>
-        <v>-1093</v>
-      </c>
-      <c r="H53" s="18"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H54" s="19"/>
+      <c r="F54" s="17" t="n">
+        <f aca="false">SUM(F30:F53)</f>
+        <v>7438</v>
+      </c>
+      <c r="G54" s="17" t="n">
+        <f aca="false">SUM(G30:G53)</f>
+        <v>-983</v>
+      </c>
+      <c r="H54" s="18"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="11"/>
+      <c r="H55" s="19"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F56" s="12" t="n">
+      <c r="A56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="11"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="12" t="n">
         <f aca="false">B9</f>
         <v>26233.0266666667</v>
       </c>
-      <c r="H56" s="19"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F57" s="12" t="n">
-        <f aca="false">-F27</f>
-        <v>-14232</v>
-      </c>
       <c r="H57" s="19"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F58" s="12" t="n">
-        <f aca="false">-F53</f>
-        <v>-7328</v>
+        <f aca="false">-F27</f>
+        <v>-14892</v>
       </c>
       <c r="H58" s="19"/>
     </row>
-    <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F59" s="9" t="n">
-        <f aca="false">SUM(F56:F58)</f>
-        <v>4673.02666666667</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H60" s="19"/>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <f aca="false">-F54</f>
+        <v>-7438</v>
+      </c>
+      <c r="H59" s="19"/>
+    </row>
+    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <f aca="false">SUM(F57:F59)</f>
+        <v>3903.02666666667</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
-        <v>102</v>
-      </c>
       <c r="H61" s="19"/>
     </row>
-    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D62" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="H62" s="14" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H62" s="19"/>
+    </row>
+    <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>38</v>
       </c>
+      <c r="D63" s="12" t="n">
+        <v>200</v>
+      </c>
       <c r="F63" s="13" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>38</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F65" s="12" t="n">
-        <f aca="false">MAX(F71-F72-F73,0)/F74</f>
-        <v>1076.25</v>
+      <c r="F65" s="13" t="n">
+        <v>200</v>
       </c>
       <c r="H65" s="14" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15" t="s">
+    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F66" s="17" t="n">
-        <f aca="false">SUM(F62:F65)</f>
+      <c r="B66" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <f aca="false">MAX(F72-F73-F74,0)/F75</f>
+        <v>1076.25</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F67" s="17" t="n">
+        <f aca="false">SUM(F63:F66)</f>
         <v>2026.25</v>
       </c>
-      <c r="H66" s="19"/>
-    </row>
-    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="F67" s="9" t="n">
-        <f aca="false">F59-F66</f>
-        <v>2646.77666666667</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H67" s="19"/>
+    </row>
+    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F68" s="9" t="n">
-        <f aca="false">F67+F65</f>
-        <v>3723.02666666667</v>
-      </c>
-      <c r="H68" s="19"/>
+        <f aca="false">F60-F67</f>
+        <v>1876.77666666667</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <f aca="false">F68+F66</f>
+        <v>2953.02666666667</v>
+      </c>
       <c r="H69" s="19"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="11"/>
+      <c r="H70" s="19"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F71" s="13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>119</v>
-      </c>
+      <c r="A71" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="11"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>695</v>
+        <v>5000</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="H73" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F74" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F75" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="H74" s="14"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H75" s="19"/>
+      <c r="H75" s="14"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="11"/>
-    </row>
-    <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="21"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F77" s="10" t="s">
+      <c r="H76" s="19"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="11"/>
+    </row>
+    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="21"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H77" s="22" t="s">
+      <c r="E78" s="10" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5" t="s">
+      <c r="F78" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H78" s="22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D78" s="12" t="n">
+      <c r="D79" s="12" t="n">
         <f aca="false">F27</f>
-        <v>14232</v>
-      </c>
-      <c r="E78" s="13" t="n">
+        <v>14892</v>
+      </c>
+      <c r="E79" s="13" t="n">
         <f aca="false">4832.88*$B$6/12</f>
         <v>9665.76</v>
       </c>
-      <c r="F78" s="23" t="n">
-        <f aca="false">(D78-E78)/($B$8/12)</f>
-        <v>1053.74769230769</v>
-      </c>
-      <c r="G78" s="6" t="n">
+      <c r="F79" s="23" t="n">
+        <f aca="false">(D79-E79)/($B$8/12)</f>
+        <v>1206.05538461538</v>
+      </c>
+      <c r="G79" s="6" t="n">
         <v>796.33</v>
       </c>
-      <c r="H78" s="24" t="n">
-        <f aca="false">F78-G78</f>
-        <v>257.417692307692</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5" t="s">
+      <c r="H79" s="24" t="n">
+        <f aca="false">F79-G79</f>
+        <v>409.725384615385</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D79" s="12" t="n">
-        <f aca="false">F53</f>
-        <v>7328</v>
-      </c>
-      <c r="E79" s="13" t="n">
+      <c r="D80" s="12" t="n">
+        <f aca="false">F54</f>
+        <v>7438</v>
+      </c>
+      <c r="E80" s="13" t="n">
         <f aca="false">2899.72*$B$6/12</f>
         <v>5799.44</v>
       </c>
-      <c r="F79" s="23" t="n">
-        <f aca="false">(D79-E79)/($B$8/12)</f>
-        <v>352.744615384616</v>
-      </c>
-      <c r="G79" s="6" t="n">
+      <c r="F80" s="23" t="n">
+        <f aca="false">(D80-E80)/($B$8/12)</f>
+        <v>378.129230769231</v>
+      </c>
+      <c r="G80" s="6" t="n">
         <v>477.8</v>
       </c>
-      <c r="H79" s="24" t="n">
-        <f aca="false">F79-G79</f>
-        <v>-125.055384615385</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D80" s="12" t="n">
-        <f aca="false">F59</f>
-        <v>4673.02666666667</v>
-      </c>
-      <c r="E80" s="13" t="n">
+      <c r="H80" s="24" t="n">
+        <f aca="false">F80-G80</f>
+        <v>-99.6707692307691</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" s="12" t="n">
+        <f aca="false">F60</f>
+        <v>3903.02666666667</v>
+      </c>
+      <c r="E81" s="13" t="n">
         <f aca="false">1933.15*$B$6/12</f>
         <v>3866.3</v>
       </c>
-      <c r="F80" s="23" t="n">
-        <f aca="false">(D80-E80)/($B$8/12)</f>
-        <v>186.167692307693</v>
-      </c>
-      <c r="G80" s="6" t="n">
+      <c r="F81" s="23" t="n">
+        <f aca="false">(D81-E81)/($B$8/12)</f>
+        <v>8.47538461538488</v>
+      </c>
+      <c r="G81" s="6" t="n">
         <v>318.53</v>
       </c>
-      <c r="H80" s="24" t="n">
-        <f aca="false">F80-G80</f>
-        <v>-132.362307692307</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D81" s="25" t="n">
-        <f aca="false">SUM(D78:D80)</f>
+      <c r="H81" s="24" t="n">
+        <f aca="false">F81-G81</f>
+        <v>-310.054615384615</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D82" s="25" t="n">
+        <f aca="false">SUM(D79:D81)</f>
         <v>26233.0266666667</v>
       </c>
-      <c r="E81" s="25" t="n">
-        <f aca="false">SUM(E78:E80)</f>
+      <c r="E82" s="25" t="n">
+        <f aca="false">SUM(E79:E81)</f>
         <v>19331.5</v>
       </c>
-      <c r="F81" s="23" t="n">
-        <f aca="false">SUM(F78:F80)</f>
+      <c r="F82" s="23" t="n">
+        <f aca="false">SUM(F79:F81)</f>
         <v>1592.66</v>
       </c>
-      <c r="G81" s="23" t="n">
-        <f aca="false">SUM(G78:G80)</f>
+      <c r="G82" s="23" t="n">
+        <f aca="false">SUM(G79:G81)</f>
         <v>1592.66</v>
       </c>
-      <c r="H81" s="26" t="n">
-        <f aca="false">SUM(H78:H80)</f>
-        <v>4.83169060316868E-013</v>
+      <c r="H82" s="26" t="n">
+        <f aca="false">SUM(H79:H81)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3240,6 +3336,625 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <f aca="false">Budget!F30</f>
+        <v>1050</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <f aca="false">B5*12/52</f>
+        <v>242.307692307692</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <f aca="false">Budget!D30*12/52</f>
+        <v>194.769230769231</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <f aca="false">C5-D5</f>
+        <v>47.5384615384616</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <f aca="false">Budget!E30*12/52</f>
+        <v>169.153846153846</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <f aca="false">Budget!F31</f>
+        <v>750</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <f aca="false">B6*12/52</f>
+        <v>173.076923076923</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <f aca="false">Budget!D31*12/52</f>
+        <v>191.076923076923</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <f aca="false">C6-D6</f>
+        <v>-18</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <f aca="false">Budget!E31*12/52</f>
+        <v>222.692307692308</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <f aca="false">Budget!F32</f>
+        <v>300</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <f aca="false">B7*12/52</f>
+        <v>69.2307692307692</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <f aca="false">Budget!D32*12/52</f>
+        <v>71.5384615384615</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <f aca="false">C7-D7</f>
+        <v>-2.30769230769231</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <f aca="false">Budget!E32*12/52</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="27" t="n">
+        <f aca="false">Budget!F35</f>
+        <v>340</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <f aca="false">B8*12/52</f>
+        <v>78.4615384615385</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <f aca="false">Budget!D35*12/52</f>
+        <v>77.0769230769231</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <f aca="false">C8-D8</f>
+        <v>1.38461538461539</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <f aca="false">Budget!E35*12/52</f>
+        <v>64.3846153846154</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <f aca="false">Budget!F44</f>
+        <v>500</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <f aca="false">B9*12/52</f>
+        <v>115.384615384615</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <f aca="false">Budget!D44*12/52</f>
+        <v>181.153846153846</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <f aca="false">C9-D9</f>
+        <v>-65.7692307692308</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <f aca="false">Budget!E44*12/52</f>
+        <v>235.846153846154</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <f aca="false">Budget!F40</f>
+        <v>200</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <f aca="false">B10*12/52</f>
+        <v>46.1538461538462</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <f aca="false">Budget!D40*12/52</f>
+        <v>47.7692307692308</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <f aca="false">C10-D10</f>
+        <v>-1.61538461538461</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <f aca="false">Budget!E40*12/52</f>
+        <v>32.0769230769231</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="27" t="n">
+        <f aca="false">Budget!F43</f>
+        <v>300</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <f aca="false">B11*12/52</f>
+        <v>69.2307692307692</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <f aca="false">Budget!D43*12/52</f>
+        <v>68.3076923076923</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <f aca="false">C11-D11</f>
+        <v>0.92307692307692</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <f aca="false">Budget!E43*12/52</f>
+        <v>67.6153846153846</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">SUM(B5:B11)</f>
+        <v>3440</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <f aca="false">SUM(C5:C11)</f>
+        <v>793.846153846154</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <f aca="false">SUM(D5:D11)</f>
+        <v>831.692307692308</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <f aca="false">SUM(E5:E11)</f>
+        <v>-37.8461538461538</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <f aca="false">SUM(F5:F11)</f>
+        <v>866.769230769231</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="27" t="n">
+        <f aca="false">Budget!F33</f>
+        <v>760</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <f aca="false">B16*12/52</f>
+        <v>175.384615384615</v>
+      </c>
+      <c r="D16" s="27" t="n">
+        <f aca="false">Budget!D33*12/52</f>
+        <v>175.615384615385</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="27" t="n">
+        <f aca="false">Budget!F34</f>
+        <v>75</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <f aca="false">B17*12/52</f>
+        <v>17.3076923076923</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <f aca="false">Budget!D34*12/52</f>
+        <v>13.3846153846154</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <f aca="false">Budget!F36</f>
+        <v>210</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <f aca="false">B18*12/52</f>
+        <v>48.4615384615385</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">Budget!D36*12/52</f>
+        <v>64.1538461538462</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="27" t="n">
+        <f aca="false">Budget!F37</f>
+        <v>300</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <f aca="false">B19*12/52</f>
+        <v>69.2307692307692</v>
+      </c>
+      <c r="D19" s="27" t="n">
+        <f aca="false">Budget!D37*12/52</f>
+        <v>83.7692307692308</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="27" t="n">
+        <f aca="false">Budget!F38</f>
+        <v>498</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <f aca="false">B20*12/52</f>
+        <v>114.923076923077</v>
+      </c>
+      <c r="D20" s="27" t="n">
+        <f aca="false">Budget!D38*12/52</f>
+        <v>114.923076923077</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="27" t="n">
+        <f aca="false">Budget!F39</f>
+        <v>490</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <f aca="false">B21*12/52</f>
+        <v>113.076923076923</v>
+      </c>
+      <c r="D21" s="27" t="n">
+        <f aca="false">Budget!D39*12/52</f>
+        <v>113.769230769231</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="27" t="n">
+        <f aca="false">Budget!F41</f>
+        <v>350</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <f aca="false">B22*12/52</f>
+        <v>80.7692307692308</v>
+      </c>
+      <c r="D22" s="27" t="n">
+        <f aca="false">Budget!D41*12/52</f>
+        <v>200.769230769231</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="27" t="n">
+        <f aca="false">Budget!F42</f>
+        <v>50</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <f aca="false">B23*12/52</f>
+        <v>11.5384615384615</v>
+      </c>
+      <c r="D23" s="27" t="n">
+        <f aca="false">Budget!D42*12/52</f>
+        <v>21.4615384615385</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="27" t="n">
+        <f aca="false">Budget!F45</f>
+        <v>250</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <f aca="false">B24*12/52</f>
+        <v>57.6923076923077</v>
+      </c>
+      <c r="D24" s="27" t="n">
+        <f aca="false">Budget!D45*12/52</f>
+        <v>64.6153846153846</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="27" t="n">
+        <f aca="false">Budget!F46</f>
+        <v>100</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <f aca="false">B25*12/52</f>
+        <v>23.0769230769231</v>
+      </c>
+      <c r="D25" s="27" t="n">
+        <f aca="false">Budget!D46*12/52</f>
+        <v>23.3076923076923</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="27" t="n">
+        <f aca="false">Budget!F47</f>
+        <v>75</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <f aca="false">B26*12/52</f>
+        <v>17.3076923076923</v>
+      </c>
+      <c r="D26" s="27" t="n">
+        <f aca="false">Budget!D47*12/52</f>
+        <v>14.5384615384615</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="27" t="n">
+        <f aca="false">Budget!F48</f>
+        <v>170</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <f aca="false">B27*12/52</f>
+        <v>39.2307692307692</v>
+      </c>
+      <c r="D27" s="27" t="n">
+        <f aca="false">Budget!D48*12/52</f>
+        <v>58.1538461538462</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="27" t="n">
+        <f aca="false">Budget!F49</f>
+        <v>90</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <f aca="false">B28*12/52</f>
+        <v>20.7692307692308</v>
+      </c>
+      <c r="D28" s="27" t="n">
+        <f aca="false">Budget!D49*12/52</f>
+        <v>35.3076923076923</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="27" t="n">
+        <f aca="false">Budget!F50</f>
+        <v>240</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <f aca="false">B29*12/52</f>
+        <v>55.3846153846154</v>
+      </c>
+      <c r="D29" s="27" t="n">
+        <f aca="false">Budget!D50*12/52</f>
+        <v>55.3846153846154</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="27" t="n">
+        <f aca="false">Budget!F51</f>
+        <v>75</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <f aca="false">B30*12/52</f>
+        <v>17.3076923076923</v>
+      </c>
+      <c r="D30" s="27" t="n">
+        <f aca="false">Budget!D51*12/52</f>
+        <v>8.76923076923077</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="27" t="n">
+        <f aca="false">Budget!F52</f>
+        <v>115</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <f aca="false">B31*12/52</f>
+        <v>26.5384615384615</v>
+      </c>
+      <c r="D31" s="27" t="n">
+        <f aca="false">Budget!D52*12/52</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="27" t="n">
+        <f aca="false">Budget!F53</f>
+        <v>150</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <f aca="false">B32*12/52</f>
+        <v>34.6153846153846</v>
+      </c>
+      <c r="D32" s="27" t="n">
+        <f aca="false">Budget!D53*12/52</f>
+        <v>36.6923076923077</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B33" s="17" t="n">
+        <f aca="false">SUM(B16:B32)</f>
+        <v>3998</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <f aca="false">SUM(C16:C32)</f>
+        <v>922.615384615385</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <f aca="false">SUM(D16:D32)</f>
+        <v>1111.61538461538</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <f aca="false">B12+B33</f>
+        <v>7438</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <f aca="false">C12+C33</f>
+        <v>1716.46153846154</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <f aca="false">D12+D33</f>
+        <v>1943.30769230769</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="12" t="n">
+        <f aca="false">B35-Budget!F54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3258,152 +3973,152 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>9800.78</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G5" s="27" t="n">
+        <v>167</v>
+      </c>
+      <c r="G5" s="28" t="n">
         <f aca="false">IFERROR(INDEX(A20:A39,MATCH(1,Q20:Q39,0)),"after Jun-28")</f>
-        <v>46447</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="28" t="n">
+        <v>168</v>
+      </c>
+      <c r="B6" s="29" t="n">
         <v>0.2974</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="G6" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="G6" s="28" t="n">
         <f aca="false">IFERROR(INDEX(A20:A39,MATCH(1,R20:R39,0)),"after Jun-28")</f>
-        <v>46478</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>5341.52</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="27" t="n">
+        <v>172</v>
+      </c>
+      <c r="G7" s="28" t="n">
         <f aca="false">IFERROR(INDEX(A20:A39,MATCH(1,S20:S39,0)),"after Jun-28")</f>
-        <v>46478</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="28" t="n">
+        <v>173</v>
+      </c>
+      <c r="B8" s="29" t="n">
         <v>0.1749</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" s="27" t="n">
+        <v>174</v>
+      </c>
+      <c r="G8" s="28" t="n">
         <f aca="false">IFERROR(INDEX(A20:A39,MATCH(1,T20:T39,0)),"after Jun-28")</f>
-        <v>46631</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="28" t="n">
+        <v>175</v>
+      </c>
+      <c r="B9" s="29" t="n">
         <v>0.01</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="G9" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="G9" s="28" t="n">
         <f aca="false">IFERROR(INDEX(A20:A39,MATCH(1,U20:U39,0)),"after Jun-28")</f>
-        <v>46722</v>
+        <v>46813</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="B10" s="13" t="n">
         <v>12081</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">SUM(F20:F39)+SUM(J20:J39)</f>
-        <v>1045.31719806486</v>
+        <v>1354.38058791701</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>30000</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">$B$5*$B$6/12+$B$7*$B$8/12</f>
@@ -3412,121 +4127,121 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>40000</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="29" t="n">
+        <v>187</v>
+      </c>
+      <c r="B13" s="30" t="n">
         <v>46419</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="B14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B15" s="29" t="n">
+        <v>191</v>
+      </c>
+      <c r="B15" s="30" t="n">
         <v>46447</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="31" t="n">
         <v>46327</v>
       </c>
-      <c r="B20" s="31" t="n">
-        <f aca="false">IF(A20&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>2646.77666666667</v>
+      <c r="B20" s="27" t="n">
+        <f aca="false">IF(A20&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>1876.77666666667</v>
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">IF(A20=$B$15,$B$14,0)</f>
@@ -3534,7 +4249,7 @@
       </c>
       <c r="D20" s="12" t="n">
         <f aca="false">B20+C20</f>
-        <v>2646.77666666667</v>
+        <v>1876.77666666667</v>
       </c>
       <c r="E20" s="12" t="n">
         <f aca="false">$B$5</f>
@@ -3546,11 +4261,11 @@
       </c>
       <c r="G20" s="12" t="n">
         <f aca="false">MIN(E20+F20,MAX(D20-K20,0))</f>
-        <v>2515.50881266667</v>
+        <v>1745.50881266667</v>
       </c>
       <c r="H20" s="12" t="n">
         <f aca="false">E20+F20-G20</f>
-        <v>7528.167185</v>
+        <v>8298.167185</v>
       </c>
       <c r="I20" s="12" t="n">
         <f aca="false">$B$7</f>
@@ -3606,12 +4321,12 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="31" t="n">
         <v>46357</v>
       </c>
-      <c r="B21" s="31" t="n">
-        <f aca="false">IF(A21&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>2646.77666666667</v>
+      <c r="B21" s="27" t="n">
+        <f aca="false">IF(A21&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>1876.77666666667</v>
       </c>
       <c r="C21" s="12" t="n">
         <f aca="false">IF(A21=$B$15,$B$14,0)</f>
@@ -3619,23 +4334,23 @@
       </c>
       <c r="D21" s="12" t="n">
         <f aca="false">B21+C21</f>
-        <v>2646.77666666667</v>
+        <v>1876.77666666667</v>
       </c>
       <c r="E21" s="12" t="n">
         <f aca="false">H20</f>
-        <v>7528.167185</v>
+        <v>8298.167185</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">E21*$B$6/12</f>
-        <v>186.573076734917</v>
+        <v>205.656243401583</v>
       </c>
       <c r="G21" s="12" t="n">
         <f aca="false">MIN(E21+F21,MAX(D21-K21,0))</f>
-        <v>2516.82149120667</v>
+        <v>1746.82149120667</v>
       </c>
       <c r="H21" s="12" t="n">
         <f aca="false">E21+F21-G21</f>
-        <v>5197.91877052825</v>
+        <v>6757.00193719491</v>
       </c>
       <c r="I21" s="12" t="n">
         <f aca="false">M20</f>
@@ -3691,12 +4406,12 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="31" t="n">
         <v>46388</v>
       </c>
-      <c r="B22" s="31" t="n">
-        <f aca="false">IF(A22&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>2646.77666666667</v>
+      <c r="B22" s="27" t="n">
+        <f aca="false">IF(A22&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>1876.77666666667</v>
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">IF(A22=$B$15,$B$14,0)</f>
@@ -3704,23 +4419,23 @@
       </c>
       <c r="D22" s="12" t="n">
         <f aca="false">B22+C22</f>
-        <v>2646.77666666667</v>
+        <v>1876.77666666667</v>
       </c>
       <c r="E22" s="12" t="n">
         <f aca="false">H21</f>
-        <v>5197.91877052825</v>
+        <v>6757.00193719491</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">E22*$B$6/12</f>
-        <v>128.821753529592</v>
+        <v>167.461031343481</v>
       </c>
       <c r="G22" s="12" t="n">
         <f aca="false">MIN(E22+F22,MAX(D22-K22,0))</f>
-        <v>2518.12104296127</v>
+        <v>1748.12104296127</v>
       </c>
       <c r="H22" s="12" t="n">
         <f aca="false">E22+F22-G22</f>
-        <v>2808.61948109657</v>
+        <v>5176.34192557713</v>
       </c>
       <c r="I22" s="12" t="n">
         <f aca="false">M21</f>
@@ -3776,12 +4491,12 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="31" t="n">
         <v>46419</v>
       </c>
-      <c r="B23" s="31" t="n">
-        <f aca="false">IF(A23&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>2646.77666666667</v>
+      <c r="B23" s="27" t="n">
+        <f aca="false">IF(A23&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>1876.77666666667</v>
       </c>
       <c r="C23" s="12" t="n">
         <f aca="false">IF(A23=$B$15,$B$14,0)</f>
@@ -3789,23 +4504,23 @@
       </c>
       <c r="D23" s="12" t="n">
         <f aca="false">B23+C23</f>
-        <v>2646.77666666667</v>
+        <v>1876.77666666667</v>
       </c>
       <c r="E23" s="12" t="n">
         <f aca="false">H22</f>
-        <v>2808.61948109657</v>
+        <v>5176.34192557713</v>
       </c>
       <c r="F23" s="12" t="n">
         <f aca="false">E23*$B$6/12</f>
-        <v>69.60695280651</v>
+        <v>128.287007388886</v>
       </c>
       <c r="G23" s="12" t="n">
         <f aca="false">MIN(E23+F23,MAX(D23-K23,0))</f>
-        <v>2519.40759919832</v>
+        <v>1749.40759919832</v>
       </c>
       <c r="H23" s="12" t="n">
         <f aca="false">E23+F23-G23</f>
-        <v>358.818834704759</v>
+        <v>3555.22133376769</v>
       </c>
       <c r="I23" s="12" t="n">
         <f aca="false">M22</f>
@@ -3861,12 +4576,12 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="31" t="n">
         <v>46447</v>
       </c>
-      <c r="B24" s="31" t="n">
-        <f aca="false">IF(A24&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B24" s="27" t="n">
+        <f aca="false">IF(A24&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">IF(A24=$B$15,$B$14,0)</f>
@@ -3874,23 +4589,23 @@
       </c>
       <c r="D24" s="12" t="n">
         <f aca="false">B24+C24</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E24" s="12" t="n">
         <f aca="false">H23</f>
-        <v>358.818834704759</v>
+        <v>3555.22133376769</v>
       </c>
       <c r="F24" s="12" t="n">
         <f aca="false">E24*$B$6/12</f>
-        <v>8.89272678676626</v>
+        <v>88.1102353885426</v>
       </c>
       <c r="G24" s="12" t="n">
         <f aca="false">MIN(E24+F24,MAX(D24-K24,0))</f>
-        <v>367.711561491525</v>
+        <v>2826.93128987301</v>
       </c>
       <c r="H24" s="12" t="n">
         <f aca="false">E24+F24-G24</f>
-        <v>0</v>
+        <v>816.400279283225</v>
       </c>
       <c r="I24" s="12" t="n">
         <f aca="false">M23</f>
@@ -3906,11 +4621,11 @@
       </c>
       <c r="L24" s="12" t="n">
         <f aca="false">MIN(I24+J24,D24-G24)</f>
-        <v>3355.31510517514</v>
+        <v>126.095376793663</v>
       </c>
       <c r="M24" s="12" t="n">
         <f aca="false">I24+J24-L24</f>
-        <v>1850.51264296037</v>
+        <v>5079.73237134185</v>
       </c>
       <c r="N24" s="12" t="n">
         <f aca="false">P23</f>
@@ -3926,7 +4641,7 @@
       </c>
       <c r="Q24" s="5" t="n">
         <f aca="false">IF(H24&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" s="5" t="n">
         <f aca="false">IF(M24&lt;=0.005,1,0)</f>
@@ -3946,12 +4661,12 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="31" t="n">
         <v>46478</v>
       </c>
-      <c r="B25" s="31" t="n">
-        <f aca="false">IF(A25&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B25" s="27" t="n">
+        <f aca="false">IF(A25&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C25" s="12" t="n">
         <f aca="false">IF(A25=$B$15,$B$14,0)</f>
@@ -3959,19 +4674,19 @@
       </c>
       <c r="D25" s="12" t="n">
         <f aca="false">B25+C25</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E25" s="12" t="n">
         <f aca="false">H24</f>
-        <v>0</v>
+        <v>816.400279283225</v>
       </c>
       <c r="F25" s="12" t="n">
         <f aca="false">E25*$B$6/12</f>
-        <v>0</v>
+        <v>20.2331202549026</v>
       </c>
       <c r="G25" s="12" t="n">
         <f aca="false">MIN(E25+F25,MAX(D25-K25,0))</f>
-        <v>0</v>
+        <v>836.633399538128</v>
       </c>
       <c r="H25" s="12" t="n">
         <f aca="false">E25+F25-G25</f>
@@ -3979,23 +4694,23 @@
       </c>
       <c r="I25" s="12" t="n">
         <f aca="false">M24</f>
-        <v>1850.51264296037</v>
+        <v>5079.73237134185</v>
       </c>
       <c r="J25" s="12" t="n">
         <f aca="false">I25*$B$8/12</f>
-        <v>26.9712217711474</v>
+        <v>74.0370993123075</v>
       </c>
       <c r="K25" s="12" t="n">
         <f aca="false">MIN(I25+J25,J25+$B$9*I25)</f>
-        <v>45.4763482007511</v>
+        <v>124.834423025726</v>
       </c>
       <c r="L25" s="12" t="n">
         <f aca="false">MIN(I25+J25,D25-G25)</f>
-        <v>1877.48386473152</v>
+        <v>2116.39326712854</v>
       </c>
       <c r="M25" s="12" t="n">
         <f aca="false">I25+J25-L25</f>
-        <v>0</v>
+        <v>3037.37620352562</v>
       </c>
       <c r="N25" s="12" t="n">
         <f aca="false">P24</f>
@@ -4003,11 +4718,11 @@
       </c>
       <c r="O25" s="12" t="n">
         <f aca="false">MAX(D25-G25-L25,0)</f>
-        <v>1845.54280193515</v>
+        <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
         <f aca="false">N25+O25</f>
-        <v>13926.5428019352</v>
+        <v>12081</v>
       </c>
       <c r="Q25" s="5" t="n">
         <f aca="false">IF(H25&lt;=0.005,1,0)</f>
@@ -4015,11 +4730,11 @@
       </c>
       <c r="R25" s="5" t="n">
         <f aca="false">IF(M25&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="5" t="n">
         <f aca="false">IF(AND(Q25=1,R25=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" s="5" t="n">
         <f aca="false">IF(P25&gt;=$B$11,1,0)</f>
@@ -4031,12 +4746,12 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="31" t="n">
         <v>46508</v>
       </c>
-      <c r="B26" s="31" t="n">
-        <f aca="false">IF(A26&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B26" s="27" t="n">
+        <f aca="false">IF(A26&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C26" s="12" t="n">
         <f aca="false">IF(A26=$B$15,$B$14,0)</f>
@@ -4044,7 +4759,7 @@
       </c>
       <c r="D26" s="12" t="n">
         <f aca="false">B26+C26</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E26" s="12" t="n">
         <f aca="false">H25</f>
@@ -4064,35 +4779,35 @@
       </c>
       <c r="I26" s="12" t="n">
         <f aca="false">M25</f>
-        <v>0</v>
+        <v>3037.37620352562</v>
       </c>
       <c r="J26" s="12" t="n">
         <f aca="false">I26*$B$8/12</f>
-        <v>0</v>
+        <v>44.2697581663859</v>
       </c>
       <c r="K26" s="12" t="n">
         <f aca="false">MIN(I26+J26,J26+$B$9*I26)</f>
-        <v>0</v>
+        <v>74.6435202016421</v>
       </c>
       <c r="L26" s="12" t="n">
         <f aca="false">MIN(I26+J26,D26-G26)</f>
-        <v>0</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="M26" s="12" t="n">
         <f aca="false">I26+J26-L26</f>
-        <v>0</v>
+        <v>128.619295025335</v>
       </c>
       <c r="N26" s="12" t="n">
         <f aca="false">P25</f>
-        <v>13926.5428019352</v>
+        <v>12081</v>
       </c>
       <c r="O26" s="12" t="n">
         <f aca="false">MAX(D26-G26-L26,0)</f>
-        <v>3723.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P26" s="12" t="n">
         <f aca="false">N26+O26</f>
-        <v>17649.5694686018</v>
+        <v>12081</v>
       </c>
       <c r="Q26" s="5" t="n">
         <f aca="false">IF(H26&lt;=0.005,1,0)</f>
@@ -4100,11 +4815,11 @@
       </c>
       <c r="R26" s="5" t="n">
         <f aca="false">IF(M26&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" s="5" t="n">
         <f aca="false">IF(AND(Q26=1,R26=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="5" t="n">
         <f aca="false">IF(P26&gt;=$B$11,1,0)</f>
@@ -4116,12 +4831,12 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="31" t="n">
         <v>46539</v>
       </c>
-      <c r="B27" s="31" t="n">
-        <f aca="false">IF(A27&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B27" s="27" t="n">
+        <f aca="false">IF(A27&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C27" s="12" t="n">
         <f aca="false">IF(A27=$B$15,$B$14,0)</f>
@@ -4129,7 +4844,7 @@
       </c>
       <c r="D27" s="12" t="n">
         <f aca="false">B27+C27</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E27" s="12" t="n">
         <f aca="false">H26</f>
@@ -4149,19 +4864,19 @@
       </c>
       <c r="I27" s="12" t="n">
         <f aca="false">M26</f>
-        <v>0</v>
+        <v>128.619295025335</v>
       </c>
       <c r="J27" s="12" t="n">
         <f aca="false">I27*$B$8/12</f>
-        <v>0</v>
+        <v>1.87462622499426</v>
       </c>
       <c r="K27" s="12" t="n">
         <f aca="false">MIN(I27+J27,J27+$B$9*I27)</f>
-        <v>0</v>
+        <v>3.1608191752476</v>
       </c>
       <c r="L27" s="12" t="n">
         <f aca="false">MIN(I27+J27,D27-G27)</f>
-        <v>0</v>
+        <v>130.493921250329</v>
       </c>
       <c r="M27" s="12" t="n">
         <f aca="false">I27+J27-L27</f>
@@ -4169,15 +4884,15 @@
       </c>
       <c r="N27" s="12" t="n">
         <f aca="false">P26</f>
-        <v>17649.5694686018</v>
+        <v>12081</v>
       </c>
       <c r="O27" s="12" t="n">
         <f aca="false">MAX(D27-G27-L27,0)</f>
-        <v>3723.02666666667</v>
+        <v>2822.53274541634</v>
       </c>
       <c r="P27" s="12" t="n">
         <f aca="false">N27+O27</f>
-        <v>21372.5961352685</v>
+        <v>14903.5327454163</v>
       </c>
       <c r="Q27" s="5" t="n">
         <f aca="false">IF(H27&lt;=0.005,1,0)</f>
@@ -4201,12 +4916,12 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="31" t="n">
         <v>46569</v>
       </c>
-      <c r="B28" s="31" t="n">
-        <f aca="false">IF(A28&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B28" s="27" t="n">
+        <f aca="false">IF(A28&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C28" s="12" t="n">
         <f aca="false">IF(A28=$B$15,$B$14,0)</f>
@@ -4214,7 +4929,7 @@
       </c>
       <c r="D28" s="12" t="n">
         <f aca="false">B28+C28</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E28" s="12" t="n">
         <f aca="false">H27</f>
@@ -4254,15 +4969,15 @@
       </c>
       <c r="N28" s="12" t="n">
         <f aca="false">P27</f>
-        <v>21372.5961352685</v>
+        <v>14903.5327454163</v>
       </c>
       <c r="O28" s="12" t="n">
         <f aca="false">MAX(D28-G28-L28,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P28" s="12" t="n">
         <f aca="false">N28+O28</f>
-        <v>25095.6228019352</v>
+        <v>17856.559412083</v>
       </c>
       <c r="Q28" s="5" t="n">
         <f aca="false">IF(H28&lt;=0.005,1,0)</f>
@@ -4286,12 +5001,12 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="31" t="n">
         <v>46600</v>
       </c>
-      <c r="B29" s="31" t="n">
-        <f aca="false">IF(A29&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B29" s="27" t="n">
+        <f aca="false">IF(A29&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">IF(A29=$B$15,$B$14,0)</f>
@@ -4299,7 +5014,7 @@
       </c>
       <c r="D29" s="12" t="n">
         <f aca="false">B29+C29</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E29" s="12" t="n">
         <f aca="false">H28</f>
@@ -4339,15 +5054,15 @@
       </c>
       <c r="N29" s="12" t="n">
         <f aca="false">P28</f>
-        <v>25095.6228019352</v>
+        <v>17856.559412083</v>
       </c>
       <c r="O29" s="12" t="n">
         <f aca="false">MAX(D29-G29-L29,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P29" s="12" t="n">
         <f aca="false">N29+O29</f>
-        <v>28818.6494686018</v>
+        <v>20809.5860787497</v>
       </c>
       <c r="Q29" s="5" t="n">
         <f aca="false">IF(H29&lt;=0.005,1,0)</f>
@@ -4371,12 +5086,12 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="31" t="n">
         <v>46631</v>
       </c>
-      <c r="B30" s="31" t="n">
-        <f aca="false">IF(A30&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B30" s="27" t="n">
+        <f aca="false">IF(A30&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">IF(A30=$B$15,$B$14,0)</f>
@@ -4384,7 +5099,7 @@
       </c>
       <c r="D30" s="12" t="n">
         <f aca="false">B30+C30</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E30" s="12" t="n">
         <f aca="false">H29</f>
@@ -4424,15 +5139,15 @@
       </c>
       <c r="N30" s="12" t="n">
         <f aca="false">P29</f>
-        <v>28818.6494686018</v>
+        <v>20809.5860787497</v>
       </c>
       <c r="O30" s="12" t="n">
         <f aca="false">MAX(D30-G30-L30,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P30" s="12" t="n">
         <f aca="false">N30+O30</f>
-        <v>32541.6761352685</v>
+        <v>23762.6127454163</v>
       </c>
       <c r="Q30" s="5" t="n">
         <f aca="false">IF(H30&lt;=0.005,1,0)</f>
@@ -4448,7 +5163,7 @@
       </c>
       <c r="T30" s="5" t="n">
         <f aca="false">IF(P30&gt;=$B$11,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" s="5" t="n">
         <f aca="false">IF(P30&gt;=$B$12,1,0)</f>
@@ -4456,12 +5171,12 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="31" t="n">
         <v>46661</v>
       </c>
-      <c r="B31" s="31" t="n">
-        <f aca="false">IF(A31&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B31" s="27" t="n">
+        <f aca="false">IF(A31&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">IF(A31=$B$15,$B$14,0)</f>
@@ -4469,7 +5184,7 @@
       </c>
       <c r="D31" s="12" t="n">
         <f aca="false">B31+C31</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E31" s="12" t="n">
         <f aca="false">H30</f>
@@ -4509,15 +5224,15 @@
       </c>
       <c r="N31" s="12" t="n">
         <f aca="false">P30</f>
-        <v>32541.6761352685</v>
+        <v>23762.6127454163</v>
       </c>
       <c r="O31" s="12" t="n">
         <f aca="false">MAX(D31-G31-L31,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P31" s="12" t="n">
         <f aca="false">N31+O31</f>
-        <v>36264.7028019352</v>
+        <v>26715.639412083</v>
       </c>
       <c r="Q31" s="5" t="n">
         <f aca="false">IF(H31&lt;=0.005,1,0)</f>
@@ -4533,7 +5248,7 @@
       </c>
       <c r="T31" s="5" t="n">
         <f aca="false">IF(P31&gt;=$B$11,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" s="5" t="n">
         <f aca="false">IF(P31&gt;=$B$12,1,0)</f>
@@ -4541,12 +5256,12 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="31" t="n">
         <v>46692</v>
       </c>
-      <c r="B32" s="31" t="n">
-        <f aca="false">IF(A32&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B32" s="27" t="n">
+        <f aca="false">IF(A32&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C32" s="12" t="n">
         <f aca="false">IF(A32=$B$15,$B$14,0)</f>
@@ -4554,7 +5269,7 @@
       </c>
       <c r="D32" s="12" t="n">
         <f aca="false">B32+C32</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E32" s="12" t="n">
         <f aca="false">H31</f>
@@ -4594,15 +5309,15 @@
       </c>
       <c r="N32" s="12" t="n">
         <f aca="false">P31</f>
-        <v>36264.7028019352</v>
+        <v>26715.639412083</v>
       </c>
       <c r="O32" s="12" t="n">
         <f aca="false">MAX(D32-G32-L32,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P32" s="12" t="n">
         <f aca="false">N32+O32</f>
-        <v>39987.7294686018</v>
+        <v>29668.6660787497</v>
       </c>
       <c r="Q32" s="5" t="n">
         <f aca="false">IF(H32&lt;=0.005,1,0)</f>
@@ -4618,7 +5333,7 @@
       </c>
       <c r="T32" s="5" t="n">
         <f aca="false">IF(P32&gt;=$B$11,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" s="5" t="n">
         <f aca="false">IF(P32&gt;=$B$12,1,0)</f>
@@ -4626,12 +5341,12 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="31" t="n">
         <v>46722</v>
       </c>
-      <c r="B33" s="31" t="n">
-        <f aca="false">IF(A33&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B33" s="27" t="n">
+        <f aca="false">IF(A33&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C33" s="12" t="n">
         <f aca="false">IF(A33=$B$15,$B$14,0)</f>
@@ -4639,7 +5354,7 @@
       </c>
       <c r="D33" s="12" t="n">
         <f aca="false">B33+C33</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E33" s="12" t="n">
         <f aca="false">H32</f>
@@ -4679,15 +5394,15 @@
       </c>
       <c r="N33" s="12" t="n">
         <f aca="false">P32</f>
-        <v>39987.7294686018</v>
+        <v>29668.6660787497</v>
       </c>
       <c r="O33" s="12" t="n">
         <f aca="false">MAX(D33-G33-L33,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P33" s="12" t="n">
         <f aca="false">N33+O33</f>
-        <v>43710.7561352685</v>
+        <v>32621.6927454164</v>
       </c>
       <c r="Q33" s="5" t="n">
         <f aca="false">IF(H33&lt;=0.005,1,0)</f>
@@ -4707,16 +5422,16 @@
       </c>
       <c r="U33" s="5" t="n">
         <f aca="false">IF(P33&gt;=$B$12,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="31" t="n">
         <v>46753</v>
       </c>
-      <c r="B34" s="31" t="n">
-        <f aca="false">IF(A34&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B34" s="27" t="n">
+        <f aca="false">IF(A34&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">IF(A34=$B$15,$B$14,0)</f>
@@ -4724,7 +5439,7 @@
       </c>
       <c r="D34" s="12" t="n">
         <f aca="false">B34+C34</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E34" s="12" t="n">
         <f aca="false">H33</f>
@@ -4764,15 +5479,15 @@
       </c>
       <c r="N34" s="12" t="n">
         <f aca="false">P33</f>
-        <v>43710.7561352685</v>
+        <v>32621.6927454164</v>
       </c>
       <c r="O34" s="12" t="n">
         <f aca="false">MAX(D34-G34-L34,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P34" s="12" t="n">
         <f aca="false">N34+O34</f>
-        <v>47433.7828019352</v>
+        <v>35574.719412083</v>
       </c>
       <c r="Q34" s="5" t="n">
         <f aca="false">IF(H34&lt;=0.005,1,0)</f>
@@ -4792,16 +5507,16 @@
       </c>
       <c r="U34" s="5" t="n">
         <f aca="false">IF(P34&gt;=$B$12,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="31" t="n">
         <v>46784</v>
       </c>
-      <c r="B35" s="31" t="n">
-        <f aca="false">IF(A35&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B35" s="27" t="n">
+        <f aca="false">IF(A35&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C35" s="12" t="n">
         <f aca="false">IF(A35=$B$15,$B$14,0)</f>
@@ -4809,7 +5524,7 @@
       </c>
       <c r="D35" s="12" t="n">
         <f aca="false">B35+C35</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E35" s="12" t="n">
         <f aca="false">H34</f>
@@ -4849,15 +5564,15 @@
       </c>
       <c r="N35" s="12" t="n">
         <f aca="false">P34</f>
-        <v>47433.7828019352</v>
+        <v>35574.719412083</v>
       </c>
       <c r="O35" s="12" t="n">
         <f aca="false">MAX(D35-G35-L35,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P35" s="12" t="n">
         <f aca="false">N35+O35</f>
-        <v>51156.8094686018</v>
+        <v>38527.7460787497</v>
       </c>
       <c r="Q35" s="5" t="n">
         <f aca="false">IF(H35&lt;=0.005,1,0)</f>
@@ -4877,16 +5592,16 @@
       </c>
       <c r="U35" s="5" t="n">
         <f aca="false">IF(P35&gt;=$B$12,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="31" t="n">
         <v>46813</v>
       </c>
-      <c r="B36" s="31" t="n">
-        <f aca="false">IF(A36&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B36" s="27" t="n">
+        <f aca="false">IF(A36&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C36" s="12" t="n">
         <f aca="false">IF(A36=$B$15,$B$14,0)</f>
@@ -4894,7 +5609,7 @@
       </c>
       <c r="D36" s="12" t="n">
         <f aca="false">B36+C36</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E36" s="12" t="n">
         <f aca="false">H35</f>
@@ -4934,15 +5649,15 @@
       </c>
       <c r="N36" s="12" t="n">
         <f aca="false">P35</f>
-        <v>51156.8094686018</v>
+        <v>38527.7460787497</v>
       </c>
       <c r="O36" s="12" t="n">
         <f aca="false">MAX(D36-G36-L36,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P36" s="12" t="n">
         <f aca="false">N36+O36</f>
-        <v>54879.8361352685</v>
+        <v>41480.7727454164</v>
       </c>
       <c r="Q36" s="5" t="n">
         <f aca="false">IF(H36&lt;=0.005,1,0)</f>
@@ -4966,12 +5681,12 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="31" t="n">
         <v>46844</v>
       </c>
-      <c r="B37" s="31" t="n">
-        <f aca="false">IF(A37&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B37" s="27" t="n">
+        <f aca="false">IF(A37&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C37" s="12" t="n">
         <f aca="false">IF(A37=$B$15,$B$14,0)</f>
@@ -4979,7 +5694,7 @@
       </c>
       <c r="D37" s="12" t="n">
         <f aca="false">B37+C37</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E37" s="12" t="n">
         <f aca="false">H36</f>
@@ -5019,15 +5734,15 @@
       </c>
       <c r="N37" s="12" t="n">
         <f aca="false">P36</f>
-        <v>54879.8361352685</v>
+        <v>41480.7727454164</v>
       </c>
       <c r="O37" s="12" t="n">
         <f aca="false">MAX(D37-G37-L37,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P37" s="12" t="n">
         <f aca="false">N37+O37</f>
-        <v>58602.8628019352</v>
+        <v>44433.799412083</v>
       </c>
       <c r="Q37" s="5" t="n">
         <f aca="false">IF(H37&lt;=0.005,1,0)</f>
@@ -5051,12 +5766,12 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="30" t="n">
+      <c r="A38" s="31" t="n">
         <v>46874</v>
       </c>
-      <c r="B38" s="31" t="n">
-        <f aca="false">IF(A38&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B38" s="27" t="n">
+        <f aca="false">IF(A38&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">IF(A38=$B$15,$B$14,0)</f>
@@ -5064,7 +5779,7 @@
       </c>
       <c r="D38" s="12" t="n">
         <f aca="false">B38+C38</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E38" s="12" t="n">
         <f aca="false">H37</f>
@@ -5104,15 +5819,15 @@
       </c>
       <c r="N38" s="12" t="n">
         <f aca="false">P37</f>
-        <v>58602.8628019352</v>
+        <v>44433.799412083</v>
       </c>
       <c r="O38" s="12" t="n">
         <f aca="false">MAX(D38-G38-L38,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P38" s="12" t="n">
         <f aca="false">N38+O38</f>
-        <v>62325.8894686019</v>
+        <v>47386.8260787497</v>
       </c>
       <c r="Q38" s="5" t="n">
         <f aca="false">IF(H38&lt;=0.005,1,0)</f>
@@ -5136,12 +5851,12 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="30" t="n">
+      <c r="A39" s="31" t="n">
         <v>46905</v>
       </c>
-      <c r="B39" s="31" t="n">
-        <f aca="false">IF(A39&lt;=$B$13,Budget!$F$67,Budget!$F$68)</f>
-        <v>3723.02666666667</v>
+      <c r="B39" s="27" t="n">
+        <f aca="false">IF(A39&lt;=$B$13,Budget!$F$68,Budget!$F$69)</f>
+        <v>2953.02666666667</v>
       </c>
       <c r="C39" s="12" t="n">
         <f aca="false">IF(A39=$B$15,$B$14,0)</f>
@@ -5149,7 +5864,7 @@
       </c>
       <c r="D39" s="12" t="n">
         <f aca="false">B39+C39</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="E39" s="12" t="n">
         <f aca="false">H38</f>
@@ -5189,15 +5904,15 @@
       </c>
       <c r="N39" s="12" t="n">
         <f aca="false">P38</f>
-        <v>62325.8894686019</v>
+        <v>47386.8260787497</v>
       </c>
       <c r="O39" s="12" t="n">
         <f aca="false">MAX(D39-G39-L39,0)</f>
-        <v>3723.02666666667</v>
+        <v>2953.02666666667</v>
       </c>
       <c r="P39" s="12" t="n">
         <f aca="false">N39+O39</f>
-        <v>66048.9161352685</v>
+        <v>50339.8527454164</v>
       </c>
       <c r="Q39" s="5" t="n">
         <f aca="false">IF(H39&lt;=0.005,1,0)</f>
@@ -5231,7 +5946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5247,12 +5962,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5260,48 +5975,48 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -5319,7 +6034,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>17767.46</v>
@@ -5366,7 +6081,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>6410.38</v>
@@ -5413,7 +6128,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>1459.54</v>
@@ -5460,7 +6175,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">SUM(B6:B8)</f>
@@ -5517,7 +6232,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -5535,7 +6250,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>4300</v>
@@ -5582,7 +6297,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="B13" s="13" t="n">
         <v>32.71</v>
@@ -5629,7 +6344,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="B14" s="13" t="n">
         <v>0</v>
@@ -5676,7 +6391,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>183.82</v>
@@ -5723,7 +6438,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="B16" s="13" t="n">
         <v>500</v>
@@ -5770,7 +6485,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">SUM(B12:B16)</f>
@@ -5827,7 +6542,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -5845,7 +6560,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="B20" s="13" t="n">
         <v>6857.93</v>
@@ -5939,7 +6654,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="B22" s="13" t="n">
         <v>1057.39</v>
@@ -6033,7 +6748,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="B24" s="13" t="n">
         <v>0</v>
@@ -6080,7 +6795,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="B25" s="13" t="n">
         <v>856.83</v>
@@ -6127,7 +6842,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="B26" s="13" t="n">
         <v>286.67</v>
@@ -6174,7 +6889,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="B27" s="13" t="n">
         <v>614</v>
@@ -6221,7 +6936,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B28" s="13" t="n">
         <v>323.39</v>
@@ -6268,7 +6983,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="B29" s="13" t="n">
         <v>368.15</v>
@@ -6315,7 +7030,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="B30" s="13" t="n">
         <v>400.62</v>
@@ -6362,7 +7077,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B31" s="13" t="n">
         <v>134.97</v>
@@ -6409,7 +7124,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="B32" s="13" t="n">
         <v>178.9</v>
@@ -6456,7 +7171,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="B33" s="13" t="n">
         <v>115.5</v>
@@ -6503,7 +7218,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="B34" s="13" t="n">
         <v>760</v>
@@ -6550,7 +7265,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="B35" s="13" t="n">
         <v>155</v>
@@ -6597,7 +7312,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="B36" s="13" t="n">
         <v>138.58</v>
@@ -6644,7 +7359,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="B37" s="13" t="n">
         <v>473.56</v>
@@ -6691,7 +7406,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="B38" s="13" t="n">
         <v>431.52</v>
@@ -6738,7 +7453,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="B39" s="13" t="n">
         <v>359.9</v>
@@ -6785,7 +7500,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="B40" s="13" t="n">
         <v>27.6</v>
@@ -6832,7 +7547,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="B41" s="13" t="n">
         <v>557.68</v>
@@ -6879,7 +7594,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="B42" s="13" t="n">
         <v>385.13</v>
@@ -6926,7 +7641,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="B43" s="13" t="n">
         <v>209</v>
@@ -6973,7 +7688,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="B44" s="13" t="n">
         <v>266.15</v>
@@ -7020,7 +7735,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B45" s="13" t="n">
         <v>501.45</v>
@@ -7067,7 +7782,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="B46" s="13" t="n">
         <v>469.36</v>
@@ -7114,7 +7829,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B47" s="13" t="n">
         <v>1.11</v>
@@ -7161,7 +7876,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="B48" s="13" t="n">
         <v>72.9</v>
@@ -7208,7 +7923,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="B49" s="13" t="n">
         <v>0.5</v>
@@ -7255,7 +7970,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="B50" s="13" t="n">
         <v>355.78</v>
@@ -7302,7 +8017,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="B51" s="13" t="n">
         <v>97.3</v>
@@ -7349,7 +8064,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B52" s="13" t="n">
         <v>129.41</v>
@@ -7396,7 +8111,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="B53" s="13" t="n">
         <v>465.78</v>
@@ -7443,7 +8158,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B54" s="13" t="n">
         <v>240</v>
@@ -7490,7 +8205,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="B55" s="13" t="n">
         <v>729.5</v>
@@ -7537,7 +8252,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="B56" s="13" t="n">
         <v>2.25</v>
@@ -7584,7 +8299,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="B57" s="13" t="n">
         <v>0</v>
@@ -7631,7 +8346,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="B58" s="13" t="n">
         <v>127.73</v>
@@ -7678,7 +8393,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="B59" s="17" t="n">
         <f aca="false">SUM(B20:B58)</f>
@@ -7735,7 +8450,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="B61" s="25" t="n">
         <f aca="false">B17+B59</f>
@@ -7792,7 +8507,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="B62" s="25" t="n">
         <f aca="false">B9</f>
@@ -7849,7 +8564,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="B63" s="9" t="n">
         <f aca="false">B62-B61</f>
@@ -7915,7 +8630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7935,35 +8650,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>20</v>
@@ -7971,10 +8686,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>72.97</v>
@@ -7984,25 +8699,25 @@
         <v>875.64</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">IF(E5="Cut",D5,0)</f>
-        <v>875.64</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>82.99</v>
@@ -8012,25 +8727,25 @@
         <v>995.88</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">IF(E6="Cut",D6,0)</f>
         <v>0</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>26.99</v>
@@ -8040,23 +8755,23 @@
         <v>323.88</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">IF(E7="Cut",D7,0)</f>
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>18.99</v>
@@ -8066,25 +8781,25 @@
         <v>227.88</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">IF(E8="Cut",D8,0)</f>
         <v>0</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>12.99</v>
@@ -8094,23 +8809,23 @@
         <v>155.88</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">IF(E9="Cut",D9,0)</f>
         <v>0</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>139</v>
@@ -8120,25 +8835,25 @@
         <v>139</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">IF(E10="Cut",D10,0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>4.99</v>
@@ -8148,25 +8863,25 @@
         <v>59.88</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">IF(E11="Cut",D11,0)</f>
         <v>0</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>6.36</v>
@@ -8176,25 +8891,25 @@
         <v>76.32</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">IF(E12="Cut",D12,0)</f>
         <v>0</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>11.99</v>
@@ -8204,25 +8919,25 @@
         <v>143.88</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">IF(E13="Cut",D13,0)</f>
         <v>0</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>8.99</v>
@@ -8232,25 +8947,25 @@
         <v>107.88</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">IF(E14="Cut",D14,0)</f>
         <v>0</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>25</v>
@@ -8260,25 +8975,25 @@
         <v>300</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F15" s="12" t="n">
         <f aca="false">IF(E15="Cut",D15,0)</f>
         <v>0</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>27.72</v>
@@ -8288,25 +9003,25 @@
         <v>332.64</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F16" s="12" t="n">
         <f aca="false">IF(E16="Cut",D16,0)</f>
         <v>0</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>99.99</v>
@@ -8316,23 +9031,23 @@
         <v>99.99</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F17" s="12" t="n">
         <f aca="false">IF(E17="Cut",D17,0)</f>
         <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>150</v>
@@ -8342,23 +9057,23 @@
         <v>150</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F18" s="12" t="n">
         <f aca="false">IF(E18="Cut",D18,0)</f>
         <v>0</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>20.7</v>
@@ -8368,25 +9083,25 @@
         <v>248.4</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F19" s="12" t="n">
         <f aca="false">IF(E19="Cut",D19,0)</f>
         <v>0</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>10</v>
@@ -8396,25 +9111,25 @@
         <v>120</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">IF(E20="Cut",D20,0)</f>
         <v>0</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>32.99</v>
@@ -8424,25 +9139,25 @@
         <v>395.88</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">IF(E21="Cut",D21,0)</f>
         <v>0</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>13.94</v>
@@ -8452,25 +9167,25 @@
         <v>167.28</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">IF(E22="Cut",D22,0)</f>
         <v>0</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>20.76</v>
@@ -8480,25 +9195,25 @@
         <v>249.12</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F23" s="12" t="n">
         <f aca="false">IF(E23="Cut",D23,0)</f>
         <v>0</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>10.63</v>
@@ -8508,23 +9223,23 @@
         <v>127.56</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F24" s="12" t="n">
         <f aca="false">IF(E24="Cut",D24,0)</f>
         <v>0</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>21.25</v>
@@ -8534,23 +9249,23 @@
         <v>255</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F25" s="12" t="n">
         <f aca="false">IF(E25="Cut",D25,0)</f>
         <v>0</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>381.44</v>
@@ -8560,25 +9275,25 @@
         <v>381.44</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F26" s="12" t="n">
         <f aca="false">IF(E26="Cut",D26,0)</f>
         <v>0</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>212.49</v>
@@ -8588,25 +9303,25 @@
         <v>212.49</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F27" s="12" t="n">
         <f aca="false">IF(E27="Cut",D27,0)</f>
         <v>0</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>114.75</v>
@@ -8616,25 +9331,25 @@
         <v>229.5</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F28" s="12" t="n">
         <f aca="false">IF(E28="Cut",D28,0)</f>
         <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>548</v>
@@ -8644,25 +9359,25 @@
         <v>548</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F29" s="12" t="n">
         <f aca="false">IF(E29="Cut",D29,0)</f>
         <v>0</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>32.95</v>
@@ -8672,25 +9387,25 @@
         <v>395.4</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F30" s="12" t="n">
         <f aca="false">IF(E30="Cut",D30,0)</f>
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>115.23</v>
@@ -8700,25 +9415,25 @@
         <v>1382.76</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F31" s="12" t="n">
         <f aca="false">IF(E31="Cut",D31,0)</f>
         <v>0</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>25</v>
@@ -8728,22 +9443,22 @@
         <v>300</v>
       </c>
       <c r="E32" s="32" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F32" s="12" t="n">
         <f aca="false">IF(E32="Cut",D32,0)</f>
         <v>0</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="D33" s="17" t="n">
         <f aca="false">SUM(D5:D32)</f>
@@ -8751,12 +9466,12 @@
       </c>
       <c r="F33" s="17" t="n">
         <f aca="false">SUM(F5:F32)</f>
-        <v>875.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="D34" s="12" t="n">
         <f aca="false">SUMIF(E5:E32,"Review",D5:D32)</f>
@@ -8765,7 +9480,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -8779,7 +9494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8793,148 +9508,148 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
+++ b/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="442">
   <si>
     <t xml:space="preserve">Household Budget — October 2026 rebuild</t>
   </si>
@@ -660,10 +660,61 @@
     <t xml:space="preserve">Patriots tickets paid in Feb.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bonus/extra lump (net) — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base case $0. Mar 2026 net bonus deposit was ≈ $38.9k — NOT assumed.</t>
+    <t xml:space="preserve">Last March net bonus deposit (all 3 accounts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar-2026 deposits ≈ $38.9k net, at a 0.95 multiplier (per you).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last year's multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected multiplier after Flagship's correction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — you did not give the number. Net bonus scales linearly with it (same salary/target).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus lump (net) — scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last year's net × (expected ÷ 0.95). Flagship's March payout per your negotiation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portion of bonus kept for lifestyle (intentional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your stack: debt → liquidity → lifestyle → investible. Enter an amount to carve it out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diogo base salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost-of-living raise %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You said assume 2–4%; midpoint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of the raise that reaches take-home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION: ~42% marginal (35% federal + 5% MA + Medicare).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise effective from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION — confirm the start date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise, net per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary × raise % × net share ÷ 12. Added to paydown; budget lines unchanged.</t>
   </si>
   <si>
     <t xml:space="preserve">Bonus lump lands in month</t>
@@ -1294,6 +1345,9 @@
   </si>
   <si>
     <t xml:space="preserve">Categories are keyword-based on merchant strings; unclassified items are shown on Actuals. Weekly checks = cleaning help ($160/wk); DoorDash/Grubhub = family takeout (per you). HELOC payment of ~$1,100 is assumed from Nov-26. Synchrony = 0% AC-repair loan; Wells Fargo = 0% plumbing loan, assumed $450/mo (one payment seen).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job change: new job starts 11/2. Take-home is assumed unchanged at the new employer (pay, cadence and benefits not yet known). March bonus and 2–4% raise are per your negotiation; the multiplier, raise start date and tax share are my assumptions.</t>
   </si>
   <si>
     <t xml:space="preserve">Not financial, tax, or legal advice.</t>
@@ -1303,7 +1357,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0"/>
@@ -1311,6 +1365,8 @@
     <numFmt numFmtId="168" formatCode="mmm\-yy"/>
     <numFmt numFmtId="169" formatCode="0.00%"/>
     <numFmt numFmtId="170" formatCode="0%"/>
+    <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1452,7 +1508,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1570,6 +1626,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4197,7 +4261,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -4251,8 +4315,8 @@
         <v>174</v>
       </c>
       <c r="G5" s="26" t="n">
-        <f aca="false">IFERROR(INDEX(A29:A76,MATCH(1,Q29:Q76,0)),"after Oct-30")</f>
-        <v>46508</v>
+        <f aca="false">IFERROR(INDEX(A38:A85,MATCH(1,Q38:Q85,0)),"after Oct-30")</f>
+        <v>46447</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4269,8 +4333,8 @@
         <v>177</v>
       </c>
       <c r="G6" s="26" t="n">
-        <f aca="false">IFERROR(INDEX(A29:A76,MATCH(1,R29:R76,0)),"after Oct-30")</f>
-        <v>46569</v>
+        <f aca="false">IFERROR(INDEX(A38:A85,MATCH(1,R38:R85,0)),"after Oct-30")</f>
+        <v>46447</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4287,8 +4351,8 @@
         <v>179</v>
       </c>
       <c r="G7" s="26" t="n">
-        <f aca="false">IFERROR(INDEX(A29:A76,MATCH(1,S29:S76,0)),"after Oct-30")</f>
-        <v>46569</v>
+        <f aca="false">IFERROR(INDEX(A38:A85,MATCH(1,S38:S85,0)),"after Oct-30")</f>
+        <v>46447</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4305,8 +4369,8 @@
         <v>181</v>
       </c>
       <c r="G8" s="26" t="n">
-        <f aca="false">IFERROR(INDEX(A29:A76,MATCH(1,T29:T76,0)),"after Oct-30")</f>
-        <v>47027</v>
+        <f aca="false">IFERROR(INDEX(A38:A85,MATCH(1,T38:T85,0)),"after Oct-30")</f>
+        <v>46508</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4323,8 +4387,8 @@
         <v>184</v>
       </c>
       <c r="G9" s="26" t="n">
-        <f aca="false">IFERROR(INDEX(A29:A76,MATCH(1,U29:U76,0)),"after Oct-30")</f>
-        <v>47423</v>
+        <f aca="false">IFERROR(INDEX(A38:A85,MATCH(1,U38:U85,0)),"after Oct-30")</f>
+        <v>46844</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4341,8 +4405,8 @@
         <v>187</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUM(F29:F76)+SUM(J29:J76)</f>
-        <v>1642.65278795969</v>
+        <f aca="false">SUM(F38:F85)+SUM(J38:J85)</f>
+        <v>1291.44070586063</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4486,7 +4550,7 @@
         <v>211</v>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0</v>
+        <v>38900</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>212</v>
@@ -4496,1017 +4560,281 @@
       <c r="A23" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B23" s="29" t="n">
-        <v>46447</v>
-      </c>
-      <c r="C23" s="2"/>
+      <c r="B23" s="30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B24" s="29" t="n">
-        <v>47119</v>
+        <v>215</v>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B25" s="25" t="n">
+        <v>217</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <f aca="false">$B$22*$B$24/$B$23</f>
+        <v>40947.3684210526</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>339000</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B28" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" s="29" t="n">
+        <v>46388</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" s="12" t="n">
+        <f aca="false">$B$27*$B$28*$B$29/12</f>
+        <v>491.55</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B32" s="29" t="n">
+        <v>46447</v>
+      </c>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>47119</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B34" s="25" t="n">
         <f aca="false">Budget!F16</f>
         <v>342</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="P28" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q28" s="10" t="s">
+      <c r="C34" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="R28" s="10" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="S28" s="10" t="s">
+      <c r="B37" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="T28" s="10" t="s">
+      <c r="C37" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="U28" s="10" t="s">
+      <c r="D37" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="V28" s="10" t="s">
+      <c r="E37" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="W28" s="10" t="s">
+      <c r="F37" s="10" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="n">
+      <c r="G37" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q37" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="R37" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="S37" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="T37" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="U37" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="V37" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="W37" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="32" t="n">
         <v>46327</v>
       </c>
-      <c r="B29" s="25" t="n">
-        <f aca="false">IF(A29&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A29&gt;$B$24,$B$25,0)</f>
+      <c r="B38" s="25" t="n">
+        <f aca="false">IF(A38&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A38&gt;$B$33,$B$34,0)+IF(A38&gt;=$B$30,$B$31,0)</f>
         <v>1426.77666666667</v>
       </c>
-      <c r="C29" s="12" t="n">
-        <f aca="false">IF(A29=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <f aca="false">B29+C29</f>
+      <c r="C38" s="12" t="n">
+        <f aca="false">IF(A38=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <f aca="false">B38+C38</f>
         <v>1426.77666666667</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E38" s="12" t="n">
         <f aca="false">$B$5</f>
         <v>9800.78</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <f aca="false">E29*$B$6/12</f>
+      <c r="F38" s="12" t="n">
+        <f aca="false">E38*$B$6/12</f>
         <v>242.895997666667</v>
       </c>
-      <c r="G29" s="12" t="n">
-        <f aca="false">MIN(E29+F29,MAX(D29-K29,0))</f>
+      <c r="G38" s="12" t="n">
+        <f aca="false">MIN(E38+F38,MAX(D38-K38,0))</f>
         <v>1295.50881266667</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <f aca="false">E29+F29-G29</f>
+      <c r="H38" s="12" t="n">
+        <f aca="false">E38+F38-G38</f>
         <v>8748.167185</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <f aca="false">$B$7</f>
         <v>5341.52</v>
       </c>
-      <c r="J29" s="12" t="n">
-        <f aca="false">I29*$B$8/12</f>
+      <c r="J38" s="12" t="n">
+        <f aca="false">I38*$B$8/12</f>
         <v>77.852654</v>
       </c>
-      <c r="K29" s="12" t="n">
-        <f aca="false">MIN(I29+J29,J29+$B$9*I29)</f>
+      <c r="K38" s="12" t="n">
+        <f aca="false">MIN(I38+J38,J38+$B$9*I38)</f>
         <v>131.267854</v>
       </c>
-      <c r="L29" s="12" t="n">
-        <f aca="false">MIN(I29+J29,D29-G29)</f>
+      <c r="L38" s="12" t="n">
+        <f aca="false">MIN(I38+J38,D38-G38)</f>
         <v>131.267854</v>
       </c>
-      <c r="M29" s="12" t="n">
-        <f aca="false">I29+J29-L29</f>
+      <c r="M38" s="12" t="n">
+        <f aca="false">I38+J38-L38</f>
         <v>5288.1048</v>
       </c>
-      <c r="N29" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <f aca="false">$B$10</f>
         <v>12081</v>
       </c>
-      <c r="O29" s="12" t="n">
-        <f aca="false">MIN(MAX(D29-G29-L29,0),MAX($B$15-$B$18-N29,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P29" s="12" t="n">
-        <f aca="false">N29+O29</f>
-        <v>12081</v>
-      </c>
-      <c r="Q29" s="5" t="n">
-        <f aca="false">IF(H29&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="5" t="n">
-        <f aca="false">IF(M29&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S29" s="5" t="n">
-        <f aca="false">IF(AND(Q29=1,R29=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T29" s="5" t="n">
-        <f aca="false">IF(P29&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U29" s="5" t="n">
-        <f aca="false">IF(P29+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V29" s="12" t="n">
-        <f aca="false">MAX(D29-G29-L29,0)-O29</f>
-        <v>0</v>
-      </c>
-      <c r="W29" s="12" t="n">
-        <f aca="false">P29+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B30" s="25" t="n">
-        <f aca="false">IF(A30&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A30&gt;$B$24,$B$25,0)</f>
-        <v>1426.77666666667</v>
-      </c>
-      <c r="C30" s="12" t="n">
-        <f aca="false">IF(A30=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <f aca="false">B30+C30</f>
-        <v>1426.77666666667</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <f aca="false">H29</f>
-        <v>8748.167185</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <f aca="false">E30*$B$6/12</f>
-        <v>216.808743401583</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <f aca="false">MIN(E30+F30,MAX(D30-K30,0))</f>
-        <v>1296.82149120667</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <f aca="false">E30+F30-G30</f>
-        <v>7668.15443719491</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <f aca="false">M29</f>
-        <v>5288.1048</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <f aca="false">I30*$B$8/12</f>
-        <v>77.07412746</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <f aca="false">MIN(I30+J30,J30+$B$9*I30)</f>
-        <v>129.95517546</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <f aca="false">MIN(I30+J30,D30-G30)</f>
-        <v>129.95517546</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <f aca="false">I30+J30-L30</f>
-        <v>5235.223752</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <f aca="false">P29</f>
-        <v>12081</v>
-      </c>
-      <c r="O30" s="12" t="n">
-        <f aca="false">MIN(MAX(D30-G30-L30,0),MAX($B$15-$B$18-N30,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P30" s="12" t="n">
-        <f aca="false">N30+O30</f>
-        <v>12081</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <f aca="false">IF(H30&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <f aca="false">IF(M30&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <f aca="false">IF(AND(Q30=1,R30=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <f aca="false">IF(P30&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <f aca="false">IF(P30+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="12" t="n">
-        <f aca="false">MAX(D30-G30-L30,0)-O30</f>
-        <v>0</v>
-      </c>
-      <c r="W30" s="12" t="n">
-        <f aca="false">P30+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30" t="n">
-        <v>46388</v>
-      </c>
-      <c r="B31" s="25" t="n">
-        <f aca="false">IF(A31&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A31&gt;$B$24,$B$25,0)</f>
-        <v>1426.77666666667</v>
-      </c>
-      <c r="C31" s="12" t="n">
-        <f aca="false">IF(A31=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="12" t="n">
-        <f aca="false">B31+C31</f>
-        <v>1426.77666666667</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <f aca="false">H30</f>
-        <v>7668.15443719491</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <f aca="false">E31*$B$6/12</f>
-        <v>190.042427468481</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <f aca="false">MIN(E31+F31,MAX(D31-K31,0))</f>
-        <v>1298.12104296127</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <f aca="false">E31+F31-G31</f>
-        <v>6560.07582170213</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <f aca="false">M30</f>
-        <v>5235.223752</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <f aca="false">I31*$B$8/12</f>
-        <v>76.3033861854</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <f aca="false">MIN(I31+J31,J31+$B$9*I31)</f>
-        <v>128.6556237054</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <f aca="false">MIN(I31+J31,D31-G31)</f>
-        <v>128.6556237054</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <f aca="false">I31+J31-L31</f>
-        <v>5182.87151448</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <f aca="false">P30</f>
-        <v>12081</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <f aca="false">MIN(MAX(D31-G31-L31,0),MAX($B$15-$B$18-N31,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="12" t="n">
-        <f aca="false">N31+O31</f>
-        <v>12081</v>
-      </c>
-      <c r="Q31" s="5" t="n">
-        <f aca="false">IF(H31&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="5" t="n">
-        <f aca="false">IF(M31&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S31" s="5" t="n">
-        <f aca="false">IF(AND(Q31=1,R31=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T31" s="5" t="n">
-        <f aca="false">IF(P31&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U31" s="5" t="n">
-        <f aca="false">IF(P31+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="12" t="n">
-        <f aca="false">MAX(D31-G31-L31,0)-O31</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="12" t="n">
-        <f aca="false">P31+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="n">
-        <v>46419</v>
-      </c>
-      <c r="B32" s="25" t="n">
-        <f aca="false">IF(A32&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A32&gt;$B$24,$B$25,0)</f>
-        <v>1426.77666666667</v>
-      </c>
-      <c r="C32" s="12" t="n">
-        <f aca="false">IF(A32=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <f aca="false">B32+C32</f>
-        <v>1426.77666666667</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <f aca="false">H31</f>
-        <v>6560.07582170213</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <f aca="false">E32*$B$6/12</f>
-        <v>162.580545781184</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <f aca="false">MIN(E32+F32,MAX(D32-K32,0))</f>
-        <v>1299.40759919832</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <f aca="false">E32+F32-G32</f>
-        <v>5423.24876828499</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <f aca="false">M31</f>
-        <v>5182.87151448</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <f aca="false">I32*$B$8/12</f>
-        <v>75.540352323546</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <f aca="false">MIN(I32+J32,J32+$B$9*I32)</f>
-        <v>127.369067468346</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <f aca="false">MIN(I32+J32,D32-G32)</f>
-        <v>127.369067468346</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <f aca="false">I32+J32-L32</f>
-        <v>5131.0427993352</v>
-      </c>
-      <c r="N32" s="12" t="n">
-        <f aca="false">P31</f>
-        <v>12081</v>
-      </c>
-      <c r="O32" s="12" t="n">
-        <f aca="false">MIN(MAX(D32-G32-L32,0),MAX($B$15-$B$18-N32,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="12" t="n">
-        <f aca="false">N32+O32</f>
-        <v>12081</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <f aca="false">IF(H32&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <f aca="false">IF(M32&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S32" s="5" t="n">
-        <f aca="false">IF(AND(Q32=1,R32=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T32" s="5" t="n">
-        <f aca="false">IF(P32&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="5" t="n">
-        <f aca="false">IF(P32+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <f aca="false">MAX(D32-G32-L32,0)-O32</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="12" t="n">
-        <f aca="false">P32+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30" t="n">
-        <v>46447</v>
-      </c>
-      <c r="B33" s="25" t="n">
-        <f aca="false">IF(A33&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A33&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="C33" s="12" t="n">
-        <f aca="false">IF(A33=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <f aca="false">B33+C33</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <f aca="false">H32</f>
-        <v>5423.24876828499</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <f aca="false">E33*$B$6/12</f>
-        <v>134.406181973996</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <f aca="false">MIN(E33+F33,MAX(D33-K33,0))</f>
-        <v>2376.93128987301</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <f aca="false">E33+F33-G33</f>
-        <v>3180.72366038598</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <f aca="false">M32</f>
-        <v>5131.0427993352</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <f aca="false">I33*$B$8/12</f>
-        <v>74.7849488003106</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <f aca="false">MIN(I33+J33,J33+$B$9*I33)</f>
-        <v>126.095376793663</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <f aca="false">MIN(I33+J33,D33-G33)</f>
-        <v>126.095376793663</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <f aca="false">I33+J33-L33</f>
-        <v>5079.73237134185</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <f aca="false">P32</f>
-        <v>12081</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <f aca="false">MIN(MAX(D33-G33-L33,0),MAX($B$15-$B$18-N33,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="12" t="n">
-        <f aca="false">N33+O33</f>
-        <v>12081</v>
-      </c>
-      <c r="Q33" s="5" t="n">
-        <f aca="false">IF(H33&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R33" s="5" t="n">
-        <f aca="false">IF(M33&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S33" s="5" t="n">
-        <f aca="false">IF(AND(Q33=1,R33=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T33" s="5" t="n">
-        <f aca="false">IF(P33&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U33" s="5" t="n">
-        <f aca="false">IF(P33+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V33" s="12" t="n">
-        <f aca="false">MAX(D33-G33-L33,0)-O33</f>
-        <v>0</v>
-      </c>
-      <c r="W33" s="12" t="n">
-        <f aca="false">P33+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30" t="n">
-        <v>46478</v>
-      </c>
-      <c r="B34" s="25" t="n">
-        <f aca="false">IF(A34&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A34&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="C34" s="12" t="n">
-        <f aca="false">IF(A34=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <f aca="false">B34+C34</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <f aca="false">H33</f>
-        <v>3180.72366038598</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <f aca="false">E34*$B$6/12</f>
-        <v>78.8289347165658</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <f aca="false">MIN(E34+F34,MAX(D34-K34,0))</f>
-        <v>2378.19224364094</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <f aca="false">E34+F34-G34</f>
-        <v>881.360351461602</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <f aca="false">M33</f>
-        <v>5079.73237134185</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <f aca="false">I34*$B$8/12</f>
-        <v>74.0370993123075</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <f aca="false">MIN(I34+J34,J34+$B$9*I34)</f>
-        <v>124.834423025726</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <f aca="false">MIN(I34+J34,D34-G34)</f>
-        <v>124.834423025726</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <f aca="false">I34+J34-L34</f>
-        <v>5028.93504762843</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <f aca="false">P33</f>
-        <v>12081</v>
-      </c>
-      <c r="O34" s="12" t="n">
-        <f aca="false">MIN(MAX(D34-G34-L34,0),MAX($B$15-$B$18-N34,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P34" s="12" t="n">
-        <f aca="false">N34+O34</f>
-        <v>12081</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <f aca="false">IF(H34&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <f aca="false">IF(M34&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <f aca="false">IF(AND(Q34=1,R34=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <f aca="false">IF(P34&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U34" s="5" t="n">
-        <f aca="false">IF(P34+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <f aca="false">MAX(D34-G34-L34,0)-O34</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="12" t="n">
-        <f aca="false">P34+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="30" t="n">
-        <v>46508</v>
-      </c>
-      <c r="B35" s="25" t="n">
-        <f aca="false">IF(A35&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A35&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="C35" s="12" t="n">
-        <f aca="false">IF(A35=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <f aca="false">B35+C35</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <f aca="false">H34</f>
-        <v>881.360351461602</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <f aca="false">E35*$B$6/12</f>
-        <v>21.8430473770567</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <f aca="false">MIN(E35+F35,MAX(D35-K35,0))</f>
-        <v>903.203398838658</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <f aca="false">E35+F35-G35</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <f aca="false">M34</f>
-        <v>5028.93504762843</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <f aca="false">I35*$B$8/12</f>
-        <v>73.2967283191844</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <f aca="false">MIN(I35+J35,J35+$B$9*I35)</f>
-        <v>123.586078795469</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <f aca="false">MIN(I35+J35,D35-G35)</f>
-        <v>1599.82326782801</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <f aca="false">I35+J35-L35</f>
-        <v>3502.40850811961</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <f aca="false">P34</f>
-        <v>12081</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <f aca="false">MIN(MAX(D35-G35-L35,0),MAX($B$15-$B$18-N35,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P35" s="12" t="n">
-        <f aca="false">N35+O35</f>
-        <v>12081</v>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <f aca="false">IF(H35&lt;=0.005,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="R35" s="5" t="n">
-        <f aca="false">IF(M35&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S35" s="5" t="n">
-        <f aca="false">IF(AND(Q35=1,R35=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T35" s="5" t="n">
-        <f aca="false">IF(P35&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U35" s="5" t="n">
-        <f aca="false">IF(P35+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V35" s="12" t="n">
-        <f aca="false">MAX(D35-G35-L35,0)-O35</f>
-        <v>0</v>
-      </c>
-      <c r="W35" s="12" t="n">
-        <f aca="false">P35+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="30" t="n">
-        <v>46539</v>
-      </c>
-      <c r="B36" s="25" t="n">
-        <f aca="false">IF(A36&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A36&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="C36" s="12" t="n">
-        <f aca="false">IF(A36=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <f aca="false">B36+C36</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <f aca="false">H35</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <f aca="false">E36*$B$6/12</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <f aca="false">MIN(E36+F36,MAX(D36-K36,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <f aca="false">E36+F36-G36</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <f aca="false">M35</f>
-        <v>3502.40850811961</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <f aca="false">I36*$B$8/12</f>
-        <v>51.0476040058433</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <f aca="false">MIN(I36+J36,J36+$B$9*I36)</f>
-        <v>86.0716890870394</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <f aca="false">MIN(I36+J36,D36-G36)</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <f aca="false">I36+J36-L36</f>
-        <v>1050.42944545878</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <f aca="false">P35</f>
-        <v>12081</v>
-      </c>
-      <c r="O36" s="12" t="n">
-        <f aca="false">MIN(MAX(D36-G36-L36,0),MAX($B$15-$B$18-N36,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P36" s="12" t="n">
-        <f aca="false">N36+O36</f>
-        <v>12081</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <f aca="false">IF(H36&lt;=0.005,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="R36" s="5" t="n">
-        <f aca="false">IF(M36&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S36" s="5" t="n">
-        <f aca="false">IF(AND(Q36=1,R36=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T36" s="5" t="n">
-        <f aca="false">IF(P36&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U36" s="5" t="n">
-        <f aca="false">IF(P36+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V36" s="12" t="n">
-        <f aca="false">MAX(D36-G36-L36,0)-O36</f>
-        <v>0</v>
-      </c>
-      <c r="W36" s="12" t="n">
-        <f aca="false">P36+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30" t="n">
-        <v>46569</v>
-      </c>
-      <c r="B37" s="25" t="n">
-        <f aca="false">IF(A37&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A37&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="C37" s="12" t="n">
-        <f aca="false">IF(A37=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <f aca="false">B37+C37</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <f aca="false">H36</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <f aca="false">E37*$B$6/12</f>
-        <v>0</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <f aca="false">MIN(E37+F37,MAX(D37-K37,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <f aca="false">E37+F37-G37</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <f aca="false">M36</f>
-        <v>1050.42944545878</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <f aca="false">I37*$B$8/12</f>
-        <v>15.3100091675618</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <f aca="false">MIN(I37+J37,J37+$B$9*I37)</f>
-        <v>25.8143036221496</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <f aca="false">MIN(I37+J37,D37-G37)</f>
-        <v>1065.73945462634</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <f aca="false">I37+J37-L37</f>
-        <v>0</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <f aca="false">P36</f>
-        <v>12081</v>
-      </c>
-      <c r="O37" s="12" t="n">
-        <f aca="false">MIN(MAX(D37-G37-L37,0),MAX($B$15-$B$18-N37,0))</f>
-        <v>1437.28721204032</v>
-      </c>
-      <c r="P37" s="12" t="n">
-        <f aca="false">N37+O37</f>
-        <v>13518.2872120403</v>
-      </c>
-      <c r="Q37" s="5" t="n">
-        <f aca="false">IF(H37&lt;=0.005,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="R37" s="5" t="n">
-        <f aca="false">IF(M37&lt;=0.005,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="S37" s="5" t="n">
-        <f aca="false">IF(AND(Q37=1,R37=1),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="T37" s="5" t="n">
-        <f aca="false">IF(P37&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U37" s="5" t="n">
-        <f aca="false">IF(P37+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="12" t="n">
-        <f aca="false">MAX(D37-G37-L37,0)-O37</f>
-        <v>0</v>
-      </c>
-      <c r="W37" s="12" t="n">
-        <f aca="false">P37+$B$18</f>
-        <v>29779.0372120403</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="30" t="n">
-        <v>46600</v>
-      </c>
-      <c r="B38" s="25" t="n">
-        <f aca="false">IF(A38&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A38&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="C38" s="12" t="n">
-        <f aca="false">IF(A38=$B$23,$B$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <f aca="false">B38+C38</f>
-        <v>2503.02666666667</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <f aca="false">H37</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <f aca="false">E38*$B$6/12</f>
-        <v>0</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <f aca="false">MIN(E38+F38,MAX(D38-K38,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <f aca="false">E38+F38-G38</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <f aca="false">M37</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <f aca="false">I38*$B$8/12</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <f aca="false">MIN(I38+J38,J38+$B$9*I38)</f>
-        <v>0</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <f aca="false">MIN(I38+J38,D38-G38)</f>
-        <v>0</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <f aca="false">I38+J38-L38</f>
-        <v>0</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <f aca="false">P37</f>
-        <v>13518.2872120403</v>
-      </c>
       <c r="O38" s="12" t="n">
         <f aca="false">MIN(MAX(D38-G38-L38,0),MAX($B$15-$B$18-N38,0))</f>
-        <v>2503.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P38" s="12" t="n">
         <f aca="false">N38+O38</f>
-        <v>16021.313878707</v>
+        <v>12081</v>
       </c>
       <c r="Q38" s="5" t="n">
         <f aca="false">IF(H38&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" s="5" t="n">
         <f aca="false">IF(M38&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="5" t="n">
         <f aca="false">IF(AND(Q38=1,R38=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" s="5" t="n">
         <f aca="false">IF(P38&gt;=$B$20,1,0)</f>
@@ -5522,84 +4850,84 @@
       </c>
       <c r="W38" s="12" t="n">
         <f aca="false">P38+$B$18</f>
-        <v>32282.063878707</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="30" t="n">
-        <v>46631</v>
+      <c r="A39" s="32" t="n">
+        <v>46357</v>
       </c>
       <c r="B39" s="25" t="n">
-        <f aca="false">IF(A39&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A39&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A39&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A39&gt;$B$33,$B$34,0)+IF(A39&gt;=$B$30,$B$31,0)</f>
+        <v>1426.77666666667</v>
       </c>
       <c r="C39" s="12" t="n">
-        <f aca="false">IF(A39=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A39=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D39" s="12" t="n">
         <f aca="false">B39+C39</f>
-        <v>2503.02666666667</v>
+        <v>1426.77666666667</v>
       </c>
       <c r="E39" s="12" t="n">
         <f aca="false">H38</f>
-        <v>0</v>
+        <v>8748.167185</v>
       </c>
       <c r="F39" s="12" t="n">
         <f aca="false">E39*$B$6/12</f>
-        <v>0</v>
+        <v>216.808743401583</v>
       </c>
       <c r="G39" s="12" t="n">
         <f aca="false">MIN(E39+F39,MAX(D39-K39,0))</f>
-        <v>0</v>
+        <v>1296.82149120667</v>
       </c>
       <c r="H39" s="12" t="n">
         <f aca="false">E39+F39-G39</f>
-        <v>0</v>
+        <v>7668.15443719491</v>
       </c>
       <c r="I39" s="12" t="n">
         <f aca="false">M38</f>
-        <v>0</v>
+        <v>5288.1048</v>
       </c>
       <c r="J39" s="12" t="n">
         <f aca="false">I39*$B$8/12</f>
-        <v>0</v>
+        <v>77.07412746</v>
       </c>
       <c r="K39" s="12" t="n">
         <f aca="false">MIN(I39+J39,J39+$B$9*I39)</f>
-        <v>0</v>
+        <v>129.95517546</v>
       </c>
       <c r="L39" s="12" t="n">
         <f aca="false">MIN(I39+J39,D39-G39)</f>
-        <v>0</v>
+        <v>129.95517546</v>
       </c>
       <c r="M39" s="12" t="n">
         <f aca="false">I39+J39-L39</f>
-        <v>0</v>
+        <v>5235.223752</v>
       </c>
       <c r="N39" s="12" t="n">
         <f aca="false">P38</f>
-        <v>16021.313878707</v>
+        <v>12081</v>
       </c>
       <c r="O39" s="12" t="n">
         <f aca="false">MIN(MAX(D39-G39-L39,0),MAX($B$15-$B$18-N39,0))</f>
-        <v>2503.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
         <f aca="false">N39+O39</f>
-        <v>18524.3405453737</v>
+        <v>12081</v>
       </c>
       <c r="Q39" s="5" t="n">
         <f aca="false">IF(H39&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" s="5" t="n">
         <f aca="false">IF(M39&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" s="5" t="n">
         <f aca="false">IF(AND(Q39=1,R39=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" s="5" t="n">
         <f aca="false">IF(P39&gt;=$B$20,1,0)</f>
@@ -5615,84 +4943,84 @@
       </c>
       <c r="W39" s="12" t="n">
         <f aca="false">P39+$B$18</f>
-        <v>34785.0905453737</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="30" t="n">
-        <v>46661</v>
+      <c r="A40" s="32" t="n">
+        <v>46388</v>
       </c>
       <c r="B40" s="25" t="n">
-        <f aca="false">IF(A40&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A40&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A40&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A40&gt;$B$33,$B$34,0)+IF(A40&gt;=$B$30,$B$31,0)</f>
+        <v>1918.32666666667</v>
       </c>
       <c r="C40" s="12" t="n">
-        <f aca="false">IF(A40=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A40=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="12" t="n">
         <f aca="false">B40+C40</f>
-        <v>2503.02666666667</v>
+        <v>1918.32666666667</v>
       </c>
       <c r="E40" s="12" t="n">
         <f aca="false">H39</f>
-        <v>0</v>
+        <v>7668.15443719491</v>
       </c>
       <c r="F40" s="12" t="n">
         <f aca="false">E40*$B$6/12</f>
-        <v>0</v>
+        <v>190.042427468481</v>
       </c>
       <c r="G40" s="12" t="n">
         <f aca="false">MIN(E40+F40,MAX(D40-K40,0))</f>
-        <v>0</v>
+        <v>1789.67104296127</v>
       </c>
       <c r="H40" s="12" t="n">
         <f aca="false">E40+F40-G40</f>
-        <v>0</v>
+        <v>6068.52582170213</v>
       </c>
       <c r="I40" s="12" t="n">
         <f aca="false">M39</f>
-        <v>0</v>
+        <v>5235.223752</v>
       </c>
       <c r="J40" s="12" t="n">
         <f aca="false">I40*$B$8/12</f>
-        <v>0</v>
+        <v>76.3033861854</v>
       </c>
       <c r="K40" s="12" t="n">
         <f aca="false">MIN(I40+J40,J40+$B$9*I40)</f>
-        <v>0</v>
+        <v>128.6556237054</v>
       </c>
       <c r="L40" s="12" t="n">
         <f aca="false">MIN(I40+J40,D40-G40)</f>
-        <v>0</v>
+        <v>128.6556237054</v>
       </c>
       <c r="M40" s="12" t="n">
         <f aca="false">I40+J40-L40</f>
-        <v>0</v>
+        <v>5182.87151448</v>
       </c>
       <c r="N40" s="12" t="n">
         <f aca="false">P39</f>
-        <v>18524.3405453737</v>
+        <v>12081</v>
       </c>
       <c r="O40" s="12" t="n">
         <f aca="false">MIN(MAX(D40-G40-L40,0),MAX($B$15-$B$18-N40,0))</f>
-        <v>2503.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P40" s="12" t="n">
         <f aca="false">N40+O40</f>
-        <v>21027.3672120403</v>
+        <v>12081</v>
       </c>
       <c r="Q40" s="5" t="n">
         <f aca="false">IF(H40&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" s="5" t="n">
         <f aca="false">IF(M40&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" s="5" t="n">
         <f aca="false">IF(AND(Q40=1,R40=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" s="5" t="n">
         <f aca="false">IF(P40&gt;=$B$20,1,0)</f>
@@ -5708,84 +5036,84 @@
       </c>
       <c r="W40" s="12" t="n">
         <f aca="false">P40+$B$18</f>
-        <v>37288.1172120403</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="30" t="n">
-        <v>46692</v>
+      <c r="A41" s="32" t="n">
+        <v>46419</v>
       </c>
       <c r="B41" s="25" t="n">
-        <f aca="false">IF(A41&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A41&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A41&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A41&gt;$B$33,$B$34,0)+IF(A41&gt;=$B$30,$B$31,0)</f>
+        <v>1918.32666666667</v>
       </c>
       <c r="C41" s="12" t="n">
-        <f aca="false">IF(A41=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A41=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D41" s="12" t="n">
         <f aca="false">B41+C41</f>
-        <v>2503.02666666667</v>
+        <v>1918.32666666667</v>
       </c>
       <c r="E41" s="12" t="n">
         <f aca="false">H40</f>
-        <v>0</v>
+        <v>6068.52582170213</v>
       </c>
       <c r="F41" s="12" t="n">
         <f aca="false">E41*$B$6/12</f>
-        <v>0</v>
+        <v>150.398298281184</v>
       </c>
       <c r="G41" s="12" t="n">
         <f aca="false">MIN(E41+F41,MAX(D41-K41,0))</f>
-        <v>0</v>
+        <v>1790.95759919832</v>
       </c>
       <c r="H41" s="12" t="n">
         <f aca="false">E41+F41-G41</f>
-        <v>0</v>
+        <v>4427.96652078499</v>
       </c>
       <c r="I41" s="12" t="n">
         <f aca="false">M40</f>
-        <v>0</v>
+        <v>5182.87151448</v>
       </c>
       <c r="J41" s="12" t="n">
         <f aca="false">I41*$B$8/12</f>
-        <v>0</v>
+        <v>75.540352323546</v>
       </c>
       <c r="K41" s="12" t="n">
         <f aca="false">MIN(I41+J41,J41+$B$9*I41)</f>
-        <v>0</v>
+        <v>127.369067468346</v>
       </c>
       <c r="L41" s="12" t="n">
         <f aca="false">MIN(I41+J41,D41-G41)</f>
-        <v>0</v>
+        <v>127.369067468346</v>
       </c>
       <c r="M41" s="12" t="n">
         <f aca="false">I41+J41-L41</f>
-        <v>0</v>
+        <v>5131.0427993352</v>
       </c>
       <c r="N41" s="12" t="n">
         <f aca="false">P40</f>
-        <v>21027.3672120403</v>
+        <v>12081</v>
       </c>
       <c r="O41" s="12" t="n">
         <f aca="false">MIN(MAX(D41-G41-L41,0),MAX($B$15-$B$18-N41,0))</f>
-        <v>2503.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
         <f aca="false">N41+O41</f>
-        <v>23530.393878707</v>
+        <v>12081</v>
       </c>
       <c r="Q41" s="5" t="n">
         <f aca="false">IF(H41&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" s="5" t="n">
         <f aca="false">IF(M41&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" s="5" t="n">
         <f aca="false">IF(AND(Q41=1,R41=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" s="5" t="n">
         <f aca="false">IF(P41&gt;=$B$20,1,0)</f>
@@ -5801,36 +5129,36 @@
       </c>
       <c r="W41" s="12" t="n">
         <f aca="false">P41+$B$18</f>
-        <v>39791.143878707</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="30" t="n">
-        <v>46722</v>
+      <c r="A42" s="32" t="n">
+        <v>46447</v>
       </c>
       <c r="B42" s="25" t="n">
-        <f aca="false">IF(A42&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A42&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A42&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A42&gt;$B$33,$B$34,0)+IF(A42&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C42" s="12" t="n">
-        <f aca="false">IF(A42=$B$23,$B$22,0)</f>
-        <v>0</v>
+        <f aca="false">IF(A42=$B$32,$B$25-$B$26,0)</f>
+        <v>40947.3684210526</v>
       </c>
       <c r="D42" s="12" t="n">
         <f aca="false">B42+C42</f>
-        <v>2503.02666666667</v>
+        <v>43941.9450877193</v>
       </c>
       <c r="E42" s="12" t="n">
         <f aca="false">H41</f>
-        <v>0</v>
+        <v>4427.96652078499</v>
       </c>
       <c r="F42" s="12" t="n">
         <f aca="false">E42*$B$6/12</f>
-        <v>0</v>
+        <v>109.739770273455</v>
       </c>
       <c r="G42" s="12" t="n">
         <f aca="false">MIN(E42+F42,MAX(D42-K42,0))</f>
-        <v>0</v>
+        <v>4537.70629105844</v>
       </c>
       <c r="H42" s="12" t="n">
         <f aca="false">E42+F42-G42</f>
@@ -5838,19 +5166,19 @@
       </c>
       <c r="I42" s="12" t="n">
         <f aca="false">M41</f>
-        <v>0</v>
+        <v>5131.0427993352</v>
       </c>
       <c r="J42" s="12" t="n">
         <f aca="false">I42*$B$8/12</f>
-        <v>0</v>
+        <v>74.7849488003106</v>
       </c>
       <c r="K42" s="12" t="n">
         <f aca="false">MIN(I42+J42,J42+$B$9*I42)</f>
-        <v>0</v>
+        <v>126.095376793663</v>
       </c>
       <c r="L42" s="12" t="n">
         <f aca="false">MIN(I42+J42,D42-G42)</f>
-        <v>0</v>
+        <v>5205.82774813551</v>
       </c>
       <c r="M42" s="12" t="n">
         <f aca="false">I42+J42-L42</f>
@@ -5858,15 +5186,15 @@
       </c>
       <c r="N42" s="12" t="n">
         <f aca="false">P41</f>
-        <v>23530.393878707</v>
+        <v>12081</v>
       </c>
       <c r="O42" s="12" t="n">
         <f aca="false">MIN(MAX(D42-G42-L42,0),MAX($B$15-$B$18-N42,0))</f>
-        <v>2503.02666666667</v>
+        <v>34198.4110485254</v>
       </c>
       <c r="P42" s="12" t="n">
         <f aca="false">N42+O42</f>
-        <v>26033.4205453737</v>
+        <v>46279.4110485254</v>
       </c>
       <c r="Q42" s="5" t="n">
         <f aca="false">IF(H42&lt;=0.005,1,0)</f>
@@ -5894,24 +5222,24 @@
       </c>
       <c r="W42" s="12" t="n">
         <f aca="false">P42+$B$18</f>
-        <v>42294.1705453737</v>
+        <v>62540.1610485254</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30" t="n">
-        <v>46753</v>
+      <c r="A43" s="32" t="n">
+        <v>46478</v>
       </c>
       <c r="B43" s="25" t="n">
-        <f aca="false">IF(A43&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A43&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A43&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A43&gt;$B$33,$B$34,0)+IF(A43&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C43" s="12" t="n">
-        <f aca="false">IF(A43=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A43=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D43" s="12" t="n">
         <f aca="false">B43+C43</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E43" s="12" t="n">
         <f aca="false">H42</f>
@@ -5951,15 +5279,15 @@
       </c>
       <c r="N43" s="12" t="n">
         <f aca="false">P42</f>
-        <v>26033.4205453737</v>
+        <v>46279.4110485254</v>
       </c>
       <c r="O43" s="12" t="n">
         <f aca="false">MIN(MAX(D43-G43-L43,0),MAX($B$15-$B$18-N43,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P43" s="12" t="n">
         <f aca="false">N43+O43</f>
-        <v>28536.4472120403</v>
+        <v>49273.987715192</v>
       </c>
       <c r="Q43" s="5" t="n">
         <f aca="false">IF(H43&lt;=0.005,1,0)</f>
@@ -5987,24 +5315,24 @@
       </c>
       <c r="W43" s="12" t="n">
         <f aca="false">P43+$B$18</f>
-        <v>44797.1972120403</v>
+        <v>65534.737715192</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30" t="n">
-        <v>46784</v>
+      <c r="A44" s="32" t="n">
+        <v>46508</v>
       </c>
       <c r="B44" s="25" t="n">
-        <f aca="false">IF(A44&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A44&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A44&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A44&gt;$B$33,$B$34,0)+IF(A44&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C44" s="12" t="n">
-        <f aca="false">IF(A44=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A44=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D44" s="12" t="n">
         <f aca="false">B44+C44</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E44" s="12" t="n">
         <f aca="false">H43</f>
@@ -6044,15 +5372,15 @@
       </c>
       <c r="N44" s="12" t="n">
         <f aca="false">P43</f>
-        <v>28536.4472120403</v>
+        <v>49273.987715192</v>
       </c>
       <c r="O44" s="12" t="n">
         <f aca="false">MIN(MAX(D44-G44-L44,0),MAX($B$15-$B$18-N44,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P44" s="12" t="n">
         <f aca="false">N44+O44</f>
-        <v>31039.473878707</v>
+        <v>52268.5643818587</v>
       </c>
       <c r="Q44" s="5" t="n">
         <f aca="false">IF(H44&lt;=0.005,1,0)</f>
@@ -6068,7 +5396,7 @@
       </c>
       <c r="T44" s="5" t="n">
         <f aca="false">IF(P44&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" s="5" t="n">
         <f aca="false">IF(P44+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6080,24 +5408,24 @@
       </c>
       <c r="W44" s="12" t="n">
         <f aca="false">P44+$B$18</f>
-        <v>47300.223878707</v>
+        <v>68529.3143818587</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="30" t="n">
-        <v>46813</v>
+      <c r="A45" s="32" t="n">
+        <v>46539</v>
       </c>
       <c r="B45" s="25" t="n">
-        <f aca="false">IF(A45&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A45&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A45&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A45&gt;$B$33,$B$34,0)+IF(A45&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C45" s="12" t="n">
-        <f aca="false">IF(A45=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A45=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D45" s="12" t="n">
         <f aca="false">B45+C45</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E45" s="12" t="n">
         <f aca="false">H44</f>
@@ -6137,15 +5465,15 @@
       </c>
       <c r="N45" s="12" t="n">
         <f aca="false">P44</f>
-        <v>31039.473878707</v>
+        <v>52268.5643818587</v>
       </c>
       <c r="O45" s="12" t="n">
         <f aca="false">MIN(MAX(D45-G45-L45,0),MAX($B$15-$B$18-N45,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P45" s="12" t="n">
         <f aca="false">N45+O45</f>
-        <v>33542.5005453737</v>
+        <v>55263.1410485254</v>
       </c>
       <c r="Q45" s="5" t="n">
         <f aca="false">IF(H45&lt;=0.005,1,0)</f>
@@ -6161,7 +5489,7 @@
       </c>
       <c r="T45" s="5" t="n">
         <f aca="false">IF(P45&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="5" t="n">
         <f aca="false">IF(P45+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6173,24 +5501,24 @@
       </c>
       <c r="W45" s="12" t="n">
         <f aca="false">P45+$B$18</f>
-        <v>49803.2505453737</v>
+        <v>71523.8910485253</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="30" t="n">
-        <v>46844</v>
+      <c r="A46" s="32" t="n">
+        <v>46569</v>
       </c>
       <c r="B46" s="25" t="n">
-        <f aca="false">IF(A46&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A46&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A46&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A46&gt;$B$33,$B$34,0)+IF(A46&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C46" s="12" t="n">
-        <f aca="false">IF(A46=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A46=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="12" t="n">
         <f aca="false">B46+C46</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E46" s="12" t="n">
         <f aca="false">H45</f>
@@ -6230,15 +5558,15 @@
       </c>
       <c r="N46" s="12" t="n">
         <f aca="false">P45</f>
-        <v>33542.5005453737</v>
+        <v>55263.1410485254</v>
       </c>
       <c r="O46" s="12" t="n">
         <f aca="false">MIN(MAX(D46-G46-L46,0),MAX($B$15-$B$18-N46,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P46" s="12" t="n">
         <f aca="false">N46+O46</f>
-        <v>36045.5272120403</v>
+        <v>58257.717715192</v>
       </c>
       <c r="Q46" s="5" t="n">
         <f aca="false">IF(H46&lt;=0.005,1,0)</f>
@@ -6254,7 +5582,7 @@
       </c>
       <c r="T46" s="5" t="n">
         <f aca="false">IF(P46&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" s="5" t="n">
         <f aca="false">IF(P46+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6266,24 +5594,24 @@
       </c>
       <c r="W46" s="12" t="n">
         <f aca="false">P46+$B$18</f>
-        <v>52306.2772120403</v>
+        <v>74518.467715192</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="30" t="n">
-        <v>46874</v>
+      <c r="A47" s="32" t="n">
+        <v>46600</v>
       </c>
       <c r="B47" s="25" t="n">
-        <f aca="false">IF(A47&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A47&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A47&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A47&gt;$B$33,$B$34,0)+IF(A47&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C47" s="12" t="n">
-        <f aca="false">IF(A47=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A47=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D47" s="12" t="n">
         <f aca="false">B47+C47</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E47" s="12" t="n">
         <f aca="false">H46</f>
@@ -6323,15 +5651,15 @@
       </c>
       <c r="N47" s="12" t="n">
         <f aca="false">P46</f>
-        <v>36045.5272120403</v>
+        <v>58257.717715192</v>
       </c>
       <c r="O47" s="12" t="n">
         <f aca="false">MIN(MAX(D47-G47-L47,0),MAX($B$15-$B$18-N47,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P47" s="12" t="n">
         <f aca="false">N47+O47</f>
-        <v>38548.553878707</v>
+        <v>61252.2943818587</v>
       </c>
       <c r="Q47" s="5" t="n">
         <f aca="false">IF(H47&lt;=0.005,1,0)</f>
@@ -6347,7 +5675,7 @@
       </c>
       <c r="T47" s="5" t="n">
         <f aca="false">IF(P47&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47" s="5" t="n">
         <f aca="false">IF(P47+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6359,24 +5687,24 @@
       </c>
       <c r="W47" s="12" t="n">
         <f aca="false">P47+$B$18</f>
-        <v>54809.303878707</v>
+        <v>77513.0443818587</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="30" t="n">
-        <v>46905</v>
+      <c r="A48" s="32" t="n">
+        <v>46631</v>
       </c>
       <c r="B48" s="25" t="n">
-        <f aca="false">IF(A48&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A48&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A48&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A48&gt;$B$33,$B$34,0)+IF(A48&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C48" s="12" t="n">
-        <f aca="false">IF(A48=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A48=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D48" s="12" t="n">
         <f aca="false">B48+C48</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E48" s="12" t="n">
         <f aca="false">H47</f>
@@ -6416,15 +5744,15 @@
       </c>
       <c r="N48" s="12" t="n">
         <f aca="false">P47</f>
-        <v>38548.553878707</v>
+        <v>61252.2943818587</v>
       </c>
       <c r="O48" s="12" t="n">
         <f aca="false">MIN(MAX(D48-G48-L48,0),MAX($B$15-$B$18-N48,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P48" s="12" t="n">
         <f aca="false">N48+O48</f>
-        <v>41051.5805453737</v>
+        <v>64246.8710485254</v>
       </c>
       <c r="Q48" s="5" t="n">
         <f aca="false">IF(H48&lt;=0.005,1,0)</f>
@@ -6440,7 +5768,7 @@
       </c>
       <c r="T48" s="5" t="n">
         <f aca="false">IF(P48&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <f aca="false">IF(P48+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6452,24 +5780,24 @@
       </c>
       <c r="W48" s="12" t="n">
         <f aca="false">P48+$B$18</f>
-        <v>57312.3305453737</v>
+        <v>80507.6210485254</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="30" t="n">
-        <v>46935</v>
+      <c r="A49" s="32" t="n">
+        <v>46661</v>
       </c>
       <c r="B49" s="25" t="n">
-        <f aca="false">IF(A49&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A49&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A49&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A49&gt;$B$33,$B$34,0)+IF(A49&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C49" s="12" t="n">
-        <f aca="false">IF(A49=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A49=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D49" s="12" t="n">
         <f aca="false">B49+C49</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E49" s="12" t="n">
         <f aca="false">H48</f>
@@ -6509,15 +5837,15 @@
       </c>
       <c r="N49" s="12" t="n">
         <f aca="false">P48</f>
-        <v>41051.5805453737</v>
+        <v>64246.8710485254</v>
       </c>
       <c r="O49" s="12" t="n">
         <f aca="false">MIN(MAX(D49-G49-L49,0),MAX($B$15-$B$18-N49,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P49" s="12" t="n">
         <f aca="false">N49+O49</f>
-        <v>43554.6072120404</v>
+        <v>67241.447715192</v>
       </c>
       <c r="Q49" s="5" t="n">
         <f aca="false">IF(H49&lt;=0.005,1,0)</f>
@@ -6533,7 +5861,7 @@
       </c>
       <c r="T49" s="5" t="n">
         <f aca="false">IF(P49&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" s="5" t="n">
         <f aca="false">IF(P49+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6545,24 +5873,24 @@
       </c>
       <c r="W49" s="12" t="n">
         <f aca="false">P49+$B$18</f>
-        <v>59815.3572120404</v>
+        <v>83502.197715192</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="30" t="n">
-        <v>46966</v>
+      <c r="A50" s="32" t="n">
+        <v>46692</v>
       </c>
       <c r="B50" s="25" t="n">
-        <f aca="false">IF(A50&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A50&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A50&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A50&gt;$B$33,$B$34,0)+IF(A50&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C50" s="12" t="n">
-        <f aca="false">IF(A50=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A50=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D50" s="12" t="n">
         <f aca="false">B50+C50</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E50" s="12" t="n">
         <f aca="false">H49</f>
@@ -6602,15 +5930,15 @@
       </c>
       <c r="N50" s="12" t="n">
         <f aca="false">P49</f>
-        <v>43554.6072120404</v>
+        <v>67241.447715192</v>
       </c>
       <c r="O50" s="12" t="n">
         <f aca="false">MIN(MAX(D50-G50-L50,0),MAX($B$15-$B$18-N50,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P50" s="12" t="n">
         <f aca="false">N50+O50</f>
-        <v>46057.633878707</v>
+        <v>70236.0243818587</v>
       </c>
       <c r="Q50" s="5" t="n">
         <f aca="false">IF(H50&lt;=0.005,1,0)</f>
@@ -6626,7 +5954,7 @@
       </c>
       <c r="T50" s="5" t="n">
         <f aca="false">IF(P50&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" s="5" t="n">
         <f aca="false">IF(P50+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6638,24 +5966,24 @@
       </c>
       <c r="W50" s="12" t="n">
         <f aca="false">P50+$B$18</f>
-        <v>62318.383878707</v>
+        <v>86496.7743818587</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="30" t="n">
-        <v>46997</v>
+      <c r="A51" s="32" t="n">
+        <v>46722</v>
       </c>
       <c r="B51" s="25" t="n">
-        <f aca="false">IF(A51&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A51&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A51&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A51&gt;$B$33,$B$34,0)+IF(A51&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C51" s="12" t="n">
-        <f aca="false">IF(A51=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A51=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D51" s="12" t="n">
         <f aca="false">B51+C51</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E51" s="12" t="n">
         <f aca="false">H50</f>
@@ -6695,15 +6023,15 @@
       </c>
       <c r="N51" s="12" t="n">
         <f aca="false">P50</f>
-        <v>46057.633878707</v>
+        <v>70236.0243818587</v>
       </c>
       <c r="O51" s="12" t="n">
         <f aca="false">MIN(MAX(D51-G51-L51,0),MAX($B$15-$B$18-N51,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P51" s="12" t="n">
         <f aca="false">N51+O51</f>
-        <v>48560.6605453737</v>
+        <v>73230.6010485254</v>
       </c>
       <c r="Q51" s="5" t="n">
         <f aca="false">IF(H51&lt;=0.005,1,0)</f>
@@ -6719,7 +6047,7 @@
       </c>
       <c r="T51" s="5" t="n">
         <f aca="false">IF(P51&gt;=$B$20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" s="5" t="n">
         <f aca="false">IF(P51+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -6731,24 +6059,24 @@
       </c>
       <c r="W51" s="12" t="n">
         <f aca="false">P51+$B$18</f>
-        <v>64821.4105453737</v>
+        <v>89491.3510485254</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="30" t="n">
-        <v>47027</v>
+      <c r="A52" s="32" t="n">
+        <v>46753</v>
       </c>
       <c r="B52" s="25" t="n">
-        <f aca="false">IF(A52&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A52&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A52&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A52&gt;$B$33,$B$34,0)+IF(A52&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C52" s="12" t="n">
-        <f aca="false">IF(A52=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A52=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D52" s="12" t="n">
         <f aca="false">B52+C52</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E52" s="12" t="n">
         <f aca="false">H51</f>
@@ -6788,15 +6116,15 @@
       </c>
       <c r="N52" s="12" t="n">
         <f aca="false">P51</f>
-        <v>48560.6605453737</v>
+        <v>73230.6010485254</v>
       </c>
       <c r="O52" s="12" t="n">
         <f aca="false">MIN(MAX(D52-G52-L52,0),MAX($B$15-$B$18-N52,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P52" s="12" t="n">
         <f aca="false">N52+O52</f>
-        <v>51063.6872120404</v>
+        <v>76225.1777151921</v>
       </c>
       <c r="Q52" s="5" t="n">
         <f aca="false">IF(H52&lt;=0.005,1,0)</f>
@@ -6824,24 +6152,24 @@
       </c>
       <c r="W52" s="12" t="n">
         <f aca="false">P52+$B$18</f>
-        <v>67324.4372120404</v>
+        <v>92485.9277151921</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="30" t="n">
-        <v>47058</v>
+      <c r="A53" s="32" t="n">
+        <v>46784</v>
       </c>
       <c r="B53" s="25" t="n">
-        <f aca="false">IF(A53&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A53&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A53&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A53&gt;$B$33,$B$34,0)+IF(A53&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C53" s="12" t="n">
-        <f aca="false">IF(A53=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A53=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D53" s="12" t="n">
         <f aca="false">B53+C53</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E53" s="12" t="n">
         <f aca="false">H52</f>
@@ -6881,15 +6209,15 @@
       </c>
       <c r="N53" s="12" t="n">
         <f aca="false">P52</f>
-        <v>51063.6872120404</v>
+        <v>76225.1777151921</v>
       </c>
       <c r="O53" s="12" t="n">
         <f aca="false">MIN(MAX(D53-G53-L53,0),MAX($B$15-$B$18-N53,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P53" s="12" t="n">
         <f aca="false">N53+O53</f>
-        <v>53566.713878707</v>
+        <v>79219.7543818587</v>
       </c>
       <c r="Q53" s="5" t="n">
         <f aca="false">IF(H53&lt;=0.005,1,0)</f>
@@ -6917,24 +6245,24 @@
       </c>
       <c r="W53" s="12" t="n">
         <f aca="false">P53+$B$18</f>
-        <v>69827.463878707</v>
+        <v>95480.5043818587</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="30" t="n">
-        <v>47088</v>
+      <c r="A54" s="32" t="n">
+        <v>46813</v>
       </c>
       <c r="B54" s="25" t="n">
-        <f aca="false">IF(A54&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A54&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A54&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A54&gt;$B$33,$B$34,0)+IF(A54&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C54" s="12" t="n">
-        <f aca="false">IF(A54=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A54=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D54" s="12" t="n">
         <f aca="false">B54+C54</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E54" s="12" t="n">
         <f aca="false">H53</f>
@@ -6974,15 +6302,15 @@
       </c>
       <c r="N54" s="12" t="n">
         <f aca="false">P53</f>
-        <v>53566.713878707</v>
+        <v>79219.7543818587</v>
       </c>
       <c r="O54" s="12" t="n">
         <f aca="false">MIN(MAX(D54-G54-L54,0),MAX($B$15-$B$18-N54,0))</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="P54" s="12" t="n">
         <f aca="false">N54+O54</f>
-        <v>56069.7405453737</v>
+        <v>82214.3310485254</v>
       </c>
       <c r="Q54" s="5" t="n">
         <f aca="false">IF(H54&lt;=0.005,1,0)</f>
@@ -7010,24 +6338,24 @@
       </c>
       <c r="W54" s="12" t="n">
         <f aca="false">P54+$B$18</f>
-        <v>72330.4905453737</v>
+        <v>98475.0810485254</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="30" t="n">
-        <v>47119</v>
+      <c r="A55" s="32" t="n">
+        <v>46844</v>
       </c>
       <c r="B55" s="25" t="n">
-        <f aca="false">IF(A55&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A55&gt;$B$24,$B$25,0)</f>
-        <v>2503.02666666667</v>
+        <f aca="false">IF(A55&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A55&gt;$B$33,$B$34,0)+IF(A55&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C55" s="12" t="n">
-        <f aca="false">IF(A55=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A55=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="12" t="n">
         <f aca="false">B55+C55</f>
-        <v>2503.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E55" s="12" t="n">
         <f aca="false">H54</f>
@@ -7067,15 +6395,15 @@
       </c>
       <c r="N55" s="12" t="n">
         <f aca="false">P54</f>
-        <v>56069.7405453737</v>
+        <v>82214.3310485254</v>
       </c>
       <c r="O55" s="12" t="n">
         <f aca="false">MIN(MAX(D55-G55-L55,0),MAX($B$15-$B$18-N55,0))</f>
-        <v>2503.02666666667</v>
+        <v>2366.9189514746</v>
       </c>
       <c r="P55" s="12" t="n">
         <f aca="false">N55+O55</f>
-        <v>58572.7672120404</v>
+        <v>84581.25</v>
       </c>
       <c r="Q55" s="5" t="n">
         <f aca="false">IF(H55&lt;=0.005,1,0)</f>
@@ -7095,32 +6423,32 @@
       </c>
       <c r="U55" s="5" t="n">
         <f aca="false">IF(P55+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="12" t="n">
         <f aca="false">MAX(D55-G55-L55,0)-O55</f>
-        <v>0</v>
+        <v>627.657715192073</v>
       </c>
       <c r="W55" s="12" t="n">
         <f aca="false">P55+$B$18</f>
-        <v>74833.5172120404</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="30" t="n">
-        <v>47150</v>
+      <c r="A56" s="32" t="n">
+        <v>46874</v>
       </c>
       <c r="B56" s="25" t="n">
-        <f aca="false">IF(A56&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A56&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A56&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A56&gt;$B$33,$B$34,0)+IF(A56&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C56" s="12" t="n">
-        <f aca="false">IF(A56=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A56=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D56" s="12" t="n">
         <f aca="false">B56+C56</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E56" s="12" t="n">
         <f aca="false">H55</f>
@@ -7160,15 +6488,15 @@
       </c>
       <c r="N56" s="12" t="n">
         <f aca="false">P55</f>
-        <v>58572.7672120404</v>
+        <v>84581.25</v>
       </c>
       <c r="O56" s="12" t="n">
         <f aca="false">MIN(MAX(D56-G56-L56,0),MAX($B$15-$B$18-N56,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P56" s="12" t="n">
         <f aca="false">N56+O56</f>
-        <v>61417.7938787071</v>
+        <v>84581.25</v>
       </c>
       <c r="Q56" s="5" t="n">
         <f aca="false">IF(H56&lt;=0.005,1,0)</f>
@@ -7188,32 +6516,32 @@
       </c>
       <c r="U56" s="5" t="n">
         <f aca="false">IF(P56+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="12" t="n">
         <f aca="false">MAX(D56-G56-L56,0)-O56</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W56" s="12" t="n">
         <f aca="false">P56+$B$18</f>
-        <v>77678.5438787071</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="30" t="n">
-        <v>47178</v>
+      <c r="A57" s="32" t="n">
+        <v>46905</v>
       </c>
       <c r="B57" s="25" t="n">
-        <f aca="false">IF(A57&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A57&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A57&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A57&gt;$B$33,$B$34,0)+IF(A57&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C57" s="12" t="n">
-        <f aca="false">IF(A57=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A57=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D57" s="12" t="n">
         <f aca="false">B57+C57</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E57" s="12" t="n">
         <f aca="false">H56</f>
@@ -7253,15 +6581,15 @@
       </c>
       <c r="N57" s="12" t="n">
         <f aca="false">P56</f>
-        <v>61417.7938787071</v>
+        <v>84581.25</v>
       </c>
       <c r="O57" s="12" t="n">
         <f aca="false">MIN(MAX(D57-G57-L57,0),MAX($B$15-$B$18-N57,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
         <f aca="false">N57+O57</f>
-        <v>64262.8205453737</v>
+        <v>84581.25</v>
       </c>
       <c r="Q57" s="5" t="n">
         <f aca="false">IF(H57&lt;=0.005,1,0)</f>
@@ -7281,32 +6609,32 @@
       </c>
       <c r="U57" s="5" t="n">
         <f aca="false">IF(P57+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="12" t="n">
         <f aca="false">MAX(D57-G57-L57,0)-O57</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W57" s="12" t="n">
         <f aca="false">P57+$B$18</f>
-        <v>80523.5705453737</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="30" t="n">
-        <v>47209</v>
+      <c r="A58" s="32" t="n">
+        <v>46935</v>
       </c>
       <c r="B58" s="25" t="n">
-        <f aca="false">IF(A58&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A58&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A58&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A58&gt;$B$33,$B$34,0)+IF(A58&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C58" s="12" t="n">
-        <f aca="false">IF(A58=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A58=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D58" s="12" t="n">
         <f aca="false">B58+C58</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E58" s="12" t="n">
         <f aca="false">H57</f>
@@ -7346,15 +6674,15 @@
       </c>
       <c r="N58" s="12" t="n">
         <f aca="false">P57</f>
-        <v>64262.8205453737</v>
+        <v>84581.25</v>
       </c>
       <c r="O58" s="12" t="n">
         <f aca="false">MIN(MAX(D58-G58-L58,0),MAX($B$15-$B$18-N58,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P58" s="12" t="n">
         <f aca="false">N58+O58</f>
-        <v>67107.8472120404</v>
+        <v>84581.25</v>
       </c>
       <c r="Q58" s="5" t="n">
         <f aca="false">IF(H58&lt;=0.005,1,0)</f>
@@ -7374,32 +6702,32 @@
       </c>
       <c r="U58" s="5" t="n">
         <f aca="false">IF(P58+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="12" t="n">
         <f aca="false">MAX(D58-G58-L58,0)-O58</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W58" s="12" t="n">
         <f aca="false">P58+$B$18</f>
-        <v>83368.5972120404</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="30" t="n">
-        <v>47239</v>
+      <c r="A59" s="32" t="n">
+        <v>46966</v>
       </c>
       <c r="B59" s="25" t="n">
-        <f aca="false">IF(A59&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A59&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A59&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A59&gt;$B$33,$B$34,0)+IF(A59&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C59" s="12" t="n">
-        <f aca="false">IF(A59=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A59=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D59" s="12" t="n">
         <f aca="false">B59+C59</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E59" s="12" t="n">
         <f aca="false">H58</f>
@@ -7439,15 +6767,15 @@
       </c>
       <c r="N59" s="12" t="n">
         <f aca="false">P58</f>
-        <v>67107.8472120404</v>
+        <v>84581.25</v>
       </c>
       <c r="O59" s="12" t="n">
         <f aca="false">MIN(MAX(D59-G59-L59,0),MAX($B$15-$B$18-N59,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
         <f aca="false">N59+O59</f>
-        <v>69952.8738787071</v>
+        <v>84581.25</v>
       </c>
       <c r="Q59" s="5" t="n">
         <f aca="false">IF(H59&lt;=0.005,1,0)</f>
@@ -7467,32 +6795,32 @@
       </c>
       <c r="U59" s="5" t="n">
         <f aca="false">IF(P59+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="12" t="n">
         <f aca="false">MAX(D59-G59-L59,0)-O59</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W59" s="12" t="n">
         <f aca="false">P59+$B$18</f>
-        <v>86213.6238787071</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="30" t="n">
-        <v>47270</v>
+      <c r="A60" s="32" t="n">
+        <v>46997</v>
       </c>
       <c r="B60" s="25" t="n">
-        <f aca="false">IF(A60&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A60&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A60&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A60&gt;$B$33,$B$34,0)+IF(A60&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C60" s="12" t="n">
-        <f aca="false">IF(A60=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A60=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D60" s="12" t="n">
         <f aca="false">B60+C60</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E60" s="12" t="n">
         <f aca="false">H59</f>
@@ -7532,15 +6860,15 @@
       </c>
       <c r="N60" s="12" t="n">
         <f aca="false">P59</f>
-        <v>69952.8738787071</v>
+        <v>84581.25</v>
       </c>
       <c r="O60" s="12" t="n">
         <f aca="false">MIN(MAX(D60-G60-L60,0),MAX($B$15-$B$18-N60,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P60" s="12" t="n">
         <f aca="false">N60+O60</f>
-        <v>72797.9005453738</v>
+        <v>84581.25</v>
       </c>
       <c r="Q60" s="5" t="n">
         <f aca="false">IF(H60&lt;=0.005,1,0)</f>
@@ -7560,32 +6888,32 @@
       </c>
       <c r="U60" s="5" t="n">
         <f aca="false">IF(P60+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="12" t="n">
         <f aca="false">MAX(D60-G60-L60,0)-O60</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W60" s="12" t="n">
         <f aca="false">P60+$B$18</f>
-        <v>89058.6505453738</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="30" t="n">
-        <v>47300</v>
+      <c r="A61" s="32" t="n">
+        <v>47027</v>
       </c>
       <c r="B61" s="25" t="n">
-        <f aca="false">IF(A61&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A61&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A61&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A61&gt;$B$33,$B$34,0)+IF(A61&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C61" s="12" t="n">
-        <f aca="false">IF(A61=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A61=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D61" s="12" t="n">
         <f aca="false">B61+C61</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E61" s="12" t="n">
         <f aca="false">H60</f>
@@ -7625,15 +6953,15 @@
       </c>
       <c r="N61" s="12" t="n">
         <f aca="false">P60</f>
-        <v>72797.9005453738</v>
+        <v>84581.25</v>
       </c>
       <c r="O61" s="12" t="n">
         <f aca="false">MIN(MAX(D61-G61-L61,0),MAX($B$15-$B$18-N61,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
         <f aca="false">N61+O61</f>
-        <v>75642.9272120404</v>
+        <v>84581.25</v>
       </c>
       <c r="Q61" s="5" t="n">
         <f aca="false">IF(H61&lt;=0.005,1,0)</f>
@@ -7653,32 +6981,32 @@
       </c>
       <c r="U61" s="5" t="n">
         <f aca="false">IF(P61+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" s="12" t="n">
         <f aca="false">MAX(D61-G61-L61,0)-O61</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W61" s="12" t="n">
         <f aca="false">P61+$B$18</f>
-        <v>91903.6772120404</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="30" t="n">
-        <v>47331</v>
+      <c r="A62" s="32" t="n">
+        <v>47058</v>
       </c>
       <c r="B62" s="25" t="n">
-        <f aca="false">IF(A62&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A62&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A62&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A62&gt;$B$33,$B$34,0)+IF(A62&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C62" s="12" t="n">
-        <f aca="false">IF(A62=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A62=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D62" s="12" t="n">
         <f aca="false">B62+C62</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E62" s="12" t="n">
         <f aca="false">H61</f>
@@ -7718,15 +7046,15 @@
       </c>
       <c r="N62" s="12" t="n">
         <f aca="false">P61</f>
-        <v>75642.9272120404</v>
+        <v>84581.25</v>
       </c>
       <c r="O62" s="12" t="n">
         <f aca="false">MIN(MAX(D62-G62-L62,0),MAX($B$15-$B$18-N62,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P62" s="12" t="n">
         <f aca="false">N62+O62</f>
-        <v>78487.9538787071</v>
+        <v>84581.25</v>
       </c>
       <c r="Q62" s="5" t="n">
         <f aca="false">IF(H62&lt;=0.005,1,0)</f>
@@ -7746,32 +7074,32 @@
       </c>
       <c r="U62" s="5" t="n">
         <f aca="false">IF(P62+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V62" s="12" t="n">
         <f aca="false">MAX(D62-G62-L62,0)-O62</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W62" s="12" t="n">
         <f aca="false">P62+$B$18</f>
-        <v>94748.7038787071</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="30" t="n">
-        <v>47362</v>
+      <c r="A63" s="32" t="n">
+        <v>47088</v>
       </c>
       <c r="B63" s="25" t="n">
-        <f aca="false">IF(A63&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A63&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A63&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A63&gt;$B$33,$B$34,0)+IF(A63&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C63" s="12" t="n">
-        <f aca="false">IF(A63=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A63=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D63" s="12" t="n">
         <f aca="false">B63+C63</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E63" s="12" t="n">
         <f aca="false">H62</f>
@@ -7811,15 +7139,15 @@
       </c>
       <c r="N63" s="12" t="n">
         <f aca="false">P62</f>
-        <v>78487.9538787071</v>
+        <v>84581.25</v>
       </c>
       <c r="O63" s="12" t="n">
         <f aca="false">MIN(MAX(D63-G63-L63,0),MAX($B$15-$B$18-N63,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
         <f aca="false">N63+O63</f>
-        <v>81332.9805453738</v>
+        <v>84581.25</v>
       </c>
       <c r="Q63" s="5" t="n">
         <f aca="false">IF(H63&lt;=0.005,1,0)</f>
@@ -7839,32 +7167,32 @@
       </c>
       <c r="U63" s="5" t="n">
         <f aca="false">IF(P63+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" s="12" t="n">
         <f aca="false">MAX(D63-G63-L63,0)-O63</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W63" s="12" t="n">
         <f aca="false">P63+$B$18</f>
-        <v>97593.7305453738</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="30" t="n">
-        <v>47392</v>
+      <c r="A64" s="32" t="n">
+        <v>47119</v>
       </c>
       <c r="B64" s="25" t="n">
-        <f aca="false">IF(A64&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A64&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A64&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A64&gt;$B$33,$B$34,0)+IF(A64&gt;=$B$30,$B$31,0)</f>
+        <v>2994.57666666667</v>
       </c>
       <c r="C64" s="12" t="n">
-        <f aca="false">IF(A64=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A64=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D64" s="12" t="n">
         <f aca="false">B64+C64</f>
-        <v>2845.02666666667</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="E64" s="12" t="n">
         <f aca="false">H63</f>
@@ -7904,15 +7232,15 @@
       </c>
       <c r="N64" s="12" t="n">
         <f aca="false">P63</f>
-        <v>81332.9805453738</v>
+        <v>84581.25</v>
       </c>
       <c r="O64" s="12" t="n">
         <f aca="false">MIN(MAX(D64-G64-L64,0),MAX($B$15-$B$18-N64,0))</f>
-        <v>2845.02666666667</v>
+        <v>0</v>
       </c>
       <c r="P64" s="12" t="n">
         <f aca="false">N64+O64</f>
-        <v>84178.0072120404</v>
+        <v>84581.25</v>
       </c>
       <c r="Q64" s="5" t="n">
         <f aca="false">IF(H64&lt;=0.005,1,0)</f>
@@ -7932,32 +7260,32 @@
       </c>
       <c r="U64" s="5" t="n">
         <f aca="false">IF(P64+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V64" s="12" t="n">
         <f aca="false">MAX(D64-G64-L64,0)-O64</f>
-        <v>0</v>
+        <v>2994.57666666667</v>
       </c>
       <c r="W64" s="12" t="n">
         <f aca="false">P64+$B$18</f>
-        <v>100438.75721204</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="30" t="n">
-        <v>47423</v>
+      <c r="A65" s="32" t="n">
+        <v>47150</v>
       </c>
       <c r="B65" s="25" t="n">
-        <f aca="false">IF(A65&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A65&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A65&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A65&gt;$B$33,$B$34,0)+IF(A65&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C65" s="12" t="n">
-        <f aca="false">IF(A65=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A65=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D65" s="12" t="n">
         <f aca="false">B65+C65</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E65" s="12" t="n">
         <f aca="false">H64</f>
@@ -7997,11 +7325,11 @@
       </c>
       <c r="N65" s="12" t="n">
         <f aca="false">P64</f>
-        <v>84178.0072120404</v>
+        <v>84581.25</v>
       </c>
       <c r="O65" s="12" t="n">
         <f aca="false">MIN(MAX(D65-G65-L65,0),MAX($B$15-$B$18-N65,0))</f>
-        <v>403.242787959563</v>
+        <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
         <f aca="false">N65+O65</f>
@@ -8029,7 +7357,7 @@
       </c>
       <c r="V65" s="12" t="n">
         <f aca="false">MAX(D65-G65-L65,0)-O65</f>
-        <v>2441.78387870711</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W65" s="12" t="n">
         <f aca="false">P65+$B$18</f>
@@ -8037,20 +7365,20 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="30" t="n">
-        <v>47453</v>
+      <c r="A66" s="32" t="n">
+        <v>47178</v>
       </c>
       <c r="B66" s="25" t="n">
-        <f aca="false">IF(A66&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A66&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A66&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A66&gt;$B$33,$B$34,0)+IF(A66&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C66" s="12" t="n">
-        <f aca="false">IF(A66=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A66=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D66" s="12" t="n">
         <f aca="false">B66+C66</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E66" s="12" t="n">
         <f aca="false">H65</f>
@@ -8122,7 +7450,7 @@
       </c>
       <c r="V66" s="12" t="n">
         <f aca="false">MAX(D66-G66-L66,0)-O66</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W66" s="12" t="n">
         <f aca="false">P66+$B$18</f>
@@ -8130,20 +7458,20 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="30" t="n">
-        <v>47484</v>
+      <c r="A67" s="32" t="n">
+        <v>47209</v>
       </c>
       <c r="B67" s="25" t="n">
-        <f aca="false">IF(A67&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A67&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A67&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A67&gt;$B$33,$B$34,0)+IF(A67&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C67" s="12" t="n">
-        <f aca="false">IF(A67=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A67=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D67" s="12" t="n">
         <f aca="false">B67+C67</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E67" s="12" t="n">
         <f aca="false">H66</f>
@@ -8215,7 +7543,7 @@
       </c>
       <c r="V67" s="12" t="n">
         <f aca="false">MAX(D67-G67-L67,0)-O67</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W67" s="12" t="n">
         <f aca="false">P67+$B$18</f>
@@ -8223,20 +7551,20 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="30" t="n">
-        <v>47515</v>
+      <c r="A68" s="32" t="n">
+        <v>47239</v>
       </c>
       <c r="B68" s="25" t="n">
-        <f aca="false">IF(A68&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A68&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A68&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A68&gt;$B$33,$B$34,0)+IF(A68&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C68" s="12" t="n">
-        <f aca="false">IF(A68=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A68=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="12" t="n">
         <f aca="false">B68+C68</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E68" s="12" t="n">
         <f aca="false">H67</f>
@@ -8308,7 +7636,7 @@
       </c>
       <c r="V68" s="12" t="n">
         <f aca="false">MAX(D68-G68-L68,0)-O68</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W68" s="12" t="n">
         <f aca="false">P68+$B$18</f>
@@ -8316,20 +7644,20 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="30" t="n">
-        <v>47543</v>
+      <c r="A69" s="32" t="n">
+        <v>47270</v>
       </c>
       <c r="B69" s="25" t="n">
-        <f aca="false">IF(A69&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A69&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A69&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A69&gt;$B$33,$B$34,0)+IF(A69&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C69" s="12" t="n">
-        <f aca="false">IF(A69=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A69=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="12" t="n">
         <f aca="false">B69+C69</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E69" s="12" t="n">
         <f aca="false">H68</f>
@@ -8401,7 +7729,7 @@
       </c>
       <c r="V69" s="12" t="n">
         <f aca="false">MAX(D69-G69-L69,0)-O69</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W69" s="12" t="n">
         <f aca="false">P69+$B$18</f>
@@ -8409,20 +7737,20 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="30" t="n">
-        <v>47574</v>
+      <c r="A70" s="32" t="n">
+        <v>47300</v>
       </c>
       <c r="B70" s="25" t="n">
-        <f aca="false">IF(A70&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A70&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A70&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A70&gt;$B$33,$B$34,0)+IF(A70&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C70" s="12" t="n">
-        <f aca="false">IF(A70=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A70=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D70" s="12" t="n">
         <f aca="false">B70+C70</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E70" s="12" t="n">
         <f aca="false">H69</f>
@@ -8494,7 +7822,7 @@
       </c>
       <c r="V70" s="12" t="n">
         <f aca="false">MAX(D70-G70-L70,0)-O70</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W70" s="12" t="n">
         <f aca="false">P70+$B$18</f>
@@ -8502,20 +7830,20 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="30" t="n">
-        <v>47604</v>
+      <c r="A71" s="32" t="n">
+        <v>47331</v>
       </c>
       <c r="B71" s="25" t="n">
-        <f aca="false">IF(A71&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A71&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A71&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A71&gt;$B$33,$B$34,0)+IF(A71&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C71" s="12" t="n">
-        <f aca="false">IF(A71=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A71=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D71" s="12" t="n">
         <f aca="false">B71+C71</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E71" s="12" t="n">
         <f aca="false">H70</f>
@@ -8587,7 +7915,7 @@
       </c>
       <c r="V71" s="12" t="n">
         <f aca="false">MAX(D71-G71-L71,0)-O71</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W71" s="12" t="n">
         <f aca="false">P71+$B$18</f>
@@ -8595,20 +7923,20 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="30" t="n">
-        <v>47635</v>
+      <c r="A72" s="32" t="n">
+        <v>47362</v>
       </c>
       <c r="B72" s="25" t="n">
-        <f aca="false">IF(A72&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A72&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A72&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A72&gt;$B$33,$B$34,0)+IF(A72&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C72" s="12" t="n">
-        <f aca="false">IF(A72=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A72=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D72" s="12" t="n">
         <f aca="false">B72+C72</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E72" s="12" t="n">
         <f aca="false">H71</f>
@@ -8680,7 +8008,7 @@
       </c>
       <c r="V72" s="12" t="n">
         <f aca="false">MAX(D72-G72-L72,0)-O72</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W72" s="12" t="n">
         <f aca="false">P72+$B$18</f>
@@ -8688,20 +8016,20 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="30" t="n">
-        <v>47665</v>
+      <c r="A73" s="32" t="n">
+        <v>47392</v>
       </c>
       <c r="B73" s="25" t="n">
-        <f aca="false">IF(A73&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A73&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A73&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A73&gt;$B$33,$B$34,0)+IF(A73&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C73" s="12" t="n">
-        <f aca="false">IF(A73=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A73=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D73" s="12" t="n">
         <f aca="false">B73+C73</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E73" s="12" t="n">
         <f aca="false">H72</f>
@@ -8773,7 +8101,7 @@
       </c>
       <c r="V73" s="12" t="n">
         <f aca="false">MAX(D73-G73-L73,0)-O73</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W73" s="12" t="n">
         <f aca="false">P73+$B$18</f>
@@ -8781,20 +8109,20 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="30" t="n">
-        <v>47696</v>
+      <c r="A74" s="32" t="n">
+        <v>47423</v>
       </c>
       <c r="B74" s="25" t="n">
-        <f aca="false">IF(A74&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A74&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A74&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A74&gt;$B$33,$B$34,0)+IF(A74&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C74" s="12" t="n">
-        <f aca="false">IF(A74=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A74=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D74" s="12" t="n">
         <f aca="false">B74+C74</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E74" s="12" t="n">
         <f aca="false">H73</f>
@@ -8866,7 +8194,7 @@
       </c>
       <c r="V74" s="12" t="n">
         <f aca="false">MAX(D74-G74-L74,0)-O74</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W74" s="12" t="n">
         <f aca="false">P74+$B$18</f>
@@ -8874,20 +8202,20 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="30" t="n">
-        <v>47727</v>
+      <c r="A75" s="32" t="n">
+        <v>47453</v>
       </c>
       <c r="B75" s="25" t="n">
-        <f aca="false">IF(A75&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A75&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A75&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A75&gt;$B$33,$B$34,0)+IF(A75&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C75" s="12" t="n">
-        <f aca="false">IF(A75=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A75=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D75" s="12" t="n">
         <f aca="false">B75+C75</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E75" s="12" t="n">
         <f aca="false">H74</f>
@@ -8959,7 +8287,7 @@
       </c>
       <c r="V75" s="12" t="n">
         <f aca="false">MAX(D75-G75-L75,0)-O75</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W75" s="12" t="n">
         <f aca="false">P75+$B$18</f>
@@ -8967,20 +8295,20 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="30" t="n">
-        <v>47757</v>
+      <c r="A76" s="32" t="n">
+        <v>47484</v>
       </c>
       <c r="B76" s="25" t="n">
-        <f aca="false">IF(A76&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A76&gt;$B$24,$B$25,0)</f>
-        <v>2845.02666666667</v>
+        <f aca="false">IF(A76&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A76&gt;$B$33,$B$34,0)+IF(A76&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
       </c>
       <c r="C76" s="12" t="n">
-        <f aca="false">IF(A76=$B$23,$B$22,0)</f>
+        <f aca="false">IF(A76=$B$32,$B$25-$B$26,0)</f>
         <v>0</v>
       </c>
       <c r="D76" s="12" t="n">
         <f aca="false">B76+C76</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="E76" s="12" t="n">
         <f aca="false">H75</f>
@@ -9052,10 +8380,847 @@
       </c>
       <c r="V76" s="12" t="n">
         <f aca="false">MAX(D76-G76-L76,0)-O76</f>
-        <v>2845.02666666667</v>
+        <v>3336.57666666667</v>
       </c>
       <c r="W76" s="12" t="n">
         <f aca="false">P76+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="32" t="n">
+        <v>47515</v>
+      </c>
+      <c r="B77" s="25" t="n">
+        <f aca="false">IF(A77&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A77&gt;$B$33,$B$34,0)+IF(A77&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C77" s="12" t="n">
+        <f aca="false">IF(A77=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D77" s="12" t="n">
+        <f aca="false">B77+C77</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E77" s="12" t="n">
+        <f aca="false">H76</f>
+        <v>0</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <f aca="false">E77*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <f aca="false">MIN(E77+F77,MAX(D77-K77,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <f aca="false">E77+F77-G77</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <f aca="false">M76</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <f aca="false">I77*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K77" s="12" t="n">
+        <f aca="false">MIN(I77+J77,J77+$B$9*I77)</f>
+        <v>0</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <f aca="false">MIN(I77+J77,D77-G77)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="12" t="n">
+        <f aca="false">I77+J77-L77</f>
+        <v>0</v>
+      </c>
+      <c r="N77" s="12" t="n">
+        <f aca="false">P76</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <f aca="false">MIN(MAX(D77-G77-L77,0),MAX($B$15-$B$18-N77,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P77" s="12" t="n">
+        <f aca="false">N77+O77</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q77" s="5" t="n">
+        <f aca="false">IF(H77&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R77" s="5" t="n">
+        <f aca="false">IF(M77&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S77" s="5" t="n">
+        <f aca="false">IF(AND(Q77=1,R77=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T77" s="5" t="n">
+        <f aca="false">IF(P77&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U77" s="5" t="n">
+        <f aca="false">IF(P77+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V77" s="12" t="n">
+        <f aca="false">MAX(D77-G77-L77,0)-O77</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W77" s="12" t="n">
+        <f aca="false">P77+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="32" t="n">
+        <v>47543</v>
+      </c>
+      <c r="B78" s="25" t="n">
+        <f aca="false">IF(A78&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A78&gt;$B$33,$B$34,0)+IF(A78&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C78" s="12" t="n">
+        <f aca="false">IF(A78=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D78" s="12" t="n">
+        <f aca="false">B78+C78</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E78" s="12" t="n">
+        <f aca="false">H77</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <f aca="false">E78*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <f aca="false">MIN(E78+F78,MAX(D78-K78,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <f aca="false">E78+F78-G78</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <f aca="false">M77</f>
+        <v>0</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <f aca="false">I78*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K78" s="12" t="n">
+        <f aca="false">MIN(I78+J78,J78+$B$9*I78)</f>
+        <v>0</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <f aca="false">MIN(I78+J78,D78-G78)</f>
+        <v>0</v>
+      </c>
+      <c r="M78" s="12" t="n">
+        <f aca="false">I78+J78-L78</f>
+        <v>0</v>
+      </c>
+      <c r="N78" s="12" t="n">
+        <f aca="false">P77</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O78" s="12" t="n">
+        <f aca="false">MIN(MAX(D78-G78-L78,0),MAX($B$15-$B$18-N78,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P78" s="12" t="n">
+        <f aca="false">N78+O78</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <f aca="false">IF(H78&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <f aca="false">IF(M78&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <f aca="false">IF(AND(Q78=1,R78=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <f aca="false">IF(P78&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U78" s="5" t="n">
+        <f aca="false">IF(P78+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V78" s="12" t="n">
+        <f aca="false">MAX(D78-G78-L78,0)-O78</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W78" s="12" t="n">
+        <f aca="false">P78+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="32" t="n">
+        <v>47574</v>
+      </c>
+      <c r="B79" s="25" t="n">
+        <f aca="false">IF(A79&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A79&gt;$B$33,$B$34,0)+IF(A79&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C79" s="12" t="n">
+        <f aca="false">IF(A79=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="12" t="n">
+        <f aca="false">B79+C79</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E79" s="12" t="n">
+        <f aca="false">H78</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="12" t="n">
+        <f aca="false">E79*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <f aca="false">MIN(E79+F79,MAX(D79-K79,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <f aca="false">E79+F79-G79</f>
+        <v>0</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <f aca="false">M78</f>
+        <v>0</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <f aca="false">I79*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <f aca="false">MIN(I79+J79,J79+$B$9*I79)</f>
+        <v>0</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <f aca="false">MIN(I79+J79,D79-G79)</f>
+        <v>0</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <f aca="false">I79+J79-L79</f>
+        <v>0</v>
+      </c>
+      <c r="N79" s="12" t="n">
+        <f aca="false">P78</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <f aca="false">MIN(MAX(D79-G79-L79,0),MAX($B$15-$B$18-N79,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P79" s="12" t="n">
+        <f aca="false">N79+O79</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q79" s="5" t="n">
+        <f aca="false">IF(H79&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R79" s="5" t="n">
+        <f aca="false">IF(M79&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S79" s="5" t="n">
+        <f aca="false">IF(AND(Q79=1,R79=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T79" s="5" t="n">
+        <f aca="false">IF(P79&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U79" s="5" t="n">
+        <f aca="false">IF(P79+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V79" s="12" t="n">
+        <f aca="false">MAX(D79-G79-L79,0)-O79</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W79" s="12" t="n">
+        <f aca="false">P79+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="32" t="n">
+        <v>47604</v>
+      </c>
+      <c r="B80" s="25" t="n">
+        <f aca="false">IF(A80&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A80&gt;$B$33,$B$34,0)+IF(A80&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C80" s="12" t="n">
+        <f aca="false">IF(A80=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="12" t="n">
+        <f aca="false">B80+C80</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E80" s="12" t="n">
+        <f aca="false">H79</f>
+        <v>0</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <f aca="false">E80*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <f aca="false">MIN(E80+F80,MAX(D80-K80,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <f aca="false">E80+F80-G80</f>
+        <v>0</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <f aca="false">M79</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="12" t="n">
+        <f aca="false">I80*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <f aca="false">MIN(I80+J80,J80+$B$9*I80)</f>
+        <v>0</v>
+      </c>
+      <c r="L80" s="12" t="n">
+        <f aca="false">MIN(I80+J80,D80-G80)</f>
+        <v>0</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <f aca="false">I80+J80-L80</f>
+        <v>0</v>
+      </c>
+      <c r="N80" s="12" t="n">
+        <f aca="false">P79</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O80" s="12" t="n">
+        <f aca="false">MIN(MAX(D80-G80-L80,0),MAX($B$15-$B$18-N80,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P80" s="12" t="n">
+        <f aca="false">N80+O80</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q80" s="5" t="n">
+        <f aca="false">IF(H80&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R80" s="5" t="n">
+        <f aca="false">IF(M80&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S80" s="5" t="n">
+        <f aca="false">IF(AND(Q80=1,R80=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T80" s="5" t="n">
+        <f aca="false">IF(P80&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U80" s="5" t="n">
+        <f aca="false">IF(P80+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V80" s="12" t="n">
+        <f aca="false">MAX(D80-G80-L80,0)-O80</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W80" s="12" t="n">
+        <f aca="false">P80+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="32" t="n">
+        <v>47635</v>
+      </c>
+      <c r="B81" s="25" t="n">
+        <f aca="false">IF(A81&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A81&gt;$B$33,$B$34,0)+IF(A81&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C81" s="12" t="n">
+        <f aca="false">IF(A81=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="12" t="n">
+        <f aca="false">B81+C81</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E81" s="12" t="n">
+        <f aca="false">H80</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="12" t="n">
+        <f aca="false">E81*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <f aca="false">MIN(E81+F81,MAX(D81-K81,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <f aca="false">E81+F81-G81</f>
+        <v>0</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <f aca="false">M80</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <f aca="false">I81*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K81" s="12" t="n">
+        <f aca="false">MIN(I81+J81,J81+$B$9*I81)</f>
+        <v>0</v>
+      </c>
+      <c r="L81" s="12" t="n">
+        <f aca="false">MIN(I81+J81,D81-G81)</f>
+        <v>0</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <f aca="false">I81+J81-L81</f>
+        <v>0</v>
+      </c>
+      <c r="N81" s="12" t="n">
+        <f aca="false">P80</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <f aca="false">MIN(MAX(D81-G81-L81,0),MAX($B$15-$B$18-N81,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <f aca="false">N81+O81</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q81" s="5" t="n">
+        <f aca="false">IF(H81&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R81" s="5" t="n">
+        <f aca="false">IF(M81&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S81" s="5" t="n">
+        <f aca="false">IF(AND(Q81=1,R81=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T81" s="5" t="n">
+        <f aca="false">IF(P81&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U81" s="5" t="n">
+        <f aca="false">IF(P81+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V81" s="12" t="n">
+        <f aca="false">MAX(D81-G81-L81,0)-O81</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W81" s="12" t="n">
+        <f aca="false">P81+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="32" t="n">
+        <v>47665</v>
+      </c>
+      <c r="B82" s="25" t="n">
+        <f aca="false">IF(A82&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A82&gt;$B$33,$B$34,0)+IF(A82&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C82" s="12" t="n">
+        <f aca="false">IF(A82=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D82" s="12" t="n">
+        <f aca="false">B82+C82</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E82" s="12" t="n">
+        <f aca="false">H81</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <f aca="false">E82*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <f aca="false">MIN(E82+F82,MAX(D82-K82,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <f aca="false">E82+F82-G82</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <f aca="false">M81</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="12" t="n">
+        <f aca="false">I82*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K82" s="12" t="n">
+        <f aca="false">MIN(I82+J82,J82+$B$9*I82)</f>
+        <v>0</v>
+      </c>
+      <c r="L82" s="12" t="n">
+        <f aca="false">MIN(I82+J82,D82-G82)</f>
+        <v>0</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <f aca="false">I82+J82-L82</f>
+        <v>0</v>
+      </c>
+      <c r="N82" s="12" t="n">
+        <f aca="false">P81</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O82" s="12" t="n">
+        <f aca="false">MIN(MAX(D82-G82-L82,0),MAX($B$15-$B$18-N82,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P82" s="12" t="n">
+        <f aca="false">N82+O82</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q82" s="5" t="n">
+        <f aca="false">IF(H82&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R82" s="5" t="n">
+        <f aca="false">IF(M82&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S82" s="5" t="n">
+        <f aca="false">IF(AND(Q82=1,R82=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T82" s="5" t="n">
+        <f aca="false">IF(P82&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U82" s="5" t="n">
+        <f aca="false">IF(P82+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V82" s="12" t="n">
+        <f aca="false">MAX(D82-G82-L82,0)-O82</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W82" s="12" t="n">
+        <f aca="false">P82+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="32" t="n">
+        <v>47696</v>
+      </c>
+      <c r="B83" s="25" t="n">
+        <f aca="false">IF(A83&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A83&gt;$B$33,$B$34,0)+IF(A83&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C83" s="12" t="n">
+        <f aca="false">IF(A83=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="12" t="n">
+        <f aca="false">B83+C83</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E83" s="12" t="n">
+        <f aca="false">H82</f>
+        <v>0</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <f aca="false">E83*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <f aca="false">MIN(E83+F83,MAX(D83-K83,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <f aca="false">E83+F83-G83</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <f aca="false">M82</f>
+        <v>0</v>
+      </c>
+      <c r="J83" s="12" t="n">
+        <f aca="false">I83*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K83" s="12" t="n">
+        <f aca="false">MIN(I83+J83,J83+$B$9*I83)</f>
+        <v>0</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <f aca="false">MIN(I83+J83,D83-G83)</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="12" t="n">
+        <f aca="false">I83+J83-L83</f>
+        <v>0</v>
+      </c>
+      <c r="N83" s="12" t="n">
+        <f aca="false">P82</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <f aca="false">MIN(MAX(D83-G83-L83,0),MAX($B$15-$B$18-N83,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P83" s="12" t="n">
+        <f aca="false">N83+O83</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q83" s="5" t="n">
+        <f aca="false">IF(H83&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R83" s="5" t="n">
+        <f aca="false">IF(M83&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S83" s="5" t="n">
+        <f aca="false">IF(AND(Q83=1,R83=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T83" s="5" t="n">
+        <f aca="false">IF(P83&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U83" s="5" t="n">
+        <f aca="false">IF(P83+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V83" s="12" t="n">
+        <f aca="false">MAX(D83-G83-L83,0)-O83</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W83" s="12" t="n">
+        <f aca="false">P83+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="32" t="n">
+        <v>47727</v>
+      </c>
+      <c r="B84" s="25" t="n">
+        <f aca="false">IF(A84&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A84&gt;$B$33,$B$34,0)+IF(A84&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C84" s="12" t="n">
+        <f aca="false">IF(A84=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <f aca="false">B84+C84</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <f aca="false">H83</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <f aca="false">E84*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <f aca="false">MIN(E84+F84,MAX(D84-K84,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <f aca="false">E84+F84-G84</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <f aca="false">M83</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <f aca="false">I84*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <f aca="false">MIN(I84+J84,J84+$B$9*I84)</f>
+        <v>0</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <f aca="false">MIN(I84+J84,D84-G84)</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <f aca="false">I84+J84-L84</f>
+        <v>0</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <f aca="false">P83</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O84" s="12" t="n">
+        <f aca="false">MIN(MAX(D84-G84-L84,0),MAX($B$15-$B$18-N84,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P84" s="12" t="n">
+        <f aca="false">N84+O84</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <f aca="false">IF(H84&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <f aca="false">IF(M84&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S84" s="5" t="n">
+        <f aca="false">IF(AND(Q84=1,R84=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <f aca="false">IF(P84&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U84" s="5" t="n">
+        <f aca="false">IF(P84+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <f aca="false">MAX(D84-G84-L84,0)-O84</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <f aca="false">P84+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="32" t="n">
+        <v>47757</v>
+      </c>
+      <c r="B85" s="25" t="n">
+        <f aca="false">IF(A85&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A85&gt;$B$33,$B$34,0)+IF(A85&gt;=$B$30,$B$31,0)</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="C85" s="12" t="n">
+        <f aca="false">IF(A85=$B$32,$B$25-$B$26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="12" t="n">
+        <f aca="false">B85+C85</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="E85" s="12" t="n">
+        <f aca="false">H84</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <f aca="false">E85*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <f aca="false">MIN(E85+F85,MAX(D85-K85,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <f aca="false">E85+F85-G85</f>
+        <v>0</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <f aca="false">M84</f>
+        <v>0</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <f aca="false">I85*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <f aca="false">MIN(I85+J85,J85+$B$9*I85)</f>
+        <v>0</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <f aca="false">MIN(I85+J85,D85-G85)</f>
+        <v>0</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <f aca="false">I85+J85-L85</f>
+        <v>0</v>
+      </c>
+      <c r="N85" s="12" t="n">
+        <f aca="false">P84</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <f aca="false">MIN(MAX(D85-G85-L85,0),MAX($B$15-$B$18-N85,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P85" s="12" t="n">
+        <f aca="false">N85+O85</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q85" s="5" t="n">
+        <f aca="false">IF(H85&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R85" s="5" t="n">
+        <f aca="false">IF(M85&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S85" s="5" t="n">
+        <f aca="false">IF(AND(Q85=1,R85=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T85" s="5" t="n">
+        <f aca="false">IF(P85&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U85" s="5" t="n">
+        <f aca="false">IF(P85+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V85" s="12" t="n">
+        <f aca="false">MAX(D85-G85-L85,0)-O85</f>
+        <v>3336.57666666667</v>
+      </c>
+      <c r="W85" s="12" t="n">
+        <f aca="false">P85+$B$18</f>
         <v>100842</v>
       </c>
     </row>
@@ -9086,12 +9251,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9099,48 +9264,48 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -9158,7 +9323,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>17767.46</v>
@@ -9205,7 +9370,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>6410.38</v>
@@ -9252,7 +9417,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>1459.54</v>
@@ -9299,7 +9464,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">SUM(B6:B8)</f>
@@ -9356,7 +9521,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -9374,7 +9539,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>4300</v>
@@ -9421,7 +9586,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B13" s="13" t="n">
         <v>32.71</v>
@@ -9468,7 +9633,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B14" s="13" t="n">
         <v>0</v>
@@ -9515,7 +9680,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>183.82</v>
@@ -9562,7 +9727,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B16" s="13" t="n">
         <v>500</v>
@@ -9609,7 +9774,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">SUM(B12:B16)</f>
@@ -9666,7 +9831,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -9684,7 +9849,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B20" s="13" t="n">
         <v>6857.93</v>
@@ -9778,7 +9943,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="B22" s="13" t="n">
         <v>1057.39</v>
@@ -9825,7 +9990,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B23" s="13" t="n">
         <v>341.99</v>
@@ -9872,7 +10037,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B24" s="13" t="n">
         <v>0</v>
@@ -9919,7 +10084,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="B25" s="13" t="n">
         <v>856.83</v>
@@ -9966,7 +10131,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B26" s="13" t="n">
         <v>286.67</v>
@@ -10013,7 +10178,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B27" s="13" t="n">
         <v>614</v>
@@ -10060,7 +10225,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B28" s="13" t="n">
         <v>323.39</v>
@@ -10107,7 +10272,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B29" s="13" t="n">
         <v>368.15</v>
@@ -10154,7 +10319,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B30" s="13" t="n">
         <v>400.62</v>
@@ -10201,7 +10366,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B31" s="13" t="n">
         <v>134.97</v>
@@ -10248,7 +10413,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B32" s="13" t="n">
         <v>178.9</v>
@@ -10295,7 +10460,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B33" s="13" t="n">
         <v>115.5</v>
@@ -10342,7 +10507,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B34" s="13" t="n">
         <v>760</v>
@@ -10389,7 +10554,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B35" s="13" t="n">
         <v>155</v>
@@ -10483,7 +10648,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B37" s="13" t="n">
         <v>473.56</v>
@@ -10530,7 +10695,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="B38" s="13" t="n">
         <v>431.52</v>
@@ -10577,7 +10742,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B39" s="13" t="n">
         <v>359.9</v>
@@ -10624,7 +10789,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="B40" s="13" t="n">
         <v>27.6</v>
@@ -10671,7 +10836,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B41" s="13" t="n">
         <v>557.68</v>
@@ -10718,7 +10883,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B42" s="13" t="n">
         <v>385.13</v>
@@ -10765,7 +10930,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="B43" s="13" t="n">
         <v>209</v>
@@ -10812,7 +10977,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="B44" s="13" t="n">
         <v>266.15</v>
@@ -10906,7 +11071,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B46" s="13" t="n">
         <v>469.36</v>
@@ -11000,7 +11165,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B48" s="13" t="n">
         <v>72.9</v>
@@ -11047,7 +11212,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="B49" s="13" t="n">
         <v>0.5</v>
@@ -11094,7 +11259,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B50" s="13" t="n">
         <v>355.78</v>
@@ -11141,7 +11306,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="B51" s="13" t="n">
         <v>97.3</v>
@@ -11188,7 +11353,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B52" s="13" t="n">
         <v>129.41</v>
@@ -11235,7 +11400,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B53" s="13" t="n">
         <v>465.78</v>
@@ -11282,7 +11447,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B54" s="13" t="n">
         <v>240</v>
@@ -11329,7 +11494,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B55" s="13" t="n">
         <v>729.5</v>
@@ -11376,7 +11541,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B56" s="13" t="n">
         <v>2.25</v>
@@ -11423,7 +11588,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B57" s="13" t="n">
         <v>0</v>
@@ -11470,7 +11635,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B58" s="13" t="n">
         <v>127.73</v>
@@ -11517,7 +11682,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B59" s="17" t="n">
         <f aca="false">SUM(B20:B58)</f>
@@ -11574,121 +11739,121 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="B61" s="31" t="n">
+        <v>320</v>
+      </c>
+      <c r="B61" s="33" t="n">
         <f aca="false">B17+B59</f>
         <v>24684.05</v>
       </c>
-      <c r="C61" s="31" t="n">
+      <c r="C61" s="33" t="n">
         <f aca="false">C17+C59</f>
         <v>27719.87</v>
       </c>
-      <c r="D61" s="31" t="n">
+      <c r="D61" s="33" t="n">
         <f aca="false">D17+D59</f>
         <v>56439.39</v>
       </c>
-      <c r="E61" s="31" t="n">
+      <c r="E61" s="33" t="n">
         <f aca="false">E17+E59</f>
         <v>22907.78</v>
       </c>
-      <c r="F61" s="31" t="n">
+      <c r="F61" s="33" t="n">
         <f aca="false">F17+F59</f>
         <v>44473.94</v>
       </c>
-      <c r="G61" s="31" t="n">
+      <c r="G61" s="33" t="n">
         <f aca="false">G17+G59</f>
         <v>26238.9</v>
       </c>
-      <c r="H61" s="31" t="n">
+      <c r="H61" s="33" t="n">
         <f aca="false">H17+H59</f>
         <v>32051.74</v>
       </c>
-      <c r="I61" s="31" t="n">
+      <c r="I61" s="33" t="n">
         <f aca="false">I17+I59</f>
         <v>22904.52</v>
       </c>
-      <c r="J61" s="31" t="n">
+      <c r="J61" s="33" t="n">
         <f aca="false">J17+J59</f>
         <v>25351.77</v>
       </c>
-      <c r="K61" s="31" t="n">
+      <c r="K61" s="33" t="n">
         <f aca="false">K17+K59</f>
         <v>14323.55</v>
       </c>
-      <c r="L61" s="31" t="n">
+      <c r="L61" s="33" t="n">
         <f aca="false">L17+L59</f>
         <v>282771.96</v>
       </c>
-      <c r="M61" s="31" t="n">
+      <c r="M61" s="33" t="n">
         <f aca="false">M17+M59</f>
         <v>31419.1066666667</v>
       </c>
-      <c r="N61" s="31" t="n">
+      <c r="N61" s="33" t="n">
         <f aca="false">N17+N59</f>
         <v>26769.3433333333</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="B62" s="31" t="n">
+        <v>321</v>
+      </c>
+      <c r="B62" s="33" t="n">
         <f aca="false">B9</f>
         <v>25637.38</v>
       </c>
-      <c r="C62" s="31" t="n">
+      <c r="C62" s="33" t="n">
         <f aca="false">C9</f>
         <v>27081.19</v>
       </c>
-      <c r="D62" s="31" t="n">
+      <c r="D62" s="33" t="n">
         <f aca="false">D9</f>
         <v>63061.87</v>
       </c>
-      <c r="E62" s="31" t="n">
+      <c r="E62" s="33" t="n">
         <f aca="false">E9</f>
         <v>50339.13</v>
       </c>
-      <c r="F62" s="31" t="n">
+      <c r="F62" s="33" t="n">
         <f aca="false">F9</f>
         <v>27082.05</v>
       </c>
-      <c r="G62" s="31" t="n">
+      <c r="G62" s="33" t="n">
         <f aca="false">G9</f>
         <v>25881.6</v>
       </c>
-      <c r="H62" s="31" t="n">
+      <c r="H62" s="33" t="n">
         <f aca="false">H9</f>
         <v>27427.38</v>
       </c>
-      <c r="I62" s="31" t="n">
+      <c r="I62" s="33" t="n">
         <f aca="false">I9</f>
         <v>25986.74</v>
       </c>
-      <c r="J62" s="31" t="n">
+      <c r="J62" s="33" t="n">
         <f aca="false">J9</f>
         <v>27979.39</v>
       </c>
-      <c r="K62" s="31" t="n">
+      <c r="K62" s="33" t="n">
         <f aca="false">K9</f>
         <v>2362.27</v>
       </c>
-      <c r="L62" s="31" t="n">
+      <c r="L62" s="33" t="n">
         <f aca="false">L9</f>
         <v>300476.73</v>
       </c>
-      <c r="M62" s="31" t="n">
+      <c r="M62" s="33" t="n">
         <f aca="false">M9</f>
         <v>33386.3033333333</v>
       </c>
-      <c r="N62" s="31" t="n">
+      <c r="N62" s="33" t="n">
         <f aca="false">N9</f>
         <v>27131.17</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B63" s="9" t="n">
         <f aca="false">B62-B61</f>
@@ -11774,35 +11939,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>20</v>
@@ -11810,10 +11975,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>72.97</v>
@@ -11822,26 +11987,26 @@
         <f aca="false">IF(B5="Monthly",C5*12,IF(B5="Semiannual",C5*2,C5))</f>
         <v>875.64</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>317</v>
+      <c r="E5" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">IF(E5="Cut",D5,0)</f>
         <v>0</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>82.99</v>
@@ -11850,26 +12015,26 @@
         <f aca="false">IF(B6="Monthly",C6*12,IF(B6="Semiannual",C6*2,C6))</f>
         <v>995.88</v>
       </c>
-      <c r="E6" s="32" t="s">
-        <v>321</v>
+      <c r="E6" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">IF(E6="Cut",D6,0)</f>
         <v>0</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>26.99</v>
@@ -11878,24 +12043,24 @@
         <f aca="false">IF(B7="Monthly",C7*12,IF(B7="Semiannual",C7*2,C7))</f>
         <v>323.88</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>317</v>
+      <c r="E7" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">IF(E7="Cut",D7,0)</f>
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>18.99</v>
@@ -11904,26 +12069,26 @@
         <f aca="false">IF(B8="Monthly",C8*12,IF(B8="Semiannual",C8*2,C8))</f>
         <v>227.88</v>
       </c>
-      <c r="E8" s="32" t="s">
-        <v>321</v>
+      <c r="E8" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">IF(E8="Cut",D8,0)</f>
         <v>0</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>12.99</v>
@@ -11932,24 +12097,24 @@
         <f aca="false">IF(B9="Monthly",C9*12,IF(B9="Semiannual",C9*2,C9))</f>
         <v>155.88</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>317</v>
+      <c r="E9" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">IF(E9="Cut",D9,0)</f>
         <v>0</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>139</v>
@@ -11958,26 +12123,26 @@
         <f aca="false">IF(B10="Monthly",C10*12,IF(B10="Semiannual",C10*2,C10))</f>
         <v>139</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>317</v>
+      <c r="E10" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">IF(E10="Cut",D10,0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>4.99</v>
@@ -11986,26 +12151,26 @@
         <f aca="false">IF(B11="Monthly",C11*12,IF(B11="Semiannual",C11*2,C11))</f>
         <v>59.88</v>
       </c>
-      <c r="E11" s="32" t="s">
-        <v>321</v>
+      <c r="E11" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">IF(E11="Cut",D11,0)</f>
         <v>0</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>6.36</v>
@@ -12014,26 +12179,26 @@
         <f aca="false">IF(B12="Monthly",C12*12,IF(B12="Semiannual",C12*2,C12))</f>
         <v>76.32</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>321</v>
+      <c r="E12" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">IF(E12="Cut",D12,0)</f>
         <v>0</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>11.99</v>
@@ -12042,26 +12207,26 @@
         <f aca="false">IF(B13="Monthly",C13*12,IF(B13="Semiannual",C13*2,C13))</f>
         <v>143.88</v>
       </c>
-      <c r="E13" s="32" t="s">
-        <v>321</v>
+      <c r="E13" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">IF(E13="Cut",D13,0)</f>
         <v>0</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>8.99</v>
@@ -12070,26 +12235,26 @@
         <f aca="false">IF(B14="Monthly",C14*12,IF(B14="Semiannual",C14*2,C14))</f>
         <v>107.88</v>
       </c>
-      <c r="E14" s="32" t="s">
-        <v>321</v>
+      <c r="E14" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">IF(E14="Cut",D14,0)</f>
         <v>0</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>25</v>
@@ -12098,26 +12263,26 @@
         <f aca="false">IF(B15="Monthly",C15*12,IF(B15="Semiannual",C15*2,C15))</f>
         <v>300</v>
       </c>
-      <c r="E15" s="32" t="s">
-        <v>321</v>
+      <c r="E15" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F15" s="12" t="n">
         <f aca="false">IF(E15="Cut",D15,0)</f>
         <v>0</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>27.72</v>
@@ -12126,26 +12291,26 @@
         <f aca="false">IF(B16="Monthly",C16*12,IF(B16="Semiannual",C16*2,C16))</f>
         <v>332.64</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>321</v>
+      <c r="E16" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F16" s="12" t="n">
         <f aca="false">IF(E16="Cut",D16,0)</f>
         <v>0</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>99.99</v>
@@ -12154,24 +12319,24 @@
         <f aca="false">IF(B17="Monthly",C17*12,IF(B17="Semiannual",C17*2,C17))</f>
         <v>99.99</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>321</v>
+      <c r="E17" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F17" s="12" t="n">
         <f aca="false">IF(E17="Cut",D17,0)</f>
         <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>150</v>
@@ -12180,24 +12345,24 @@
         <f aca="false">IF(B18="Monthly",C18*12,IF(B18="Semiannual",C18*2,C18))</f>
         <v>150</v>
       </c>
-      <c r="E18" s="32" t="s">
-        <v>321</v>
+      <c r="E18" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F18" s="12" t="n">
         <f aca="false">IF(E18="Cut",D18,0)</f>
         <v>0</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>20.7</v>
@@ -12206,26 +12371,26 @@
         <f aca="false">IF(B19="Monthly",C19*12,IF(B19="Semiannual",C19*2,C19))</f>
         <v>248.4</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>317</v>
+      <c r="E19" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F19" s="12" t="n">
         <f aca="false">IF(E19="Cut",D19,0)</f>
         <v>0</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>10</v>
@@ -12234,26 +12399,26 @@
         <f aca="false">IF(B20="Monthly",C20*12,IF(B20="Semiannual",C20*2,C20))</f>
         <v>120</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>317</v>
+      <c r="E20" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">IF(E20="Cut",D20,0)</f>
         <v>0</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>32.99</v>
@@ -12262,26 +12427,26 @@
         <f aca="false">IF(B21="Monthly",C21*12,IF(B21="Semiannual",C21*2,C21))</f>
         <v>395.88</v>
       </c>
-      <c r="E21" s="32" t="s">
-        <v>321</v>
+      <c r="E21" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">IF(E21="Cut",D21,0)</f>
         <v>0</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>13.94</v>
@@ -12290,26 +12455,26 @@
         <f aca="false">IF(B22="Monthly",C22*12,IF(B22="Semiannual",C22*2,C22))</f>
         <v>167.28</v>
       </c>
-      <c r="E22" s="32" t="s">
-        <v>321</v>
+      <c r="E22" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">IF(E22="Cut",D22,0)</f>
         <v>0</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>20.76</v>
@@ -12318,26 +12483,26 @@
         <f aca="false">IF(B23="Monthly",C23*12,IF(B23="Semiannual",C23*2,C23))</f>
         <v>249.12</v>
       </c>
-      <c r="E23" s="32" t="s">
-        <v>321</v>
+      <c r="E23" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F23" s="12" t="n">
         <f aca="false">IF(E23="Cut",D23,0)</f>
         <v>0</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>10.63</v>
@@ -12346,24 +12511,24 @@
         <f aca="false">IF(B24="Monthly",C24*12,IF(B24="Semiannual",C24*2,C24))</f>
         <v>127.56</v>
       </c>
-      <c r="E24" s="32" t="s">
-        <v>317</v>
+      <c r="E24" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F24" s="12" t="n">
         <f aca="false">IF(E24="Cut",D24,0)</f>
         <v>0</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>21.25</v>
@@ -12372,24 +12537,24 @@
         <f aca="false">IF(B25="Monthly",C25*12,IF(B25="Semiannual",C25*2,C25))</f>
         <v>255</v>
       </c>
-      <c r="E25" s="32" t="s">
-        <v>317</v>
+      <c r="E25" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F25" s="12" t="n">
         <f aca="false">IF(E25="Cut",D25,0)</f>
         <v>0</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>381.44</v>
@@ -12398,26 +12563,26 @@
         <f aca="false">IF(B26="Monthly",C26*12,IF(B26="Semiannual",C26*2,C26))</f>
         <v>381.44</v>
       </c>
-      <c r="E26" s="32" t="s">
-        <v>317</v>
+      <c r="E26" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F26" s="12" t="n">
         <f aca="false">IF(E26="Cut",D26,0)</f>
         <v>0</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>212.49</v>
@@ -12426,26 +12591,26 @@
         <f aca="false">IF(B27="Monthly",C27*12,IF(B27="Semiannual",C27*2,C27))</f>
         <v>212.49</v>
       </c>
-      <c r="E27" s="32" t="s">
-        <v>321</v>
+      <c r="E27" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F27" s="12" t="n">
         <f aca="false">IF(E27="Cut",D27,0)</f>
         <v>0</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>114.75</v>
@@ -12454,26 +12619,26 @@
         <f aca="false">IF(B28="Monthly",C28*12,IF(B28="Semiannual",C28*2,C28))</f>
         <v>229.5</v>
       </c>
-      <c r="E28" s="32" t="s">
-        <v>321</v>
+      <c r="E28" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F28" s="12" t="n">
         <f aca="false">IF(E28="Cut",D28,0)</f>
         <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>548</v>
@@ -12482,26 +12647,26 @@
         <f aca="false">IF(B29="Monthly",C29*12,IF(B29="Semiannual",C29*2,C29))</f>
         <v>548</v>
       </c>
-      <c r="E29" s="32" t="s">
-        <v>317</v>
+      <c r="E29" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="12" t="n">
         <f aca="false">IF(E29="Cut",D29,0)</f>
         <v>0</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>32.95</v>
@@ -12510,26 +12675,26 @@
         <f aca="false">IF(B30="Monthly",C30*12,IF(B30="Semiannual",C30*2,C30))</f>
         <v>395.4</v>
       </c>
-      <c r="E30" s="32" t="s">
-        <v>321</v>
+      <c r="E30" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F30" s="12" t="n">
         <f aca="false">IF(E30="Cut",D30,0)</f>
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>115.23</v>
@@ -12538,26 +12703,26 @@
         <f aca="false">IF(B31="Monthly",C31*12,IF(B31="Semiannual",C31*2,C31))</f>
         <v>1382.76</v>
       </c>
-      <c r="E31" s="32" t="s">
-        <v>321</v>
+      <c r="E31" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="F31" s="12" t="n">
         <f aca="false">IF(E31="Cut",D31,0)</f>
         <v>0</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>25</v>
@@ -12566,23 +12731,23 @@
         <f aca="false">IF(B32="Monthly",C32*12,IF(B32="Semiannual",C32*2,C32))</f>
         <v>300</v>
       </c>
-      <c r="E32" s="32" t="s">
-        <v>317</v>
+      <c r="E32" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="F32" s="12" t="n">
         <f aca="false">IF(E32="Cut",D32,0)</f>
         <v>0</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="D33" s="17" t="n">
         <f aca="false">SUM(D5:D32)</f>
@@ -12595,7 +12760,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="D34" s="12" t="n">
         <f aca="false">SUMIF(E5:E32,"Review",D5:D32)</f>
@@ -12604,7 +12769,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -12623,7 +12788,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -12632,148 +12797,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>396</v>
+      <c r="A3" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>398</v>
+      <c r="A4" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>400</v>
+      <c r="A5" s="35" t="s">
+        <v>416</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>402</v>
+      <c r="A6" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
-        <v>403</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>404</v>
+      <c r="A7" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
-        <v>405</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>406</v>
+      <c r="A8" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>408</v>
+      <c r="A9" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>410</v>
+      <c r="A10" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>412</v>
+      <c r="A11" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="s">
-        <v>413</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>414</v>
+      <c r="A12" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>417</v>
+        <v>433</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>418</v>
+        <v>433</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>419</v>
+        <v>433</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>420</v>
+        <v>433</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>421</v>
+        <v>433</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>433</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>423</v>
+        <v>433</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
+++ b/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="478">
   <si>
     <t xml:space="preserve">Household Budget — October 2026 rebuild</t>
   </si>
@@ -772,7 +772,22 @@
     <t xml:space="preserve">Pre-funds camp/trips due before enough has built up (Sinking Funds sheet). Your stack: debt → liquidity → lifestyle → investible. Overwrite to change.</t>
   </si>
   <si>
-    <t xml:space="preserve">Diogo base salary</t>
+    <t xml:space="preserve">Flagship base salary (bonus basis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per you: the March bonus is paid on the current $339k.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New base salary (from 11/2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per you. The March raise applies to this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net effect of the +$1k base from Nov-26 (per month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(New − old salary) × net share ÷ 12. Take-home otherwise assumed unchanged.</t>
   </si>
   <si>
     <t xml:space="preserve">Cost-of-living raise %</t>
@@ -1441,7 +1456,7 @@
     <t xml:space="preserve">Categories are keyword-based on merchant strings; unclassified items are shown on Actuals. Weekly checks = cleaning help ($160/wk); DoorDash/Grubhub = family takeout (per you). HELOC payment of ~$1,100 is assumed from Nov-26. Synchrony = 0% AC-repair loan; Wells Fargo = 0% plumbing loan, assumed $450/mo (one payment seen).</t>
   </si>
   <si>
-    <t xml:space="preserve">Job change: new job starts 11/2. Take-home is assumed unchanged at the new employer (pay, cadence and benefits not yet known). Bonus = 25% of $339k at an assumed 1.00 multiplier, paid in March net of withholding; ~$4k extra tax is reserved for April. Raise (3% midpoint of your 2–4%) starts in March with 2 months of back pay (assumed Jan 1).</t>
+    <t xml:space="preserve">Job change: new job starts 11/2. Pay cadence is unchanged and the first new-employer paycheck is 11/15 (no missed paycheck); take-home is assumed unchanged apart from +$50/mo from the $1k higher base. Benefits start date still unknown. Bonus = 25% of $339k at an assumed 1.00 multiplier, paid in March net of withholding; ~$4k extra tax is reserved for April. Raise (3% midpoint of your 2–4%) applies to the new $340k base, starts in March, with 2 months of back pay (assumed Jan 1).</t>
   </si>
   <si>
     <t xml:space="preserve">Not financial, tax, or legal advice.</t>
@@ -4616,7 +4631,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W90"/>
+  <dimension ref="A1:W92"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -4670,7 +4685,7 @@
         <v>195</v>
       </c>
       <c r="G5" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A43:A90,MATCH(1,Q43:Q90,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,Q45:Q92,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4688,7 +4703,7 @@
         <v>198</v>
       </c>
       <c r="G6" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A43:A90,MATCH(1,R43:R90,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,R45:R92,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4706,7 +4721,7 @@
         <v>200</v>
       </c>
       <c r="G7" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A43:A90,MATCH(1,S43:S90,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,S45:S92,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4724,7 +4739,7 @@
         <v>202</v>
       </c>
       <c r="G8" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A43:A90,MATCH(1,T43:T90,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,T45:T92,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4742,8 +4757,8 @@
         <v>205</v>
       </c>
       <c r="G9" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A43:A90,MATCH(1,U43:U90,0)),"after Oct-30")</f>
-        <v>46905</v>
+        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,U45:U92,0)),"after Oct-30")</f>
+        <v>46874</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4760,8 +4775,8 @@
         <v>208</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUM(F43:F90)+SUM(J43:J90)</f>
-        <v>1455.31534406423</v>
+        <f aca="false">SUM(F45:F92)+SUM(J45:J92)</f>
+        <v>1442.47513468667</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5000,419 +5015,256 @@
         <v>339000</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B31" s="33" t="n">
-        <v>0.03</v>
+        <v>250</v>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>340000</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B32" s="33" t="n">
-        <v>0.6065</v>
+        <v>252</v>
+      </c>
+      <c r="B32" s="12" t="n">
+        <f aca="false">($B$31-$B$30)*$B$34/12</f>
+        <v>50.5416666666667</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B33" s="26" t="n">
-        <v>46447</v>
+        <v>254</v>
+      </c>
+      <c r="B33" s="33" t="n">
+        <v>0.03</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>2</v>
+        <v>256</v>
+      </c>
+      <c r="B34" s="33" t="n">
+        <v>0.6065</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B35" s="12" t="n">
-        <f aca="false">$B$30*$B$31*$B$32/12</f>
-        <v>514.00875</v>
+        <v>258</v>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>46447</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>0</v>
+        <v>260</v>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B37" s="26" t="n">
-        <v>46447</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="B37" s="12" t="n">
+        <f aca="false">$B$31*$B$33*$B$34/12</f>
+        <v>515.525</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B38" s="26" t="n">
-        <v>47119</v>
+        <v>264</v>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B39" s="21" t="n">
+        <v>266</v>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>46447</v>
+      </c>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B40" s="26" t="n">
+        <v>47119</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B41" s="21" t="n">
         <f aca="false">Budget!F16</f>
         <v>342</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="E42" s="10" t="s">
+      <c r="C41" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="F42" s="10" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="B44" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="C44" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="I42" s="10" t="s">
+      <c r="D44" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="E44" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="K42" s="10" t="s">
+      <c r="F44" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="L42" s="10" t="s">
+      <c r="G44" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="M42" s="10" t="s">
+      <c r="H44" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="N42" s="10" t="s">
+      <c r="I44" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="O42" s="10" t="s">
+      <c r="J44" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="P42" s="10" t="s">
+      <c r="K44" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="Q42" s="10" t="s">
+      <c r="L44" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="R42" s="10" t="s">
+      <c r="M44" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="S42" s="10" t="s">
+      <c r="N44" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="T42" s="10" t="s">
+      <c r="O44" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="U42" s="10" t="s">
+      <c r="P44" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="V42" s="10" t="s">
+      <c r="Q44" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="W42" s="10" t="s">
+      <c r="R44" s="10" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="34" t="n">
+      <c r="S44" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="T44" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="U44" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="V44" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="W44" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="34" t="n">
         <v>46327</v>
       </c>
-      <c r="B43" s="21" t="n">
-        <f aca="false">IF(A43&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A43&gt;$B$38,$B$39,0)+IF(A43&gt;=$B$33,$B$35,0)</f>
-        <v>926.776666666669</v>
-      </c>
-      <c r="C43" s="12" t="n">
-        <f aca="false">IF(A43=$B$37,$B$26-$B$29,0)-IF(A43=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A43=$B$33,$B$35*$B$34,0)+$B$36</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <f aca="false">B43+C43</f>
-        <v>926.776666666669</v>
-      </c>
-      <c r="E43" s="12" t="n">
+      <c r="B45" s="21" t="n">
+        <f aca="false">IF(A45&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A45&gt;$B$40,$B$41,0)+IF(A45&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>977.318333333335</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <f aca="false">IF(A45=$B$39,$B$26-$B$29,0)-IF(A45=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A45=$B$35,$B$37*$B$36,0)+$B$38</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <f aca="false">B45+C45</f>
+        <v>977.318333333335</v>
+      </c>
+      <c r="E45" s="12" t="n">
         <f aca="false">$B$5</f>
         <v>9800.78</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <f aca="false">E43*$B$6/12</f>
+      <c r="F45" s="12" t="n">
+        <f aca="false">E45*$B$6/12</f>
         <v>242.895997666667</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <f aca="false">MIN(E43+F43,MAX(D43-K43,0))</f>
-        <v>795.508812666668</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <f aca="false">E43+F43-G43</f>
-        <v>9248.167185</v>
-      </c>
-      <c r="I43" s="12" t="n">
+      <c r="G45" s="12" t="n">
+        <f aca="false">MIN(E45+F45,MAX(D45-K45,0))</f>
+        <v>846.050479333335</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <f aca="false">E45+F45-G45</f>
+        <v>9197.62551833333</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <f aca="false">$B$7</f>
         <v>5341.52</v>
       </c>
-      <c r="J43" s="12" t="n">
-        <f aca="false">I43*$B$8/12</f>
-        <v>77.852654</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <f aca="false">MIN(I43+J43,J43+$B$9*I43)</f>
-        <v>131.267854</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <f aca="false">MIN(I43+J43,MAX(D43-G43,0))</f>
-        <v>131.267854</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <f aca="false">I43+J43-L43</f>
-        <v>5288.1048</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <f aca="false">$B$10-$B$36</f>
-        <v>12081</v>
-      </c>
-      <c r="O43" s="12" t="n">
-        <f aca="false">MIN(D43-G43-L43,MAX($B$15-$B$18-N43,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P43" s="12" t="n">
-        <f aca="false">N43+O43</f>
-        <v>12081</v>
-      </c>
-      <c r="Q43" s="5" t="n">
-        <f aca="false">IF(H43&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R43" s="5" t="n">
-        <f aca="false">IF(M43&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S43" s="5" t="n">
-        <f aca="false">IF(AND(Q43=1,R43=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T43" s="5" t="n">
-        <f aca="false">IF(P43&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="5" t="n">
-        <f aca="false">IF(P43+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="12" t="n">
-        <f aca="false">MAX(D43-G43-L43,0)-MAX(O43,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W43" s="12" t="n">
-        <f aca="false">P43+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="34" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B44" s="21" t="n">
-        <f aca="false">IF(A44&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A44&gt;$B$38,$B$39,0)+IF(A44&gt;=$B$33,$B$35,0)</f>
-        <v>926.776666666669</v>
-      </c>
-      <c r="C44" s="12" t="n">
-        <f aca="false">IF(A44=$B$37,$B$26-$B$29,0)-IF(A44=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A44=$B$33,$B$35*$B$34,0)+0</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="12" t="n">
-        <f aca="false">B44+C44</f>
-        <v>926.776666666669</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <f aca="false">H43</f>
-        <v>9248.167185</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <f aca="false">E44*$B$6/12</f>
-        <v>229.20041006825</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <f aca="false">MIN(E44+F44,MAX(D44-K44,0))</f>
-        <v>796.821491206669</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <f aca="false">E44+F44-G44</f>
-        <v>8680.54610386158</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <f aca="false">M43</f>
-        <v>5288.1048</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <f aca="false">I44*$B$8/12</f>
-        <v>77.07412746</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <f aca="false">MIN(I44+J44,J44+$B$9*I44)</f>
-        <v>129.95517546</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <f aca="false">MIN(I44+J44,MAX(D44-G44,0))</f>
-        <v>129.95517546</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <f aca="false">I44+J44-L44</f>
-        <v>5235.223752</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <f aca="false">P43</f>
-        <v>12081</v>
-      </c>
-      <c r="O44" s="12" t="n">
-        <f aca="false">MIN(D44-G44-L44,MAX($B$15-$B$18-N44,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P44" s="12" t="n">
-        <f aca="false">N44+O44</f>
-        <v>12081</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <f aca="false">IF(H44&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R44" s="5" t="n">
-        <f aca="false">IF(M44&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S44" s="5" t="n">
-        <f aca="false">IF(AND(Q44=1,R44=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T44" s="5" t="n">
-        <f aca="false">IF(P44&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U44" s="5" t="n">
-        <f aca="false">IF(P44+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V44" s="12" t="n">
-        <f aca="false">MAX(D44-G44-L44,0)-MAX(O44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W44" s="12" t="n">
-        <f aca="false">P44+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34" t="n">
-        <v>46388</v>
-      </c>
-      <c r="B45" s="21" t="n">
-        <f aca="false">IF(A45&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A45&gt;$B$38,$B$39,0)+IF(A45&gt;=$B$33,$B$35,0)</f>
-        <v>926.776666666669</v>
-      </c>
-      <c r="C45" s="12" t="n">
-        <f aca="false">IF(A45=$B$37,$B$26-$B$29,0)-IF(A45=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A45=$B$33,$B$35*$B$34,0)+0</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <f aca="false">B45+C45</f>
-        <v>926.776666666669</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <f aca="false">H44</f>
-        <v>8680.54610386158</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <f aca="false">E45*$B$6/12</f>
-        <v>215.132867607369</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <f aca="false">MIN(E45+F45,MAX(D45-K45,0))</f>
-        <v>798.121042961268</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <f aca="false">E45+F45-G45</f>
-        <v>8097.55792850768</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <f aca="false">M44</f>
-        <v>5235.223752</v>
-      </c>
       <c r="J45" s="12" t="n">
         <f aca="false">I45*$B$8/12</f>
-        <v>76.3033861854</v>
+        <v>77.852654</v>
       </c>
       <c r="K45" s="12" t="n">
         <f aca="false">MIN(I45+J45,J45+$B$9*I45)</f>
-        <v>128.6556237054</v>
+        <v>131.267854</v>
       </c>
       <c r="L45" s="12" t="n">
         <f aca="false">MIN(I45+J45,MAX(D45-G45,0))</f>
-        <v>128.6556237054</v>
+        <v>131.267854</v>
       </c>
       <c r="M45" s="12" t="n">
         <f aca="false">I45+J45-L45</f>
-        <v>5182.87151448</v>
+        <v>5288.1048</v>
       </c>
       <c r="N45" s="12" t="n">
-        <f aca="false">P44</f>
+        <f aca="false">$B$10-$B$38</f>
         <v>12081</v>
       </c>
       <c r="O45" s="12" t="n">
@@ -5454,55 +5306,55 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="34" t="n">
-        <v>46419</v>
+        <v>46357</v>
       </c>
       <c r="B46" s="21" t="n">
-        <f aca="false">IF(A46&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A46&gt;$B$38,$B$39,0)+IF(A46&gt;=$B$33,$B$35,0)</f>
-        <v>926.776666666669</v>
+        <f aca="false">IF(A46&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A46&gt;$B$40,$B$41,0)+IF(A46&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>977.318333333335</v>
       </c>
       <c r="C46" s="12" t="n">
-        <f aca="false">IF(A46=$B$37,$B$26-$B$29,0)-IF(A46=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A46=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A46=$B$39,$B$26-$B$29,0)-IF(A46=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A46=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D46" s="12" t="n">
         <f aca="false">B46+C46</f>
-        <v>926.776666666669</v>
+        <v>977.318333333335</v>
       </c>
       <c r="E46" s="12" t="n">
         <f aca="false">H45</f>
-        <v>8097.55792850768</v>
+        <v>9197.62551833333</v>
       </c>
       <c r="F46" s="12" t="n">
         <f aca="false">E46*$B$6/12</f>
-        <v>200.684477328182</v>
+        <v>227.947819096028</v>
       </c>
       <c r="G46" s="12" t="n">
         <f aca="false">MIN(E46+F46,MAX(D46-K46,0))</f>
-        <v>799.407599198322</v>
+        <v>847.363157873335</v>
       </c>
       <c r="H46" s="12" t="n">
         <f aca="false">E46+F46-G46</f>
-        <v>7498.83480663754</v>
+        <v>8578.21017955603</v>
       </c>
       <c r="I46" s="12" t="n">
         <f aca="false">M45</f>
-        <v>5182.87151448</v>
+        <v>5288.1048</v>
       </c>
       <c r="J46" s="12" t="n">
         <f aca="false">I46*$B$8/12</f>
-        <v>75.540352323546</v>
+        <v>77.07412746</v>
       </c>
       <c r="K46" s="12" t="n">
         <f aca="false">MIN(I46+J46,J46+$B$9*I46)</f>
-        <v>127.369067468346</v>
+        <v>129.95517546</v>
       </c>
       <c r="L46" s="12" t="n">
         <f aca="false">MIN(I46+J46,MAX(D46-G46,0))</f>
-        <v>127.369067468346</v>
+        <v>129.95517546</v>
       </c>
       <c r="M46" s="12" t="n">
         <f aca="false">I46+J46-L46</f>
-        <v>5131.0427993352</v>
+        <v>5235.223752</v>
       </c>
       <c r="N46" s="12" t="n">
         <f aca="false">P45</f>
@@ -5547,55 +5399,55 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="34" t="n">
-        <v>46447</v>
+        <v>46388</v>
       </c>
       <c r="B47" s="21" t="n">
-        <f aca="false">IF(A47&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A47&gt;$B$38,$B$39,0)+IF(A47&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A47&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A47&gt;$B$40,$B$41,0)+IF(A47&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>977.318333333335</v>
       </c>
       <c r="C47" s="12" t="n">
-        <f aca="false">IF(A47=$B$37,$B$26-$B$29,0)-IF(A47=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A47=$B$33,$B$35*$B$34,0)+0</f>
-        <v>51578.8091666667</v>
+        <f aca="false">IF(A47=$B$39,$B$26-$B$29,0)-IF(A47=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A47=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
       </c>
       <c r="D47" s="12" t="n">
         <f aca="false">B47+C47</f>
-        <v>54095.8445833333</v>
+        <v>977.318333333335</v>
       </c>
       <c r="E47" s="12" t="n">
         <f aca="false">H46</f>
-        <v>7498.83480663754</v>
+        <v>8578.21017955603</v>
       </c>
       <c r="F47" s="12" t="n">
         <f aca="false">E47*$B$6/12</f>
-        <v>185.8461226245</v>
+        <v>212.59664228333</v>
       </c>
       <c r="G47" s="12" t="n">
         <f aca="false">MIN(E47+F47,MAX(D47-K47,0))</f>
-        <v>7684.68092926204</v>
+        <v>848.662709627935</v>
       </c>
       <c r="H47" s="12" t="n">
         <f aca="false">E47+F47-G47</f>
-        <v>0</v>
+        <v>7942.14411221142</v>
       </c>
       <c r="I47" s="12" t="n">
         <f aca="false">M46</f>
-        <v>5131.0427993352</v>
+        <v>5235.223752</v>
       </c>
       <c r="J47" s="12" t="n">
         <f aca="false">I47*$B$8/12</f>
-        <v>74.7849488003106</v>
+        <v>76.3033861854</v>
       </c>
       <c r="K47" s="12" t="n">
         <f aca="false">MIN(I47+J47,J47+$B$9*I47)</f>
-        <v>126.095376793663</v>
+        <v>128.6556237054</v>
       </c>
       <c r="L47" s="12" t="n">
         <f aca="false">MIN(I47+J47,MAX(D47-G47,0))</f>
-        <v>5205.82774813551</v>
+        <v>128.6556237054</v>
       </c>
       <c r="M47" s="12" t="n">
         <f aca="false">I47+J47-L47</f>
-        <v>0</v>
+        <v>5182.87151448</v>
       </c>
       <c r="N47" s="12" t="n">
         <f aca="false">P46</f>
@@ -5603,27 +5455,27 @@
       </c>
       <c r="O47" s="12" t="n">
         <f aca="false">MIN(D47-G47-L47,MAX($B$15-$B$18-N47,0))</f>
-        <v>41205.3359059358</v>
+        <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
         <f aca="false">N47+O47</f>
-        <v>53286.3359059358</v>
+        <v>12081</v>
       </c>
       <c r="Q47" s="5" t="n">
         <f aca="false">IF(H47&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="5" t="n">
         <f aca="false">IF(M47&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="5" t="n">
         <f aca="false">IF(AND(Q47=1,R47=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" s="5" t="n">
         <f aca="false">IF(P47&gt;=$B$20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" s="5" t="n">
         <f aca="false">IF(P47+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -5635,88 +5487,88 @@
       </c>
       <c r="W47" s="12" t="n">
         <f aca="false">P47+$B$18</f>
-        <v>69547.0859059358</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="34" t="n">
-        <v>46478</v>
+        <v>46419</v>
       </c>
       <c r="B48" s="21" t="n">
-        <f aca="false">IF(A48&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A48&gt;$B$38,$B$39,0)+IF(A48&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A48&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A48&gt;$B$40,$B$41,0)+IF(A48&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>977.318333333335</v>
       </c>
       <c r="C48" s="12" t="n">
-        <f aca="false">IF(A48=$B$37,$B$26-$B$29,0)-IF(A48=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A48=$B$33,$B$35*$B$34,0)+0</f>
-        <v>-3983.25</v>
+        <f aca="false">IF(A48=$B$39,$B$26-$B$29,0)-IF(A48=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A48=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
       </c>
       <c r="D48" s="12" t="n">
         <f aca="false">B48+C48</f>
-        <v>-1466.21458333333</v>
+        <v>977.318333333335</v>
       </c>
       <c r="E48" s="12" t="n">
         <f aca="false">H47</f>
-        <v>0</v>
+        <v>7942.14411221142</v>
       </c>
       <c r="F48" s="12" t="n">
         <f aca="false">E48*$B$6/12</f>
-        <v>0</v>
+        <v>196.832804914306</v>
       </c>
       <c r="G48" s="12" t="n">
         <f aca="false">MIN(E48+F48,MAX(D48-K48,0))</f>
-        <v>0</v>
+        <v>849.949265864989</v>
       </c>
       <c r="H48" s="12" t="n">
         <f aca="false">E48+F48-G48</f>
-        <v>0</v>
+        <v>7289.02765126074</v>
       </c>
       <c r="I48" s="12" t="n">
         <f aca="false">M47</f>
-        <v>0</v>
+        <v>5182.87151448</v>
       </c>
       <c r="J48" s="12" t="n">
         <f aca="false">I48*$B$8/12</f>
-        <v>0</v>
+        <v>75.540352323546</v>
       </c>
       <c r="K48" s="12" t="n">
         <f aca="false">MIN(I48+J48,J48+$B$9*I48)</f>
-        <v>0</v>
+        <v>127.369067468346</v>
       </c>
       <c r="L48" s="12" t="n">
         <f aca="false">MIN(I48+J48,MAX(D48-G48,0))</f>
-        <v>0</v>
+        <v>127.369067468346</v>
       </c>
       <c r="M48" s="12" t="n">
         <f aca="false">I48+J48-L48</f>
-        <v>0</v>
+        <v>5131.0427993352</v>
       </c>
       <c r="N48" s="12" t="n">
         <f aca="false">P47</f>
-        <v>53286.3359059358</v>
+        <v>12081</v>
       </c>
       <c r="O48" s="12" t="n">
         <f aca="false">MIN(D48-G48-L48,MAX($B$15-$B$18-N48,0))</f>
-        <v>-1466.21458333333</v>
+        <v>0</v>
       </c>
       <c r="P48" s="12" t="n">
         <f aca="false">N48+O48</f>
-        <v>51820.1213226025</v>
+        <v>12081</v>
       </c>
       <c r="Q48" s="5" t="n">
         <f aca="false">IF(H48&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" s="5" t="n">
         <f aca="false">IF(M48&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" s="5" t="n">
         <f aca="false">IF(AND(Q48=1,R48=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" s="5" t="n">
         <f aca="false">IF(P48&gt;=$B$20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="5" t="n">
         <f aca="false">IF(P48+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -5728,36 +5580,36 @@
       </c>
       <c r="W48" s="12" t="n">
         <f aca="false">P48+$B$18</f>
-        <v>68080.8713226024</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="34" t="n">
-        <v>46508</v>
+        <v>46447</v>
       </c>
       <c r="B49" s="21" t="n">
-        <f aca="false">IF(A49&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A49&gt;$B$38,$B$39,0)+IF(A49&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A49&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A49&gt;$B$40,$B$41,0)+IF(A49&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C49" s="12" t="n">
-        <f aca="false">IF(A49=$B$37,$B$26-$B$29,0)-IF(A49=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A49=$B$33,$B$35*$B$34,0)+0</f>
-        <v>0</v>
+        <f aca="false">IF(A49=$B$39,$B$26-$B$29,0)-IF(A49=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A49=$B$35,$B$37*$B$36,0)+0</f>
+        <v>51581.8416666667</v>
       </c>
       <c r="D49" s="12" t="n">
         <f aca="false">B49+C49</f>
-        <v>2517.03541666667</v>
+        <v>54150.935</v>
       </c>
       <c r="E49" s="12" t="n">
         <f aca="false">H48</f>
-        <v>0</v>
+        <v>7289.02765126074</v>
       </c>
       <c r="F49" s="12" t="n">
         <f aca="false">E49*$B$6/12</f>
-        <v>0</v>
+        <v>180.646401957079</v>
       </c>
       <c r="G49" s="12" t="n">
         <f aca="false">MIN(E49+F49,MAX(D49-K49,0))</f>
-        <v>0</v>
+        <v>7469.67405321782</v>
       </c>
       <c r="H49" s="12" t="n">
         <f aca="false">E49+F49-G49</f>
@@ -5765,19 +5617,19 @@
       </c>
       <c r="I49" s="12" t="n">
         <f aca="false">M48</f>
-        <v>0</v>
+        <v>5131.0427993352</v>
       </c>
       <c r="J49" s="12" t="n">
         <f aca="false">I49*$B$8/12</f>
-        <v>0</v>
+        <v>74.7849488003106</v>
       </c>
       <c r="K49" s="12" t="n">
         <f aca="false">MIN(I49+J49,J49+$B$9*I49)</f>
-        <v>0</v>
+        <v>126.095376793663</v>
       </c>
       <c r="L49" s="12" t="n">
         <f aca="false">MIN(I49+J49,MAX(D49-G49,0))</f>
-        <v>0</v>
+        <v>5205.82774813551</v>
       </c>
       <c r="M49" s="12" t="n">
         <f aca="false">I49+J49-L49</f>
@@ -5785,15 +5637,15 @@
       </c>
       <c r="N49" s="12" t="n">
         <f aca="false">P48</f>
-        <v>51820.1213226025</v>
+        <v>12081</v>
       </c>
       <c r="O49" s="12" t="n">
         <f aca="false">MIN(D49-G49-L49,MAX($B$15-$B$18-N49,0))</f>
-        <v>2517.03541666667</v>
+        <v>41475.4331986467</v>
       </c>
       <c r="P49" s="12" t="n">
         <f aca="false">N49+O49</f>
-        <v>54337.1567392691</v>
+        <v>53556.4331986467</v>
       </c>
       <c r="Q49" s="5" t="n">
         <f aca="false">IF(H49&lt;=0.005,1,0)</f>
@@ -5821,24 +5673,24 @@
       </c>
       <c r="W49" s="12" t="n">
         <f aca="false">P49+$B$18</f>
-        <v>70597.9067392691</v>
+        <v>69817.1831986467</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="34" t="n">
-        <v>46539</v>
+        <v>46478</v>
       </c>
       <c r="B50" s="21" t="n">
-        <f aca="false">IF(A50&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A50&gt;$B$38,$B$39,0)+IF(A50&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A50&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A50&gt;$B$40,$B$41,0)+IF(A50&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C50" s="12" t="n">
-        <f aca="false">IF(A50=$B$37,$B$26-$B$29,0)-IF(A50=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A50=$B$33,$B$35*$B$34,0)+0</f>
-        <v>0</v>
+        <f aca="false">IF(A50=$B$39,$B$26-$B$29,0)-IF(A50=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A50=$B$35,$B$37*$B$36,0)+0</f>
+        <v>-3983.25</v>
       </c>
       <c r="D50" s="12" t="n">
         <f aca="false">B50+C50</f>
-        <v>2517.03541666667</v>
+        <v>-1414.15666666667</v>
       </c>
       <c r="E50" s="12" t="n">
         <f aca="false">H49</f>
@@ -5878,15 +5730,15 @@
       </c>
       <c r="N50" s="12" t="n">
         <f aca="false">P49</f>
-        <v>54337.1567392691</v>
+        <v>53556.4331986467</v>
       </c>
       <c r="O50" s="12" t="n">
         <f aca="false">MIN(D50-G50-L50,MAX($B$15-$B$18-N50,0))</f>
-        <v>2517.03541666667</v>
+        <v>-1414.15666666667</v>
       </c>
       <c r="P50" s="12" t="n">
         <f aca="false">N50+O50</f>
-        <v>56854.1921559358</v>
+        <v>52142.27653198</v>
       </c>
       <c r="Q50" s="5" t="n">
         <f aca="false">IF(H50&lt;=0.005,1,0)</f>
@@ -5914,24 +5766,24 @@
       </c>
       <c r="W50" s="12" t="n">
         <f aca="false">P50+$B$18</f>
-        <v>73114.9421559358</v>
+        <v>68403.02653198</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="34" t="n">
-        <v>46569</v>
+        <v>46508</v>
       </c>
       <c r="B51" s="21" t="n">
-        <f aca="false">IF(A51&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A51&gt;$B$38,$B$39,0)+IF(A51&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A51&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A51&gt;$B$40,$B$41,0)+IF(A51&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C51" s="12" t="n">
-        <f aca="false">IF(A51=$B$37,$B$26-$B$29,0)-IF(A51=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A51=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A51=$B$39,$B$26-$B$29,0)-IF(A51=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A51=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D51" s="12" t="n">
         <f aca="false">B51+C51</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E51" s="12" t="n">
         <f aca="false">H50</f>
@@ -5971,15 +5823,15 @@
       </c>
       <c r="N51" s="12" t="n">
         <f aca="false">P50</f>
-        <v>56854.1921559358</v>
+        <v>52142.27653198</v>
       </c>
       <c r="O51" s="12" t="n">
         <f aca="false">MIN(D51-G51-L51,MAX($B$15-$B$18-N51,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P51" s="12" t="n">
         <f aca="false">N51+O51</f>
-        <v>59371.2275726024</v>
+        <v>54711.3698653134</v>
       </c>
       <c r="Q51" s="5" t="n">
         <f aca="false">IF(H51&lt;=0.005,1,0)</f>
@@ -6007,24 +5859,24 @@
       </c>
       <c r="W51" s="12" t="n">
         <f aca="false">P51+$B$18</f>
-        <v>75631.9775726025</v>
+        <v>70972.1198653134</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="34" t="n">
-        <v>46600</v>
+        <v>46539</v>
       </c>
       <c r="B52" s="21" t="n">
-        <f aca="false">IF(A52&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A52&gt;$B$38,$B$39,0)+IF(A52&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A52&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A52&gt;$B$40,$B$41,0)+IF(A52&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C52" s="12" t="n">
-        <f aca="false">IF(A52=$B$37,$B$26-$B$29,0)-IF(A52=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A52=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A52=$B$39,$B$26-$B$29,0)-IF(A52=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A52=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D52" s="12" t="n">
         <f aca="false">B52+C52</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E52" s="12" t="n">
         <f aca="false">H51</f>
@@ -6064,15 +5916,15 @@
       </c>
       <c r="N52" s="12" t="n">
         <f aca="false">P51</f>
-        <v>59371.2275726024</v>
+        <v>54711.3698653134</v>
       </c>
       <c r="O52" s="12" t="n">
         <f aca="false">MIN(D52-G52-L52,MAX($B$15-$B$18-N52,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P52" s="12" t="n">
         <f aca="false">N52+O52</f>
-        <v>61888.2629892691</v>
+        <v>57280.4631986467</v>
       </c>
       <c r="Q52" s="5" t="n">
         <f aca="false">IF(H52&lt;=0.005,1,0)</f>
@@ -6100,24 +5952,24 @@
       </c>
       <c r="W52" s="12" t="n">
         <f aca="false">P52+$B$18</f>
-        <v>78149.0129892691</v>
+        <v>73541.2131986467</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="34" t="n">
-        <v>46631</v>
+        <v>46569</v>
       </c>
       <c r="B53" s="21" t="n">
-        <f aca="false">IF(A53&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A53&gt;$B$38,$B$39,0)+IF(A53&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A53&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A53&gt;$B$40,$B$41,0)+IF(A53&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C53" s="12" t="n">
-        <f aca="false">IF(A53=$B$37,$B$26-$B$29,0)-IF(A53=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A53=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A53=$B$39,$B$26-$B$29,0)-IF(A53=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A53=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D53" s="12" t="n">
         <f aca="false">B53+C53</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E53" s="12" t="n">
         <f aca="false">H52</f>
@@ -6157,15 +6009,15 @@
       </c>
       <c r="N53" s="12" t="n">
         <f aca="false">P52</f>
-        <v>61888.2629892691</v>
+        <v>57280.4631986467</v>
       </c>
       <c r="O53" s="12" t="n">
         <f aca="false">MIN(D53-G53-L53,MAX($B$15-$B$18-N53,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P53" s="12" t="n">
         <f aca="false">N53+O53</f>
-        <v>64405.2984059358</v>
+        <v>59849.55653198</v>
       </c>
       <c r="Q53" s="5" t="n">
         <f aca="false">IF(H53&lt;=0.005,1,0)</f>
@@ -6193,24 +6045,24 @@
       </c>
       <c r="W53" s="12" t="n">
         <f aca="false">P53+$B$18</f>
-        <v>80666.0484059358</v>
+        <v>76110.30653198</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="34" t="n">
-        <v>46661</v>
+        <v>46600</v>
       </c>
       <c r="B54" s="21" t="n">
-        <f aca="false">IF(A54&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A54&gt;$B$38,$B$39,0)+IF(A54&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A54&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A54&gt;$B$40,$B$41,0)+IF(A54&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C54" s="12" t="n">
-        <f aca="false">IF(A54=$B$37,$B$26-$B$29,0)-IF(A54=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A54=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A54=$B$39,$B$26-$B$29,0)-IF(A54=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A54=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D54" s="12" t="n">
         <f aca="false">B54+C54</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E54" s="12" t="n">
         <f aca="false">H53</f>
@@ -6250,15 +6102,15 @@
       </c>
       <c r="N54" s="12" t="n">
         <f aca="false">P53</f>
-        <v>64405.2984059358</v>
+        <v>59849.55653198</v>
       </c>
       <c r="O54" s="12" t="n">
         <f aca="false">MIN(D54-G54-L54,MAX($B$15-$B$18-N54,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P54" s="12" t="n">
         <f aca="false">N54+O54</f>
-        <v>66922.3338226025</v>
+        <v>62418.6498653134</v>
       </c>
       <c r="Q54" s="5" t="n">
         <f aca="false">IF(H54&lt;=0.005,1,0)</f>
@@ -6286,24 +6138,24 @@
       </c>
       <c r="W54" s="12" t="n">
         <f aca="false">P54+$B$18</f>
-        <v>83183.0838226025</v>
+        <v>78679.3998653134</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="34" t="n">
-        <v>46692</v>
+        <v>46631</v>
       </c>
       <c r="B55" s="21" t="n">
-        <f aca="false">IF(A55&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A55&gt;$B$38,$B$39,0)+IF(A55&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A55&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A55&gt;$B$40,$B$41,0)+IF(A55&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C55" s="12" t="n">
-        <f aca="false">IF(A55=$B$37,$B$26-$B$29,0)-IF(A55=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A55=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A55=$B$39,$B$26-$B$29,0)-IF(A55=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A55=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D55" s="12" t="n">
         <f aca="false">B55+C55</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E55" s="12" t="n">
         <f aca="false">H54</f>
@@ -6343,15 +6195,15 @@
       </c>
       <c r="N55" s="12" t="n">
         <f aca="false">P54</f>
-        <v>66922.3338226025</v>
+        <v>62418.6498653134</v>
       </c>
       <c r="O55" s="12" t="n">
         <f aca="false">MIN(D55-G55-L55,MAX($B$15-$B$18-N55,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P55" s="12" t="n">
         <f aca="false">N55+O55</f>
-        <v>69439.3692392691</v>
+        <v>64987.7431986467</v>
       </c>
       <c r="Q55" s="5" t="n">
         <f aca="false">IF(H55&lt;=0.005,1,0)</f>
@@ -6379,24 +6231,24 @@
       </c>
       <c r="W55" s="12" t="n">
         <f aca="false">P55+$B$18</f>
-        <v>85700.1192392691</v>
+        <v>81248.4931986467</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="34" t="n">
-        <v>46722</v>
+        <v>46661</v>
       </c>
       <c r="B56" s="21" t="n">
-        <f aca="false">IF(A56&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A56&gt;$B$38,$B$39,0)+IF(A56&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A56&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A56&gt;$B$40,$B$41,0)+IF(A56&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C56" s="12" t="n">
-        <f aca="false">IF(A56=$B$37,$B$26-$B$29,0)-IF(A56=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A56=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A56=$B$39,$B$26-$B$29,0)-IF(A56=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A56=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D56" s="12" t="n">
         <f aca="false">B56+C56</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E56" s="12" t="n">
         <f aca="false">H55</f>
@@ -6436,15 +6288,15 @@
       </c>
       <c r="N56" s="12" t="n">
         <f aca="false">P55</f>
-        <v>69439.3692392691</v>
+        <v>64987.7431986467</v>
       </c>
       <c r="O56" s="12" t="n">
         <f aca="false">MIN(D56-G56-L56,MAX($B$15-$B$18-N56,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P56" s="12" t="n">
         <f aca="false">N56+O56</f>
-        <v>71956.4046559358</v>
+        <v>67556.83653198</v>
       </c>
       <c r="Q56" s="5" t="n">
         <f aca="false">IF(H56&lt;=0.005,1,0)</f>
@@ -6472,24 +6324,24 @@
       </c>
       <c r="W56" s="12" t="n">
         <f aca="false">P56+$B$18</f>
-        <v>88217.1546559358</v>
+        <v>83817.58653198</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="34" t="n">
-        <v>46753</v>
+        <v>46692</v>
       </c>
       <c r="B57" s="21" t="n">
-        <f aca="false">IF(A57&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A57&gt;$B$38,$B$39,0)+IF(A57&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A57&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A57&gt;$B$40,$B$41,0)+IF(A57&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C57" s="12" t="n">
-        <f aca="false">IF(A57=$B$37,$B$26-$B$29,0)-IF(A57=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A57=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A57=$B$39,$B$26-$B$29,0)-IF(A57=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A57=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D57" s="12" t="n">
         <f aca="false">B57+C57</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E57" s="12" t="n">
         <f aca="false">H56</f>
@@ -6529,15 +6381,15 @@
       </c>
       <c r="N57" s="12" t="n">
         <f aca="false">P56</f>
-        <v>71956.4046559358</v>
+        <v>67556.83653198</v>
       </c>
       <c r="O57" s="12" t="n">
         <f aca="false">MIN(D57-G57-L57,MAX($B$15-$B$18-N57,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P57" s="12" t="n">
         <f aca="false">N57+O57</f>
-        <v>74473.4400726025</v>
+        <v>70125.9298653134</v>
       </c>
       <c r="Q57" s="5" t="n">
         <f aca="false">IF(H57&lt;=0.005,1,0)</f>
@@ -6565,24 +6417,24 @@
       </c>
       <c r="W57" s="12" t="n">
         <f aca="false">P57+$B$18</f>
-        <v>90734.1900726025</v>
+        <v>86386.6798653134</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="34" t="n">
-        <v>46784</v>
+        <v>46722</v>
       </c>
       <c r="B58" s="21" t="n">
-        <f aca="false">IF(A58&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A58&gt;$B$38,$B$39,0)+IF(A58&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A58&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A58&gt;$B$40,$B$41,0)+IF(A58&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C58" s="12" t="n">
-        <f aca="false">IF(A58=$B$37,$B$26-$B$29,0)-IF(A58=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A58=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A58=$B$39,$B$26-$B$29,0)-IF(A58=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A58=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D58" s="12" t="n">
         <f aca="false">B58+C58</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E58" s="12" t="n">
         <f aca="false">H57</f>
@@ -6622,15 +6474,15 @@
       </c>
       <c r="N58" s="12" t="n">
         <f aca="false">P57</f>
-        <v>74473.4400726025</v>
+        <v>70125.9298653134</v>
       </c>
       <c r="O58" s="12" t="n">
         <f aca="false">MIN(D58-G58-L58,MAX($B$15-$B$18-N58,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P58" s="12" t="n">
         <f aca="false">N58+O58</f>
-        <v>76990.4754892691</v>
+        <v>72695.0231986467</v>
       </c>
       <c r="Q58" s="5" t="n">
         <f aca="false">IF(H58&lt;=0.005,1,0)</f>
@@ -6658,24 +6510,24 @@
       </c>
       <c r="W58" s="12" t="n">
         <f aca="false">P58+$B$18</f>
-        <v>93251.2254892691</v>
+        <v>88955.7731986467</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="34" t="n">
-        <v>46813</v>
+        <v>46753</v>
       </c>
       <c r="B59" s="21" t="n">
-        <f aca="false">IF(A59&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A59&gt;$B$38,$B$39,0)+IF(A59&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A59&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A59&gt;$B$40,$B$41,0)+IF(A59&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C59" s="12" t="n">
-        <f aca="false">IF(A59=$B$37,$B$26-$B$29,0)-IF(A59=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A59=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A59=$B$39,$B$26-$B$29,0)-IF(A59=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A59=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D59" s="12" t="n">
         <f aca="false">B59+C59</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E59" s="12" t="n">
         <f aca="false">H58</f>
@@ -6715,15 +6567,15 @@
       </c>
       <c r="N59" s="12" t="n">
         <f aca="false">P58</f>
-        <v>76990.4754892691</v>
+        <v>72695.0231986467</v>
       </c>
       <c r="O59" s="12" t="n">
         <f aca="false">MIN(D59-G59-L59,MAX($B$15-$B$18-N59,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P59" s="12" t="n">
         <f aca="false">N59+O59</f>
-        <v>79507.5109059358</v>
+        <v>75264.1165319801</v>
       </c>
       <c r="Q59" s="5" t="n">
         <f aca="false">IF(H59&lt;=0.005,1,0)</f>
@@ -6751,24 +6603,24 @@
       </c>
       <c r="W59" s="12" t="n">
         <f aca="false">P59+$B$18</f>
-        <v>95768.2609059358</v>
+        <v>91524.8665319801</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="34" t="n">
-        <v>46844</v>
+        <v>46784</v>
       </c>
       <c r="B60" s="21" t="n">
-        <f aca="false">IF(A60&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A60&gt;$B$38,$B$39,0)+IF(A60&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A60&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A60&gt;$B$40,$B$41,0)+IF(A60&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C60" s="12" t="n">
-        <f aca="false">IF(A60=$B$37,$B$26-$B$29,0)-IF(A60=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A60=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A60=$B$39,$B$26-$B$29,0)-IF(A60=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A60=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D60" s="12" t="n">
         <f aca="false">B60+C60</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E60" s="12" t="n">
         <f aca="false">H59</f>
@@ -6808,15 +6660,15 @@
       </c>
       <c r="N60" s="12" t="n">
         <f aca="false">P59</f>
-        <v>79507.5109059358</v>
+        <v>75264.1165319801</v>
       </c>
       <c r="O60" s="12" t="n">
         <f aca="false">MIN(D60-G60-L60,MAX($B$15-$B$18-N60,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P60" s="12" t="n">
         <f aca="false">N60+O60</f>
-        <v>82024.5463226024</v>
+        <v>77833.2098653134</v>
       </c>
       <c r="Q60" s="5" t="n">
         <f aca="false">IF(H60&lt;=0.005,1,0)</f>
@@ -6844,24 +6696,24 @@
       </c>
       <c r="W60" s="12" t="n">
         <f aca="false">P60+$B$18</f>
-        <v>98285.2963226024</v>
+        <v>94093.9598653134</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="34" t="n">
-        <v>46874</v>
+        <v>46813</v>
       </c>
       <c r="B61" s="21" t="n">
-        <f aca="false">IF(A61&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A61&gt;$B$38,$B$39,0)+IF(A61&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A61&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A61&gt;$B$40,$B$41,0)+IF(A61&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C61" s="12" t="n">
-        <f aca="false">IF(A61=$B$37,$B$26-$B$29,0)-IF(A61=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A61=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A61=$B$39,$B$26-$B$29,0)-IF(A61=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A61=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D61" s="12" t="n">
         <f aca="false">B61+C61</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E61" s="12" t="n">
         <f aca="false">H60</f>
@@ -6901,15 +6753,15 @@
       </c>
       <c r="N61" s="12" t="n">
         <f aca="false">P60</f>
-        <v>82024.5463226024</v>
+        <v>77833.2098653134</v>
       </c>
       <c r="O61" s="12" t="n">
         <f aca="false">MIN(D61-G61-L61,MAX($B$15-$B$18-N61,0))</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P61" s="12" t="n">
         <f aca="false">N61+O61</f>
-        <v>84541.5817392691</v>
+        <v>80402.3031986467</v>
       </c>
       <c r="Q61" s="5" t="n">
         <f aca="false">IF(H61&lt;=0.005,1,0)</f>
@@ -6937,24 +6789,24 @@
       </c>
       <c r="W61" s="12" t="n">
         <f aca="false">P61+$B$18</f>
-        <v>100802.331739269</v>
+        <v>96663.0531986467</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="34" t="n">
-        <v>46905</v>
+        <v>46844</v>
       </c>
       <c r="B62" s="21" t="n">
-        <f aca="false">IF(A62&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A62&gt;$B$38,$B$39,0)+IF(A62&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A62&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A62&gt;$B$40,$B$41,0)+IF(A62&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C62" s="12" t="n">
-        <f aca="false">IF(A62=$B$37,$B$26-$B$29,0)-IF(A62=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A62=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A62=$B$39,$B$26-$B$29,0)-IF(A62=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A62=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D62" s="12" t="n">
         <f aca="false">B62+C62</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E62" s="12" t="n">
         <f aca="false">H61</f>
@@ -6994,15 +6846,15 @@
       </c>
       <c r="N62" s="12" t="n">
         <f aca="false">P61</f>
-        <v>84541.5817392691</v>
+        <v>80402.3031986467</v>
       </c>
       <c r="O62" s="12" t="n">
         <f aca="false">MIN(D62-G62-L62,MAX($B$15-$B$18-N62,0))</f>
-        <v>39.6682607308903</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P62" s="12" t="n">
         <f aca="false">N62+O62</f>
-        <v>84581.25</v>
+        <v>82971.3965319801</v>
       </c>
       <c r="Q62" s="5" t="n">
         <f aca="false">IF(H62&lt;=0.005,1,0)</f>
@@ -7022,32 +6874,32 @@
       </c>
       <c r="U62" s="5" t="n">
         <f aca="false">IF(P62+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V62" s="12" t="n">
         <f aca="false">MAX(D62-G62-L62,0)-MAX(O62,0)</f>
-        <v>2477.36715593578</v>
+        <v>0</v>
       </c>
       <c r="W62" s="12" t="n">
         <f aca="false">P62+$B$18</f>
-        <v>100842</v>
+        <v>99232.1465319801</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="34" t="n">
-        <v>46935</v>
+        <v>46874</v>
       </c>
       <c r="B63" s="21" t="n">
-        <f aca="false">IF(A63&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A63&gt;$B$38,$B$39,0)+IF(A63&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A63&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A63&gt;$B$40,$B$41,0)+IF(A63&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C63" s="12" t="n">
-        <f aca="false">IF(A63=$B$37,$B$26-$B$29,0)-IF(A63=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A63=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A63=$B$39,$B$26-$B$29,0)-IF(A63=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A63=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D63" s="12" t="n">
         <f aca="false">B63+C63</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E63" s="12" t="n">
         <f aca="false">H62</f>
@@ -7087,11 +6939,11 @@
       </c>
       <c r="N63" s="12" t="n">
         <f aca="false">P62</f>
-        <v>84581.25</v>
+        <v>82971.3965319801</v>
       </c>
       <c r="O63" s="12" t="n">
         <f aca="false">MIN(D63-G63-L63,MAX($B$15-$B$18-N63,0))</f>
-        <v>0</v>
+        <v>1609.85346801994</v>
       </c>
       <c r="P63" s="12" t="n">
         <f aca="false">N63+O63</f>
@@ -7119,7 +6971,7 @@
       </c>
       <c r="V63" s="12" t="n">
         <f aca="false">MAX(D63-G63-L63,0)-MAX(O63,0)</f>
-        <v>2517.03541666667</v>
+        <v>959.239865313398</v>
       </c>
       <c r="W63" s="12" t="n">
         <f aca="false">P63+$B$18</f>
@@ -7128,19 +6980,19 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="34" t="n">
-        <v>46966</v>
+        <v>46905</v>
       </c>
       <c r="B64" s="21" t="n">
-        <f aca="false">IF(A64&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A64&gt;$B$38,$B$39,0)+IF(A64&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A64&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A64&gt;$B$40,$B$41,0)+IF(A64&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C64" s="12" t="n">
-        <f aca="false">IF(A64=$B$37,$B$26-$B$29,0)-IF(A64=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A64=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A64=$B$39,$B$26-$B$29,0)-IF(A64=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A64=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D64" s="12" t="n">
         <f aca="false">B64+C64</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E64" s="12" t="n">
         <f aca="false">H63</f>
@@ -7212,7 +7064,7 @@
       </c>
       <c r="V64" s="12" t="n">
         <f aca="false">MAX(D64-G64-L64,0)-MAX(O64,0)</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W64" s="12" t="n">
         <f aca="false">P64+$B$18</f>
@@ -7221,19 +7073,19 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="34" t="n">
-        <v>46997</v>
+        <v>46935</v>
       </c>
       <c r="B65" s="21" t="n">
-        <f aca="false">IF(A65&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A65&gt;$B$38,$B$39,0)+IF(A65&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A65&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A65&gt;$B$40,$B$41,0)+IF(A65&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C65" s="12" t="n">
-        <f aca="false">IF(A65=$B$37,$B$26-$B$29,0)-IF(A65=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A65=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A65=$B$39,$B$26-$B$29,0)-IF(A65=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A65=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D65" s="12" t="n">
         <f aca="false">B65+C65</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E65" s="12" t="n">
         <f aca="false">H64</f>
@@ -7305,7 +7157,7 @@
       </c>
       <c r="V65" s="12" t="n">
         <f aca="false">MAX(D65-G65-L65,0)-MAX(O65,0)</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W65" s="12" t="n">
         <f aca="false">P65+$B$18</f>
@@ -7314,19 +7166,19 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="34" t="n">
-        <v>47027</v>
+        <v>46966</v>
       </c>
       <c r="B66" s="21" t="n">
-        <f aca="false">IF(A66&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A66&gt;$B$38,$B$39,0)+IF(A66&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A66&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A66&gt;$B$40,$B$41,0)+IF(A66&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C66" s="12" t="n">
-        <f aca="false">IF(A66=$B$37,$B$26-$B$29,0)-IF(A66=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A66=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A66=$B$39,$B$26-$B$29,0)-IF(A66=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A66=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D66" s="12" t="n">
         <f aca="false">B66+C66</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E66" s="12" t="n">
         <f aca="false">H65</f>
@@ -7398,7 +7250,7 @@
       </c>
       <c r="V66" s="12" t="n">
         <f aca="false">MAX(D66-G66-L66,0)-MAX(O66,0)</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W66" s="12" t="n">
         <f aca="false">P66+$B$18</f>
@@ -7407,19 +7259,19 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="34" t="n">
-        <v>47058</v>
+        <v>46997</v>
       </c>
       <c r="B67" s="21" t="n">
-        <f aca="false">IF(A67&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A67&gt;$B$38,$B$39,0)+IF(A67&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A67&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A67&gt;$B$40,$B$41,0)+IF(A67&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C67" s="12" t="n">
-        <f aca="false">IF(A67=$B$37,$B$26-$B$29,0)-IF(A67=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A67=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A67=$B$39,$B$26-$B$29,0)-IF(A67=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A67=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D67" s="12" t="n">
         <f aca="false">B67+C67</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E67" s="12" t="n">
         <f aca="false">H66</f>
@@ -7491,7 +7343,7 @@
       </c>
       <c r="V67" s="12" t="n">
         <f aca="false">MAX(D67-G67-L67,0)-MAX(O67,0)</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W67" s="12" t="n">
         <f aca="false">P67+$B$18</f>
@@ -7500,19 +7352,19 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="34" t="n">
-        <v>47088</v>
+        <v>47027</v>
       </c>
       <c r="B68" s="21" t="n">
-        <f aca="false">IF(A68&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A68&gt;$B$38,$B$39,0)+IF(A68&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A68&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A68&gt;$B$40,$B$41,0)+IF(A68&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C68" s="12" t="n">
-        <f aca="false">IF(A68=$B$37,$B$26-$B$29,0)-IF(A68=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A68=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A68=$B$39,$B$26-$B$29,0)-IF(A68=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A68=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D68" s="12" t="n">
         <f aca="false">B68+C68</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E68" s="12" t="n">
         <f aca="false">H67</f>
@@ -7584,7 +7436,7 @@
       </c>
       <c r="V68" s="12" t="n">
         <f aca="false">MAX(D68-G68-L68,0)-MAX(O68,0)</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W68" s="12" t="n">
         <f aca="false">P68+$B$18</f>
@@ -7593,19 +7445,19 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="34" t="n">
-        <v>47119</v>
+        <v>47058</v>
       </c>
       <c r="B69" s="21" t="n">
-        <f aca="false">IF(A69&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A69&gt;$B$38,$B$39,0)+IF(A69&gt;=$B$33,$B$35,0)</f>
-        <v>2517.03541666667</v>
+        <f aca="false">IF(A69&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A69&gt;$B$40,$B$41,0)+IF(A69&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C69" s="12" t="n">
-        <f aca="false">IF(A69=$B$37,$B$26-$B$29,0)-IF(A69=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A69=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A69=$B$39,$B$26-$B$29,0)-IF(A69=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A69=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D69" s="12" t="n">
         <f aca="false">B69+C69</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E69" s="12" t="n">
         <f aca="false">H68</f>
@@ -7677,7 +7529,7 @@
       </c>
       <c r="V69" s="12" t="n">
         <f aca="false">MAX(D69-G69-L69,0)-MAX(O69,0)</f>
-        <v>2517.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W69" s="12" t="n">
         <f aca="false">P69+$B$18</f>
@@ -7686,19 +7538,19 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="34" t="n">
-        <v>47150</v>
+        <v>47088</v>
       </c>
       <c r="B70" s="21" t="n">
-        <f aca="false">IF(A70&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A70&gt;$B$38,$B$39,0)+IF(A70&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A70&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A70&gt;$B$40,$B$41,0)+IF(A70&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C70" s="12" t="n">
-        <f aca="false">IF(A70=$B$37,$B$26-$B$29,0)-IF(A70=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A70=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A70=$B$39,$B$26-$B$29,0)-IF(A70=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A70=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D70" s="12" t="n">
         <f aca="false">B70+C70</f>
-        <v>2859.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E70" s="12" t="n">
         <f aca="false">H69</f>
@@ -7770,7 +7622,7 @@
       </c>
       <c r="V70" s="12" t="n">
         <f aca="false">MAX(D70-G70-L70,0)-MAX(O70,0)</f>
-        <v>2859.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W70" s="12" t="n">
         <f aca="false">P70+$B$18</f>
@@ -7779,19 +7631,19 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="34" t="n">
-        <v>47178</v>
+        <v>47119</v>
       </c>
       <c r="B71" s="21" t="n">
-        <f aca="false">IF(A71&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A71&gt;$B$38,$B$39,0)+IF(A71&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A71&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A71&gt;$B$40,$B$41,0)+IF(A71&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C71" s="12" t="n">
-        <f aca="false">IF(A71=$B$37,$B$26-$B$29,0)-IF(A71=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A71=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A71=$B$39,$B$26-$B$29,0)-IF(A71=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A71=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D71" s="12" t="n">
         <f aca="false">B71+C71</f>
-        <v>2859.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E71" s="12" t="n">
         <f aca="false">H70</f>
@@ -7863,7 +7715,7 @@
       </c>
       <c r="V71" s="12" t="n">
         <f aca="false">MAX(D71-G71-L71,0)-MAX(O71,0)</f>
-        <v>2859.03541666667</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W71" s="12" t="n">
         <f aca="false">P71+$B$18</f>
@@ -7872,19 +7724,19 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="34" t="n">
-        <v>47209</v>
+        <v>47150</v>
       </c>
       <c r="B72" s="21" t="n">
-        <f aca="false">IF(A72&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A72&gt;$B$38,$B$39,0)+IF(A72&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A72&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A72&gt;$B$40,$B$41,0)+IF(A72&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C72" s="12" t="n">
-        <f aca="false">IF(A72=$B$37,$B$26-$B$29,0)-IF(A72=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A72=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A72=$B$39,$B$26-$B$29,0)-IF(A72=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A72=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D72" s="12" t="n">
         <f aca="false">B72+C72</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E72" s="12" t="n">
         <f aca="false">H71</f>
@@ -7956,7 +7808,7 @@
       </c>
       <c r="V72" s="12" t="n">
         <f aca="false">MAX(D72-G72-L72,0)-MAX(O72,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W72" s="12" t="n">
         <f aca="false">P72+$B$18</f>
@@ -7965,19 +7817,19 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="34" t="n">
-        <v>47239</v>
+        <v>47178</v>
       </c>
       <c r="B73" s="21" t="n">
-        <f aca="false">IF(A73&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A73&gt;$B$38,$B$39,0)+IF(A73&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A73&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A73&gt;$B$40,$B$41,0)+IF(A73&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C73" s="12" t="n">
-        <f aca="false">IF(A73=$B$37,$B$26-$B$29,0)-IF(A73=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A73=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A73=$B$39,$B$26-$B$29,0)-IF(A73=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A73=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D73" s="12" t="n">
         <f aca="false">B73+C73</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E73" s="12" t="n">
         <f aca="false">H72</f>
@@ -8049,7 +7901,7 @@
       </c>
       <c r="V73" s="12" t="n">
         <f aca="false">MAX(D73-G73-L73,0)-MAX(O73,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W73" s="12" t="n">
         <f aca="false">P73+$B$18</f>
@@ -8058,19 +7910,19 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="34" t="n">
-        <v>47270</v>
+        <v>47209</v>
       </c>
       <c r="B74" s="21" t="n">
-        <f aca="false">IF(A74&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A74&gt;$B$38,$B$39,0)+IF(A74&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A74&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A74&gt;$B$40,$B$41,0)+IF(A74&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C74" s="12" t="n">
-        <f aca="false">IF(A74=$B$37,$B$26-$B$29,0)-IF(A74=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A74=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A74=$B$39,$B$26-$B$29,0)-IF(A74=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A74=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D74" s="12" t="n">
         <f aca="false">B74+C74</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E74" s="12" t="n">
         <f aca="false">H73</f>
@@ -8142,7 +7994,7 @@
       </c>
       <c r="V74" s="12" t="n">
         <f aca="false">MAX(D74-G74-L74,0)-MAX(O74,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W74" s="12" t="n">
         <f aca="false">P74+$B$18</f>
@@ -8151,19 +8003,19 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="34" t="n">
-        <v>47300</v>
+        <v>47239</v>
       </c>
       <c r="B75" s="21" t="n">
-        <f aca="false">IF(A75&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A75&gt;$B$38,$B$39,0)+IF(A75&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A75&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A75&gt;$B$40,$B$41,0)+IF(A75&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C75" s="12" t="n">
-        <f aca="false">IF(A75=$B$37,$B$26-$B$29,0)-IF(A75=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A75=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A75=$B$39,$B$26-$B$29,0)-IF(A75=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A75=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D75" s="12" t="n">
         <f aca="false">B75+C75</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E75" s="12" t="n">
         <f aca="false">H74</f>
@@ -8235,7 +8087,7 @@
       </c>
       <c r="V75" s="12" t="n">
         <f aca="false">MAX(D75-G75-L75,0)-MAX(O75,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W75" s="12" t="n">
         <f aca="false">P75+$B$18</f>
@@ -8244,19 +8096,19 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="34" t="n">
-        <v>47331</v>
+        <v>47270</v>
       </c>
       <c r="B76" s="21" t="n">
-        <f aca="false">IF(A76&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A76&gt;$B$38,$B$39,0)+IF(A76&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A76&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A76&gt;$B$40,$B$41,0)+IF(A76&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C76" s="12" t="n">
-        <f aca="false">IF(A76=$B$37,$B$26-$B$29,0)-IF(A76=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A76=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A76=$B$39,$B$26-$B$29,0)-IF(A76=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A76=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D76" s="12" t="n">
         <f aca="false">B76+C76</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E76" s="12" t="n">
         <f aca="false">H75</f>
@@ -8328,7 +8180,7 @@
       </c>
       <c r="V76" s="12" t="n">
         <f aca="false">MAX(D76-G76-L76,0)-MAX(O76,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W76" s="12" t="n">
         <f aca="false">P76+$B$18</f>
@@ -8337,19 +8189,19 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="34" t="n">
-        <v>47362</v>
+        <v>47300</v>
       </c>
       <c r="B77" s="21" t="n">
-        <f aca="false">IF(A77&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A77&gt;$B$38,$B$39,0)+IF(A77&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A77&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A77&gt;$B$40,$B$41,0)+IF(A77&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C77" s="12" t="n">
-        <f aca="false">IF(A77=$B$37,$B$26-$B$29,0)-IF(A77=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A77=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A77=$B$39,$B$26-$B$29,0)-IF(A77=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A77=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D77" s="12" t="n">
         <f aca="false">B77+C77</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E77" s="12" t="n">
         <f aca="false">H76</f>
@@ -8421,7 +8273,7 @@
       </c>
       <c r="V77" s="12" t="n">
         <f aca="false">MAX(D77-G77-L77,0)-MAX(O77,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W77" s="12" t="n">
         <f aca="false">P77+$B$18</f>
@@ -8430,19 +8282,19 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="34" t="n">
-        <v>47392</v>
+        <v>47331</v>
       </c>
       <c r="B78" s="21" t="n">
-        <f aca="false">IF(A78&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A78&gt;$B$38,$B$39,0)+IF(A78&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A78&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A78&gt;$B$40,$B$41,0)+IF(A78&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C78" s="12" t="n">
-        <f aca="false">IF(A78=$B$37,$B$26-$B$29,0)-IF(A78=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A78=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A78=$B$39,$B$26-$B$29,0)-IF(A78=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A78=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D78" s="12" t="n">
         <f aca="false">B78+C78</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E78" s="12" t="n">
         <f aca="false">H77</f>
@@ -8514,7 +8366,7 @@
       </c>
       <c r="V78" s="12" t="n">
         <f aca="false">MAX(D78-G78-L78,0)-MAX(O78,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W78" s="12" t="n">
         <f aca="false">P78+$B$18</f>
@@ -8523,19 +8375,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="34" t="n">
-        <v>47423</v>
+        <v>47362</v>
       </c>
       <c r="B79" s="21" t="n">
-        <f aca="false">IF(A79&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A79&gt;$B$38,$B$39,0)+IF(A79&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A79&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A79&gt;$B$40,$B$41,0)+IF(A79&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C79" s="12" t="n">
-        <f aca="false">IF(A79=$B$37,$B$26-$B$29,0)-IF(A79=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A79=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A79=$B$39,$B$26-$B$29,0)-IF(A79=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A79=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D79" s="12" t="n">
         <f aca="false">B79+C79</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E79" s="12" t="n">
         <f aca="false">H78</f>
@@ -8607,7 +8459,7 @@
       </c>
       <c r="V79" s="12" t="n">
         <f aca="false">MAX(D79-G79-L79,0)-MAX(O79,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W79" s="12" t="n">
         <f aca="false">P79+$B$18</f>
@@ -8616,19 +8468,19 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="34" t="n">
-        <v>47453</v>
+        <v>47392</v>
       </c>
       <c r="B80" s="21" t="n">
-        <f aca="false">IF(A80&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A80&gt;$B$38,$B$39,0)+IF(A80&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A80&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A80&gt;$B$40,$B$41,0)+IF(A80&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C80" s="12" t="n">
-        <f aca="false">IF(A80=$B$37,$B$26-$B$29,0)-IF(A80=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A80=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A80=$B$39,$B$26-$B$29,0)-IF(A80=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A80=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D80" s="12" t="n">
         <f aca="false">B80+C80</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E80" s="12" t="n">
         <f aca="false">H79</f>
@@ -8700,7 +8552,7 @@
       </c>
       <c r="V80" s="12" t="n">
         <f aca="false">MAX(D80-G80-L80,0)-MAX(O80,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W80" s="12" t="n">
         <f aca="false">P80+$B$18</f>
@@ -8709,19 +8561,19 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="34" t="n">
-        <v>47484</v>
+        <v>47423</v>
       </c>
       <c r="B81" s="21" t="n">
-        <f aca="false">IF(A81&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A81&gt;$B$38,$B$39,0)+IF(A81&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A81&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A81&gt;$B$40,$B$41,0)+IF(A81&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C81" s="12" t="n">
-        <f aca="false">IF(A81=$B$37,$B$26-$B$29,0)-IF(A81=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A81=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A81=$B$39,$B$26-$B$29,0)-IF(A81=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A81=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D81" s="12" t="n">
         <f aca="false">B81+C81</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E81" s="12" t="n">
         <f aca="false">H80</f>
@@ -8793,7 +8645,7 @@
       </c>
       <c r="V81" s="12" t="n">
         <f aca="false">MAX(D81-G81-L81,0)-MAX(O81,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W81" s="12" t="n">
         <f aca="false">P81+$B$18</f>
@@ -8802,19 +8654,19 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="34" t="n">
-        <v>47515</v>
+        <v>47453</v>
       </c>
       <c r="B82" s="21" t="n">
-        <f aca="false">IF(A82&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A82&gt;$B$38,$B$39,0)+IF(A82&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A82&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A82&gt;$B$40,$B$41,0)+IF(A82&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C82" s="12" t="n">
-        <f aca="false">IF(A82=$B$37,$B$26-$B$29,0)-IF(A82=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A82=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A82=$B$39,$B$26-$B$29,0)-IF(A82=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A82=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D82" s="12" t="n">
         <f aca="false">B82+C82</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E82" s="12" t="n">
         <f aca="false">H81</f>
@@ -8886,7 +8738,7 @@
       </c>
       <c r="V82" s="12" t="n">
         <f aca="false">MAX(D82-G82-L82,0)-MAX(O82,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W82" s="12" t="n">
         <f aca="false">P82+$B$18</f>
@@ -8895,19 +8747,19 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="34" t="n">
-        <v>47543</v>
+        <v>47484</v>
       </c>
       <c r="B83" s="21" t="n">
-        <f aca="false">IF(A83&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A83&gt;$B$38,$B$39,0)+IF(A83&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A83&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A83&gt;$B$40,$B$41,0)+IF(A83&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C83" s="12" t="n">
-        <f aca="false">IF(A83=$B$37,$B$26-$B$29,0)-IF(A83=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A83=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A83=$B$39,$B$26-$B$29,0)-IF(A83=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A83=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D83" s="12" t="n">
         <f aca="false">B83+C83</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E83" s="12" t="n">
         <f aca="false">H82</f>
@@ -8979,7 +8831,7 @@
       </c>
       <c r="V83" s="12" t="n">
         <f aca="false">MAX(D83-G83-L83,0)-MAX(O83,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W83" s="12" t="n">
         <f aca="false">P83+$B$18</f>
@@ -8988,19 +8840,19 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="34" t="n">
-        <v>47574</v>
+        <v>47515</v>
       </c>
       <c r="B84" s="21" t="n">
-        <f aca="false">IF(A84&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A84&gt;$B$38,$B$39,0)+IF(A84&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A84&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A84&gt;$B$40,$B$41,0)+IF(A84&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C84" s="12" t="n">
-        <f aca="false">IF(A84=$B$37,$B$26-$B$29,0)-IF(A84=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A84=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A84=$B$39,$B$26-$B$29,0)-IF(A84=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A84=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D84" s="12" t="n">
         <f aca="false">B84+C84</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E84" s="12" t="n">
         <f aca="false">H83</f>
@@ -9072,7 +8924,7 @@
       </c>
       <c r="V84" s="12" t="n">
         <f aca="false">MAX(D84-G84-L84,0)-MAX(O84,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W84" s="12" t="n">
         <f aca="false">P84+$B$18</f>
@@ -9081,19 +8933,19 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="34" t="n">
-        <v>47604</v>
+        <v>47543</v>
       </c>
       <c r="B85" s="21" t="n">
-        <f aca="false">IF(A85&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A85&gt;$B$38,$B$39,0)+IF(A85&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A85&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A85&gt;$B$40,$B$41,0)+IF(A85&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C85" s="12" t="n">
-        <f aca="false">IF(A85=$B$37,$B$26-$B$29,0)-IF(A85=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A85=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A85=$B$39,$B$26-$B$29,0)-IF(A85=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A85=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D85" s="12" t="n">
         <f aca="false">B85+C85</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E85" s="12" t="n">
         <f aca="false">H84</f>
@@ -9165,7 +9017,7 @@
       </c>
       <c r="V85" s="12" t="n">
         <f aca="false">MAX(D85-G85-L85,0)-MAX(O85,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W85" s="12" t="n">
         <f aca="false">P85+$B$18</f>
@@ -9174,19 +9026,19 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="34" t="n">
-        <v>47635</v>
+        <v>47574</v>
       </c>
       <c r="B86" s="21" t="n">
-        <f aca="false">IF(A86&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A86&gt;$B$38,$B$39,0)+IF(A86&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A86&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A86&gt;$B$40,$B$41,0)+IF(A86&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C86" s="12" t="n">
-        <f aca="false">IF(A86=$B$37,$B$26-$B$29,0)-IF(A86=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A86=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A86=$B$39,$B$26-$B$29,0)-IF(A86=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A86=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D86" s="12" t="n">
         <f aca="false">B86+C86</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E86" s="12" t="n">
         <f aca="false">H85</f>
@@ -9258,7 +9110,7 @@
       </c>
       <c r="V86" s="12" t="n">
         <f aca="false">MAX(D86-G86-L86,0)-MAX(O86,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W86" s="12" t="n">
         <f aca="false">P86+$B$18</f>
@@ -9267,19 +9119,19 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="34" t="n">
-        <v>47665</v>
+        <v>47604</v>
       </c>
       <c r="B87" s="21" t="n">
-        <f aca="false">IF(A87&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A87&gt;$B$38,$B$39,0)+IF(A87&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A87&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A87&gt;$B$40,$B$41,0)+IF(A87&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C87" s="12" t="n">
-        <f aca="false">IF(A87=$B$37,$B$26-$B$29,0)-IF(A87=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A87=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A87=$B$39,$B$26-$B$29,0)-IF(A87=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A87=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D87" s="12" t="n">
         <f aca="false">B87+C87</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E87" s="12" t="n">
         <f aca="false">H86</f>
@@ -9351,7 +9203,7 @@
       </c>
       <c r="V87" s="12" t="n">
         <f aca="false">MAX(D87-G87-L87,0)-MAX(O87,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W87" s="12" t="n">
         <f aca="false">P87+$B$18</f>
@@ -9360,19 +9212,19 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="34" t="n">
-        <v>47696</v>
+        <v>47635</v>
       </c>
       <c r="B88" s="21" t="n">
-        <f aca="false">IF(A88&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A88&gt;$B$38,$B$39,0)+IF(A88&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A88&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A88&gt;$B$40,$B$41,0)+IF(A88&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C88" s="12" t="n">
-        <f aca="false">IF(A88=$B$37,$B$26-$B$29,0)-IF(A88=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A88=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A88=$B$39,$B$26-$B$29,0)-IF(A88=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A88=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D88" s="12" t="n">
         <f aca="false">B88+C88</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E88" s="12" t="n">
         <f aca="false">H87</f>
@@ -9444,7 +9296,7 @@
       </c>
       <c r="V88" s="12" t="n">
         <f aca="false">MAX(D88-G88-L88,0)-MAX(O88,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W88" s="12" t="n">
         <f aca="false">P88+$B$18</f>
@@ -9453,19 +9305,19 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="34" t="n">
-        <v>47727</v>
+        <v>47665</v>
       </c>
       <c r="B89" s="21" t="n">
-        <f aca="false">IF(A89&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A89&gt;$B$38,$B$39,0)+IF(A89&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A89&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A89&gt;$B$40,$B$41,0)+IF(A89&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C89" s="12" t="n">
-        <f aca="false">IF(A89=$B$37,$B$26-$B$29,0)-IF(A89=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A89=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A89=$B$39,$B$26-$B$29,0)-IF(A89=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A89=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D89" s="12" t="n">
         <f aca="false">B89+C89</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E89" s="12" t="n">
         <f aca="false">H88</f>
@@ -9537,7 +9389,7 @@
       </c>
       <c r="V89" s="12" t="n">
         <f aca="false">MAX(D89-G89-L89,0)-MAX(O89,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W89" s="12" t="n">
         <f aca="false">P89+$B$18</f>
@@ -9546,19 +9398,19 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="34" t="n">
-        <v>47757</v>
+        <v>47696</v>
       </c>
       <c r="B90" s="21" t="n">
-        <f aca="false">IF(A90&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A90&gt;$B$38,$B$39,0)+IF(A90&gt;=$B$33,$B$35,0)</f>
-        <v>2859.03541666667</v>
+        <f aca="false">IF(A90&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A90&gt;$B$40,$B$41,0)+IF(A90&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
       </c>
       <c r="C90" s="12" t="n">
-        <f aca="false">IF(A90=$B$37,$B$26-$B$29,0)-IF(A90=DATE(YEAR($B$37),MONTH($B$37)+1,1),$B$28,0)+IF(A90=$B$33,$B$35*$B$34,0)+0</f>
+        <f aca="false">IF(A90=$B$39,$B$26-$B$29,0)-IF(A90=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A90=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D90" s="12" t="n">
         <f aca="false">B90+C90</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="E90" s="12" t="n">
         <f aca="false">H89</f>
@@ -9630,10 +9482,196 @@
       </c>
       <c r="V90" s="12" t="n">
         <f aca="false">MAX(D90-G90-L90,0)-MAX(O90,0)</f>
-        <v>2859.03541666667</v>
+        <v>2911.09333333334</v>
       </c>
       <c r="W90" s="12" t="n">
         <f aca="false">P90+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="34" t="n">
+        <v>47727</v>
+      </c>
+      <c r="B91" s="21" t="n">
+        <f aca="false">IF(A91&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A91&gt;$B$40,$B$41,0)+IF(A91&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="C91" s="12" t="n">
+        <f aca="false">IF(A91=$B$39,$B$26-$B$29,0)-IF(A91=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A91=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
+      </c>
+      <c r="D91" s="12" t="n">
+        <f aca="false">B91+C91</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="E91" s="12" t="n">
+        <f aca="false">H90</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <f aca="false">E91*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <f aca="false">MIN(E91+F91,MAX(D91-K91,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <f aca="false">E91+F91-G91</f>
+        <v>0</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <f aca="false">M90</f>
+        <v>0</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <f aca="false">I91*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <f aca="false">MIN(I91+J91,J91+$B$9*I91)</f>
+        <v>0</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <f aca="false">MIN(I91+J91,MAX(D91-G91,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <f aca="false">I91+J91-L91</f>
+        <v>0</v>
+      </c>
+      <c r="N91" s="12" t="n">
+        <f aca="false">P90</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <f aca="false">MIN(D91-G91-L91,MAX($B$15-$B$18-N91,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P91" s="12" t="n">
+        <f aca="false">N91+O91</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q91" s="5" t="n">
+        <f aca="false">IF(H91&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R91" s="5" t="n">
+        <f aca="false">IF(M91&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S91" s="5" t="n">
+        <f aca="false">IF(AND(Q91=1,R91=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T91" s="5" t="n">
+        <f aca="false">IF(P91&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U91" s="5" t="n">
+        <f aca="false">IF(P91+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <f aca="false">MAX(D91-G91-L91,0)-MAX(O91,0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="W91" s="12" t="n">
+        <f aca="false">P91+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="34" t="n">
+        <v>47757</v>
+      </c>
+      <c r="B92" s="21" t="n">
+        <f aca="false">IF(A92&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A92&gt;$B$40,$B$41,0)+IF(A92&gt;=$B$35,$B$37,0)+$B$32</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="C92" s="12" t="n">
+        <f aca="false">IF(A92=$B$39,$B$26-$B$29,0)-IF(A92=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A92=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
+      </c>
+      <c r="D92" s="12" t="n">
+        <f aca="false">B92+C92</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="E92" s="12" t="n">
+        <f aca="false">H91</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <f aca="false">E92*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <f aca="false">MIN(E92+F92,MAX(D92-K92,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <f aca="false">E92+F92-G92</f>
+        <v>0</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <f aca="false">M91</f>
+        <v>0</v>
+      </c>
+      <c r="J92" s="12" t="n">
+        <f aca="false">I92*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <f aca="false">MIN(I92+J92,J92+$B$9*I92)</f>
+        <v>0</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <f aca="false">MIN(I92+J92,MAX(D92-G92,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M92" s="12" t="n">
+        <f aca="false">I92+J92-L92</f>
+        <v>0</v>
+      </c>
+      <c r="N92" s="12" t="n">
+        <f aca="false">P91</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O92" s="12" t="n">
+        <f aca="false">MIN(D92-G92-L92,MAX($B$15-$B$18-N92,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P92" s="12" t="n">
+        <f aca="false">N92+O92</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q92" s="5" t="n">
+        <f aca="false">IF(H92&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R92" s="5" t="n">
+        <f aca="false">IF(M92&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S92" s="5" t="n">
+        <f aca="false">IF(AND(Q92=1,R92=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T92" s="5" t="n">
+        <f aca="false">IF(P92&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U92" s="5" t="n">
+        <f aca="false">IF(P92+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V92" s="12" t="n">
+        <f aca="false">MAX(D92-G92-L92,0)-MAX(O92,0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="W92" s="12" t="n">
+        <f aca="false">P92+$B$18</f>
         <v>100842</v>
       </c>
     </row>
@@ -9664,12 +9702,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9677,48 +9715,48 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -9736,7 +9774,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>17767.46</v>
@@ -9783,7 +9821,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>6410.38</v>
@@ -9830,7 +9868,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>1459.54</v>
@@ -9877,7 +9915,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">SUM(B6:B8)</f>
@@ -9934,7 +9972,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -9952,7 +9990,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>4300</v>
@@ -9999,7 +10037,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B13" s="13" t="n">
         <v>32.71</v>
@@ -10046,7 +10084,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B14" s="13" t="n">
         <v>0</v>
@@ -10093,7 +10131,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>183.82</v>
@@ -10140,7 +10178,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B16" s="13" t="n">
         <v>500</v>
@@ -10187,7 +10225,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">SUM(B12:B16)</f>
@@ -10244,7 +10282,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -10262,7 +10300,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B20" s="13" t="n">
         <v>6857.93</v>
@@ -10356,7 +10394,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B22" s="13" t="n">
         <v>1057.39</v>
@@ -10403,7 +10441,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B23" s="13" t="n">
         <v>341.99</v>
@@ -10450,7 +10488,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B24" s="13" t="n">
         <v>0</v>
@@ -10497,7 +10535,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B25" s="13" t="n">
         <v>856.83</v>
@@ -10544,7 +10582,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B26" s="13" t="n">
         <v>286.67</v>
@@ -10591,7 +10629,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B27" s="13" t="n">
         <v>614</v>
@@ -10638,7 +10676,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B28" s="13" t="n">
         <v>323.39</v>
@@ -10685,7 +10723,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B29" s="13" t="n">
         <v>368.15</v>
@@ -10732,7 +10770,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B30" s="13" t="n">
         <v>400.62</v>
@@ -10779,7 +10817,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B31" s="13" t="n">
         <v>134.97</v>
@@ -10826,7 +10864,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B32" s="13" t="n">
         <v>178.9</v>
@@ -10873,7 +10911,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B33" s="13" t="n">
         <v>115.5</v>
@@ -10920,7 +10958,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B34" s="13" t="n">
         <v>760</v>
@@ -10967,7 +11005,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B35" s="13" t="n">
         <v>155</v>
@@ -11061,7 +11099,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B37" s="13" t="n">
         <v>473.56</v>
@@ -11108,7 +11146,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B38" s="13" t="n">
         <v>431.52</v>
@@ -11155,7 +11193,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B39" s="13" t="n">
         <v>359.9</v>
@@ -11202,7 +11240,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B40" s="13" t="n">
         <v>27.6</v>
@@ -11249,7 +11287,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B41" s="13" t="n">
         <v>557.68</v>
@@ -11296,7 +11334,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B42" s="13" t="n">
         <v>385.13</v>
@@ -11343,7 +11381,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B43" s="13" t="n">
         <v>209</v>
@@ -11390,7 +11428,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B44" s="13" t="n">
         <v>266.15</v>
@@ -11484,7 +11522,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B46" s="13" t="n">
         <v>469.36</v>
@@ -11578,7 +11616,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B48" s="13" t="n">
         <v>72.9</v>
@@ -11625,7 +11663,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B49" s="13" t="n">
         <v>0.5</v>
@@ -11672,7 +11710,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B50" s="13" t="n">
         <v>355.78</v>
@@ -11719,7 +11757,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B51" s="13" t="n">
         <v>97.3</v>
@@ -11766,7 +11804,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B52" s="13" t="n">
         <v>129.41</v>
@@ -11813,7 +11851,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B53" s="13" t="n">
         <v>465.78</v>
@@ -11860,7 +11898,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B54" s="13" t="n">
         <v>240</v>
@@ -11907,7 +11945,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B55" s="13" t="n">
         <v>729.5</v>
@@ -11954,7 +11992,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B56" s="13" t="n">
         <v>2.25</v>
@@ -12001,7 +12039,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B57" s="13" t="n">
         <v>0</v>
@@ -12048,7 +12086,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B58" s="13" t="n">
         <v>127.73</v>
@@ -12095,7 +12133,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B59" s="17" t="n">
         <f aca="false">SUM(B20:B58)</f>
@@ -12152,7 +12190,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B61" s="28" t="n">
         <f aca="false">B17+B59</f>
@@ -12209,7 +12247,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B62" s="28" t="n">
         <f aca="false">B9</f>
@@ -12266,7 +12304,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B63" s="9" t="n">
         <f aca="false">B62-B61</f>
@@ -12352,35 +12390,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>20</v>
@@ -12388,10 +12426,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>72.97</v>
@@ -12401,25 +12439,25 @@
         <v>875.64</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">IF(E5="Cut",D5,0)</f>
         <v>0</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>82.99</v>
@@ -12429,25 +12467,25 @@
         <v>995.88</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">IF(E6="Cut",D6,0)</f>
         <v>0</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>26.99</v>
@@ -12457,23 +12495,23 @@
         <v>323.88</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">IF(E7="Cut",D7,0)</f>
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>18.99</v>
@@ -12483,25 +12521,25 @@
         <v>227.88</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">IF(E8="Cut",D8,0)</f>
         <v>0</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>12.99</v>
@@ -12511,23 +12549,23 @@
         <v>155.88</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">IF(E9="Cut",D9,0)</f>
         <v>0</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>139</v>
@@ -12537,25 +12575,25 @@
         <v>139</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">IF(E10="Cut",D10,0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>4.99</v>
@@ -12565,25 +12603,25 @@
         <v>59.88</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">IF(E11="Cut",D11,0)</f>
         <v>0</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>6.36</v>
@@ -12593,25 +12631,25 @@
         <v>76.32</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">IF(E12="Cut",D12,0)</f>
         <v>0</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>11.99</v>
@@ -12621,25 +12659,25 @@
         <v>143.88</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">IF(E13="Cut",D13,0)</f>
         <v>0</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>8.99</v>
@@ -12649,25 +12687,25 @@
         <v>107.88</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">IF(E14="Cut",D14,0)</f>
         <v>0</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>25</v>
@@ -12677,25 +12715,25 @@
         <v>300</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F15" s="12" t="n">
         <f aca="false">IF(E15="Cut",D15,0)</f>
         <v>0</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>27.72</v>
@@ -12705,25 +12743,25 @@
         <v>332.64</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F16" s="12" t="n">
         <f aca="false">IF(E16="Cut",D16,0)</f>
         <v>0</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>99.99</v>
@@ -12733,23 +12771,23 @@
         <v>99.99</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F17" s="12" t="n">
         <f aca="false">IF(E17="Cut",D17,0)</f>
         <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>150</v>
@@ -12759,23 +12797,23 @@
         <v>150</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F18" s="12" t="n">
         <f aca="false">IF(E18="Cut",D18,0)</f>
         <v>0</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>20.7</v>
@@ -12785,25 +12823,25 @@
         <v>248.4</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F19" s="12" t="n">
         <f aca="false">IF(E19="Cut",D19,0)</f>
         <v>0</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>10</v>
@@ -12813,25 +12851,25 @@
         <v>120</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">IF(E20="Cut",D20,0)</f>
         <v>0</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>32.99</v>
@@ -12841,25 +12879,25 @@
         <v>395.88</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">IF(E21="Cut",D21,0)</f>
         <v>0</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>13.94</v>
@@ -12869,25 +12907,25 @@
         <v>167.28</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">IF(E22="Cut",D22,0)</f>
         <v>0</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>20.76</v>
@@ -12897,25 +12935,25 @@
         <v>249.12</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F23" s="12" t="n">
         <f aca="false">IF(E23="Cut",D23,0)</f>
         <v>0</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>10.63</v>
@@ -12925,23 +12963,23 @@
         <v>127.56</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F24" s="12" t="n">
         <f aca="false">IF(E24="Cut",D24,0)</f>
         <v>0</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>21.25</v>
@@ -12951,23 +12989,23 @@
         <v>255</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F25" s="12" t="n">
         <f aca="false">IF(E25="Cut",D25,0)</f>
         <v>0</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>381.44</v>
@@ -12977,25 +13015,25 @@
         <v>381.44</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F26" s="12" t="n">
         <f aca="false">IF(E26="Cut",D26,0)</f>
         <v>0</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>212.49</v>
@@ -13005,25 +13043,25 @@
         <v>212.49</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F27" s="12" t="n">
         <f aca="false">IF(E27="Cut",D27,0)</f>
         <v>0</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>114.75</v>
@@ -13033,25 +13071,25 @@
         <v>229.5</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F28" s="12" t="n">
         <f aca="false">IF(E28="Cut",D28,0)</f>
         <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>548</v>
@@ -13061,25 +13099,25 @@
         <v>548</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F29" s="12" t="n">
         <f aca="false">IF(E29="Cut",D29,0)</f>
         <v>0</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>32.95</v>
@@ -13089,25 +13127,25 @@
         <v>395.4</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F30" s="12" t="n">
         <f aca="false">IF(E30="Cut",D30,0)</f>
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>115.23</v>
@@ -13117,25 +13155,25 @@
         <v>1382.76</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F31" s="12" t="n">
         <f aca="false">IF(E31="Cut",D31,0)</f>
         <v>0</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>25</v>
@@ -13145,22 +13183,22 @@
         <v>300</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F32" s="12" t="n">
         <f aca="false">IF(E32="Cut",D32,0)</f>
         <v>0</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D33" s="17" t="n">
         <f aca="false">SUM(D5:D32)</f>
@@ -13173,7 +13211,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D34" s="12" t="n">
         <f aca="false">SUMIF(E5:E32,"Review",D5:D32)</f>
@@ -13182,7 +13220,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -13210,156 +13248,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="36" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="36" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
+++ b/Dashboards/Areas/💰 Finance/Household Budget 2026-10.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="484">
   <si>
     <t xml:space="preserve">Household Budget — October 2026 rebuild</t>
   </si>
@@ -824,6 +824,24 @@
   </si>
   <si>
     <t xml:space="preserve">Set to 5000 to test pulling $5k from SPAXX into JetBlue in Nov-26.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">401(k) catch-up, gross per month (scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age-50 catch-up is $8,000 in 2026. $667 = full-year pace; $889 = the full $8k squeezed into Apr–Dec 2027. 0 = not doing it. Phase 1 says no new investing until cards are cleared.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch-up starts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First month after the cards clear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal tax shield on catch-up (0% if Roth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-tax: ~32% federal. MA does not exempt 401(k) deferrals (my read — confirm with your CPA). Roth catch-up: enter 0%.</t>
   </si>
   <si>
     <t xml:space="preserve">Bonus lump lands in month</t>
@@ -4631,7 +4649,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W92"/>
+  <dimension ref="A1:W95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -4685,7 +4703,7 @@
         <v>195</v>
       </c>
       <c r="G5" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,Q45:Q92,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A48:A95,MATCH(1,Q48:Q95,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4703,7 +4721,7 @@
         <v>198</v>
       </c>
       <c r="G6" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,R45:R92,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A48:A95,MATCH(1,R48:R95,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4721,7 +4739,7 @@
         <v>200</v>
       </c>
       <c r="G7" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,S45:S92,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A48:A95,MATCH(1,S48:S95,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4739,7 +4757,7 @@
         <v>202</v>
       </c>
       <c r="G8" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,T45:T92,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A48:A95,MATCH(1,T48:T95,0)),"after Oct-30")</f>
         <v>46447</v>
       </c>
     </row>
@@ -4757,7 +4775,7 @@
         <v>205</v>
       </c>
       <c r="G9" s="29" t="n">
-        <f aca="false">IFERROR(INDEX(A45:A92,MATCH(1,U45:U92,0)),"after Oct-30")</f>
+        <f aca="false">IFERROR(INDEX(A48:A95,MATCH(1,U48:U95,0)),"after Oct-30")</f>
         <v>46874</v>
       </c>
     </row>
@@ -4775,7 +4793,7 @@
         <v>208</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUM(F45:F92)+SUM(J45:J92)</f>
+        <f aca="false">SUM(F48:F95)+SUM(J48:J95)</f>
         <v>1442.47513468667</v>
       </c>
     </row>
@@ -5112,394 +5130,148 @@
       <c r="A39" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B39" s="26" t="n">
-        <v>46447</v>
-      </c>
-      <c r="C39" s="2"/>
+      <c r="B39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B40" s="26" t="n">
-        <v>47119</v>
+        <v>46478</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B41" s="21" t="n">
+        <v>270</v>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B42" s="26" t="n">
+        <v>46447</v>
+      </c>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>47119</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B44" s="21" t="n">
         <f aca="false">Budget!F16</f>
         <v>342</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="F44" s="10" t="s">
+      <c r="C44" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="G44" s="10" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="B47" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="I44" s="10" t="s">
+      <c r="C47" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="D47" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="E47" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="L44" s="10" t="s">
+      <c r="F47" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="M44" s="10" t="s">
+      <c r="G47" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="N44" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="O44" s="10" t="s">
+      <c r="I47" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="P44" s="10" t="s">
+      <c r="J47" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="Q44" s="10" t="s">
+      <c r="K47" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="R44" s="10" t="s">
+      <c r="L47" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="S44" s="10" t="s">
+      <c r="M47" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="T44" s="10" t="s">
+      <c r="N47" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="U44" s="10" t="s">
+      <c r="O47" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="V44" s="10" t="s">
+      <c r="P47" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="W44" s="10" t="s">
+      <c r="Q47" s="10" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B45" s="21" t="n">
-        <f aca="false">IF(A45&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A45&gt;$B$40,$B$41,0)+IF(A45&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>977.318333333335</v>
-      </c>
-      <c r="C45" s="12" t="n">
-        <f aca="false">IF(A45=$B$39,$B$26-$B$29,0)-IF(A45=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A45=$B$35,$B$37*$B$36,0)+$B$38</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <f aca="false">B45+C45</f>
-        <v>977.318333333335</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <f aca="false">$B$5</f>
-        <v>9800.78</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <f aca="false">E45*$B$6/12</f>
-        <v>242.895997666667</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <f aca="false">MIN(E45+F45,MAX(D45-K45,0))</f>
-        <v>846.050479333335</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <f aca="false">E45+F45-G45</f>
-        <v>9197.62551833333</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <f aca="false">$B$7</f>
-        <v>5341.52</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <f aca="false">I45*$B$8/12</f>
-        <v>77.852654</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <f aca="false">MIN(I45+J45,J45+$B$9*I45)</f>
-        <v>131.267854</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <f aca="false">MIN(I45+J45,MAX(D45-G45,0))</f>
-        <v>131.267854</v>
-      </c>
-      <c r="M45" s="12" t="n">
-        <f aca="false">I45+J45-L45</f>
-        <v>5288.1048</v>
-      </c>
-      <c r="N45" s="12" t="n">
-        <f aca="false">$B$10-$B$38</f>
-        <v>12081</v>
-      </c>
-      <c r="O45" s="12" t="n">
-        <f aca="false">MIN(D45-G45-L45,MAX($B$15-$B$18-N45,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P45" s="12" t="n">
-        <f aca="false">N45+O45</f>
-        <v>12081</v>
-      </c>
-      <c r="Q45" s="5" t="n">
-        <f aca="false">IF(H45&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R45" s="5" t="n">
-        <f aca="false">IF(M45&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S45" s="5" t="n">
-        <f aca="false">IF(AND(Q45=1,R45=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T45" s="5" t="n">
-        <f aca="false">IF(P45&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U45" s="5" t="n">
-        <f aca="false">IF(P45+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V45" s="12" t="n">
-        <f aca="false">MAX(D45-G45-L45,0)-MAX(O45,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W45" s="12" t="n">
-        <f aca="false">P45+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="34" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B46" s="21" t="n">
-        <f aca="false">IF(A46&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A46&gt;$B$40,$B$41,0)+IF(A46&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>977.318333333335</v>
-      </c>
-      <c r="C46" s="12" t="n">
-        <f aca="false">IF(A46=$B$39,$B$26-$B$29,0)-IF(A46=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A46=$B$35,$B$37*$B$36,0)+0</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <f aca="false">B46+C46</f>
-        <v>977.318333333335</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <f aca="false">H45</f>
-        <v>9197.62551833333</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <f aca="false">E46*$B$6/12</f>
-        <v>227.947819096028</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <f aca="false">MIN(E46+F46,MAX(D46-K46,0))</f>
-        <v>847.363157873335</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <f aca="false">E46+F46-G46</f>
-        <v>8578.21017955603</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <f aca="false">M45</f>
-        <v>5288.1048</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <f aca="false">I46*$B$8/12</f>
-        <v>77.07412746</v>
-      </c>
-      <c r="K46" s="12" t="n">
-        <f aca="false">MIN(I46+J46,J46+$B$9*I46)</f>
-        <v>129.95517546</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <f aca="false">MIN(I46+J46,MAX(D46-G46,0))</f>
-        <v>129.95517546</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <f aca="false">I46+J46-L46</f>
-        <v>5235.223752</v>
-      </c>
-      <c r="N46" s="12" t="n">
-        <f aca="false">P45</f>
-        <v>12081</v>
-      </c>
-      <c r="O46" s="12" t="n">
-        <f aca="false">MIN(D46-G46-L46,MAX($B$15-$B$18-N46,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P46" s="12" t="n">
-        <f aca="false">N46+O46</f>
-        <v>12081</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <f aca="false">IF(H46&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R46" s="5" t="n">
-        <f aca="false">IF(M46&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S46" s="5" t="n">
-        <f aca="false">IF(AND(Q46=1,R46=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T46" s="5" t="n">
-        <f aca="false">IF(P46&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U46" s="5" t="n">
-        <f aca="false">IF(P46+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <f aca="false">MAX(D46-G46-L46,0)-MAX(O46,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W46" s="12" t="n">
-        <f aca="false">P46+$B$18</f>
-        <v>28341.75</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="34" t="n">
-        <v>46388</v>
-      </c>
-      <c r="B47" s="21" t="n">
-        <f aca="false">IF(A47&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A47&gt;$B$40,$B$41,0)+IF(A47&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>977.318333333335</v>
-      </c>
-      <c r="C47" s="12" t="n">
-        <f aca="false">IF(A47=$B$39,$B$26-$B$29,0)-IF(A47=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A47=$B$35,$B$37*$B$36,0)+0</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <f aca="false">B47+C47</f>
-        <v>977.318333333335</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <f aca="false">H46</f>
-        <v>8578.21017955603</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <f aca="false">E47*$B$6/12</f>
-        <v>212.59664228333</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <f aca="false">MIN(E47+F47,MAX(D47-K47,0))</f>
-        <v>848.662709627935</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <f aca="false">E47+F47-G47</f>
-        <v>7942.14411221142</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <f aca="false">M46</f>
-        <v>5235.223752</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <f aca="false">I47*$B$8/12</f>
-        <v>76.3033861854</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <f aca="false">MIN(I47+J47,J47+$B$9*I47)</f>
-        <v>128.6556237054</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <f aca="false">MIN(I47+J47,MAX(D47-G47,0))</f>
-        <v>128.6556237054</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <f aca="false">I47+J47-L47</f>
-        <v>5182.87151448</v>
-      </c>
-      <c r="N47" s="12" t="n">
-        <f aca="false">P46</f>
-        <v>12081</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <f aca="false">MIN(D47-G47-L47,MAX($B$15-$B$18-N47,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P47" s="12" t="n">
-        <f aca="false">N47+O47</f>
-        <v>12081</v>
-      </c>
-      <c r="Q47" s="5" t="n">
-        <f aca="false">IF(H47&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R47" s="5" t="n">
-        <f aca="false">IF(M47&lt;=0.005,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S47" s="5" t="n">
-        <f aca="false">IF(AND(Q47=1,R47=1),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T47" s="5" t="n">
-        <f aca="false">IF(P47&gt;=$B$20,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U47" s="5" t="n">
-        <f aca="false">IF(P47+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="12" t="n">
-        <f aca="false">MAX(D47-G47-L47,0)-MAX(O47,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W47" s="12" t="n">
-        <f aca="false">P47+$B$18</f>
-        <v>28341.75</v>
+      <c r="R47" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="S47" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="T47" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="U47" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="V47" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="W47" s="10" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="34" t="n">
-        <v>46419</v>
+        <v>46327</v>
       </c>
       <c r="B48" s="21" t="n">
-        <f aca="false">IF(A48&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A48&gt;$B$40,$B$41,0)+IF(A48&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A48&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A48&gt;$B$43,$B$44,0)+IF(A48&gt;=$B$35,$B$37,0)+$B$32-IF(A48&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>977.318333333335</v>
       </c>
       <c r="C48" s="12" t="n">
-        <f aca="false">IF(A48=$B$39,$B$26-$B$29,0)-IF(A48=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A48=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A48=$B$42,$B$26-$B$29,0)-IF(A48=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A48=$B$35,$B$37*$B$36,0)+$B$38</f>
         <v>0</v>
       </c>
       <c r="D48" s="12" t="n">
@@ -5507,43 +5279,43 @@
         <v>977.318333333335</v>
       </c>
       <c r="E48" s="12" t="n">
-        <f aca="false">H47</f>
-        <v>7942.14411221142</v>
+        <f aca="false">$B$5</f>
+        <v>9800.78</v>
       </c>
       <c r="F48" s="12" t="n">
         <f aca="false">E48*$B$6/12</f>
-        <v>196.832804914306</v>
+        <v>242.895997666667</v>
       </c>
       <c r="G48" s="12" t="n">
         <f aca="false">MIN(E48+F48,MAX(D48-K48,0))</f>
-        <v>849.949265864989</v>
+        <v>846.050479333335</v>
       </c>
       <c r="H48" s="12" t="n">
         <f aca="false">E48+F48-G48</f>
-        <v>7289.02765126074</v>
+        <v>9197.62551833333</v>
       </c>
       <c r="I48" s="12" t="n">
-        <f aca="false">M47</f>
-        <v>5182.87151448</v>
+        <f aca="false">$B$7</f>
+        <v>5341.52</v>
       </c>
       <c r="J48" s="12" t="n">
         <f aca="false">I48*$B$8/12</f>
-        <v>75.540352323546</v>
+        <v>77.852654</v>
       </c>
       <c r="K48" s="12" t="n">
         <f aca="false">MIN(I48+J48,J48+$B$9*I48)</f>
-        <v>127.369067468346</v>
+        <v>131.267854</v>
       </c>
       <c r="L48" s="12" t="n">
         <f aca="false">MIN(I48+J48,MAX(D48-G48,0))</f>
-        <v>127.369067468346</v>
+        <v>131.267854</v>
       </c>
       <c r="M48" s="12" t="n">
         <f aca="false">I48+J48-L48</f>
-        <v>5131.0427993352</v>
+        <v>5288.1048</v>
       </c>
       <c r="N48" s="12" t="n">
-        <f aca="false">P47</f>
+        <f aca="false">$B$10-$B$38</f>
         <v>12081</v>
       </c>
       <c r="O48" s="12" t="n">
@@ -5585,55 +5357,55 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="34" t="n">
-        <v>46447</v>
+        <v>46357</v>
       </c>
       <c r="B49" s="21" t="n">
-        <f aca="false">IF(A49&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A49&gt;$B$40,$B$41,0)+IF(A49&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>2569.09333333334</v>
+        <f aca="false">IF(A49&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A49&gt;$B$43,$B$44,0)+IF(A49&gt;=$B$35,$B$37,0)+$B$32-IF(A49&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>977.318333333335</v>
       </c>
       <c r="C49" s="12" t="n">
-        <f aca="false">IF(A49=$B$39,$B$26-$B$29,0)-IF(A49=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A49=$B$35,$B$37*$B$36,0)+0</f>
-        <v>51581.8416666667</v>
+        <f aca="false">IF(A49=$B$42,$B$26-$B$29,0)-IF(A49=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A49=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
       </c>
       <c r="D49" s="12" t="n">
         <f aca="false">B49+C49</f>
-        <v>54150.935</v>
+        <v>977.318333333335</v>
       </c>
       <c r="E49" s="12" t="n">
         <f aca="false">H48</f>
-        <v>7289.02765126074</v>
+        <v>9197.62551833333</v>
       </c>
       <c r="F49" s="12" t="n">
         <f aca="false">E49*$B$6/12</f>
-        <v>180.646401957079</v>
+        <v>227.947819096028</v>
       </c>
       <c r="G49" s="12" t="n">
         <f aca="false">MIN(E49+F49,MAX(D49-K49,0))</f>
-        <v>7469.67405321782</v>
+        <v>847.363157873335</v>
       </c>
       <c r="H49" s="12" t="n">
         <f aca="false">E49+F49-G49</f>
-        <v>0</v>
+        <v>8578.21017955603</v>
       </c>
       <c r="I49" s="12" t="n">
         <f aca="false">M48</f>
-        <v>5131.0427993352</v>
+        <v>5288.1048</v>
       </c>
       <c r="J49" s="12" t="n">
         <f aca="false">I49*$B$8/12</f>
-        <v>74.7849488003106</v>
+        <v>77.07412746</v>
       </c>
       <c r="K49" s="12" t="n">
         <f aca="false">MIN(I49+J49,J49+$B$9*I49)</f>
-        <v>126.095376793663</v>
+        <v>129.95517546</v>
       </c>
       <c r="L49" s="12" t="n">
         <f aca="false">MIN(I49+J49,MAX(D49-G49,0))</f>
-        <v>5205.82774813551</v>
+        <v>129.95517546</v>
       </c>
       <c r="M49" s="12" t="n">
         <f aca="false">I49+J49-L49</f>
-        <v>0</v>
+        <v>5235.223752</v>
       </c>
       <c r="N49" s="12" t="n">
         <f aca="false">P48</f>
@@ -5641,27 +5413,27 @@
       </c>
       <c r="O49" s="12" t="n">
         <f aca="false">MIN(D49-G49-L49,MAX($B$15-$B$18-N49,0))</f>
-        <v>41475.4331986467</v>
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
         <f aca="false">N49+O49</f>
-        <v>53556.4331986467</v>
+        <v>12081</v>
       </c>
       <c r="Q49" s="5" t="n">
         <f aca="false">IF(H49&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="5" t="n">
         <f aca="false">IF(M49&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="5" t="n">
         <f aca="false">IF(AND(Q49=1,R49=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="5" t="n">
         <f aca="false">IF(P49&gt;=$B$20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" s="5" t="n">
         <f aca="false">IF(P49+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -5673,88 +5445,88 @@
       </c>
       <c r="W49" s="12" t="n">
         <f aca="false">P49+$B$18</f>
-        <v>69817.1831986467</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="34" t="n">
-        <v>46478</v>
+        <v>46388</v>
       </c>
       <c r="B50" s="21" t="n">
-        <f aca="false">IF(A50&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A50&gt;$B$40,$B$41,0)+IF(A50&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>2569.09333333334</v>
+        <f aca="false">IF(A50&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A50&gt;$B$43,$B$44,0)+IF(A50&gt;=$B$35,$B$37,0)+$B$32-IF(A50&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>977.318333333335</v>
       </c>
       <c r="C50" s="12" t="n">
-        <f aca="false">IF(A50=$B$39,$B$26-$B$29,0)-IF(A50=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A50=$B$35,$B$37*$B$36,0)+0</f>
-        <v>-3983.25</v>
+        <f aca="false">IF(A50=$B$42,$B$26-$B$29,0)-IF(A50=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A50=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
       </c>
       <c r="D50" s="12" t="n">
         <f aca="false">B50+C50</f>
-        <v>-1414.15666666667</v>
+        <v>977.318333333335</v>
       </c>
       <c r="E50" s="12" t="n">
         <f aca="false">H49</f>
-        <v>0</v>
+        <v>8578.21017955603</v>
       </c>
       <c r="F50" s="12" t="n">
         <f aca="false">E50*$B$6/12</f>
-        <v>0</v>
+        <v>212.59664228333</v>
       </c>
       <c r="G50" s="12" t="n">
         <f aca="false">MIN(E50+F50,MAX(D50-K50,0))</f>
-        <v>0</v>
+        <v>848.662709627935</v>
       </c>
       <c r="H50" s="12" t="n">
         <f aca="false">E50+F50-G50</f>
-        <v>0</v>
+        <v>7942.14411221142</v>
       </c>
       <c r="I50" s="12" t="n">
         <f aca="false">M49</f>
-        <v>0</v>
+        <v>5235.223752</v>
       </c>
       <c r="J50" s="12" t="n">
         <f aca="false">I50*$B$8/12</f>
-        <v>0</v>
+        <v>76.3033861854</v>
       </c>
       <c r="K50" s="12" t="n">
         <f aca="false">MIN(I50+J50,J50+$B$9*I50)</f>
-        <v>0</v>
+        <v>128.6556237054</v>
       </c>
       <c r="L50" s="12" t="n">
         <f aca="false">MIN(I50+J50,MAX(D50-G50,0))</f>
-        <v>0</v>
+        <v>128.6556237054</v>
       </c>
       <c r="M50" s="12" t="n">
         <f aca="false">I50+J50-L50</f>
-        <v>0</v>
+        <v>5182.87151448</v>
       </c>
       <c r="N50" s="12" t="n">
         <f aca="false">P49</f>
-        <v>53556.4331986467</v>
+        <v>12081</v>
       </c>
       <c r="O50" s="12" t="n">
         <f aca="false">MIN(D50-G50-L50,MAX($B$15-$B$18-N50,0))</f>
-        <v>-1414.15666666667</v>
+        <v>0</v>
       </c>
       <c r="P50" s="12" t="n">
         <f aca="false">N50+O50</f>
-        <v>52142.27653198</v>
+        <v>12081</v>
       </c>
       <c r="Q50" s="5" t="n">
         <f aca="false">IF(H50&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="5" t="n">
         <f aca="false">IF(M50&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="5" t="n">
         <f aca="false">IF(AND(Q50=1,R50=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" s="5" t="n">
         <f aca="false">IF(P50&gt;=$B$20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" s="5" t="n">
         <f aca="false">IF(P50+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -5766,88 +5538,88 @@
       </c>
       <c r="W50" s="12" t="n">
         <f aca="false">P50+$B$18</f>
-        <v>68403.02653198</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="34" t="n">
-        <v>46508</v>
+        <v>46419</v>
       </c>
       <c r="B51" s="21" t="n">
-        <f aca="false">IF(A51&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A51&gt;$B$40,$B$41,0)+IF(A51&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>2569.09333333334</v>
+        <f aca="false">IF(A51&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A51&gt;$B$43,$B$44,0)+IF(A51&gt;=$B$35,$B$37,0)+$B$32-IF(A51&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>977.318333333335</v>
       </c>
       <c r="C51" s="12" t="n">
-        <f aca="false">IF(A51=$B$39,$B$26-$B$29,0)-IF(A51=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A51=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A51=$B$42,$B$26-$B$29,0)-IF(A51=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A51=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D51" s="12" t="n">
         <f aca="false">B51+C51</f>
-        <v>2569.09333333334</v>
+        <v>977.318333333335</v>
       </c>
       <c r="E51" s="12" t="n">
         <f aca="false">H50</f>
-        <v>0</v>
+        <v>7942.14411221142</v>
       </c>
       <c r="F51" s="12" t="n">
         <f aca="false">E51*$B$6/12</f>
-        <v>0</v>
+        <v>196.832804914306</v>
       </c>
       <c r="G51" s="12" t="n">
         <f aca="false">MIN(E51+F51,MAX(D51-K51,0))</f>
-        <v>0</v>
+        <v>849.949265864989</v>
       </c>
       <c r="H51" s="12" t="n">
         <f aca="false">E51+F51-G51</f>
-        <v>0</v>
+        <v>7289.02765126074</v>
       </c>
       <c r="I51" s="12" t="n">
         <f aca="false">M50</f>
-        <v>0</v>
+        <v>5182.87151448</v>
       </c>
       <c r="J51" s="12" t="n">
         <f aca="false">I51*$B$8/12</f>
-        <v>0</v>
+        <v>75.540352323546</v>
       </c>
       <c r="K51" s="12" t="n">
         <f aca="false">MIN(I51+J51,J51+$B$9*I51)</f>
-        <v>0</v>
+        <v>127.369067468346</v>
       </c>
       <c r="L51" s="12" t="n">
         <f aca="false">MIN(I51+J51,MAX(D51-G51,0))</f>
-        <v>0</v>
+        <v>127.369067468346</v>
       </c>
       <c r="M51" s="12" t="n">
         <f aca="false">I51+J51-L51</f>
-        <v>0</v>
+        <v>5131.0427993352</v>
       </c>
       <c r="N51" s="12" t="n">
         <f aca="false">P50</f>
-        <v>52142.27653198</v>
+        <v>12081</v>
       </c>
       <c r="O51" s="12" t="n">
         <f aca="false">MIN(D51-G51-L51,MAX($B$15-$B$18-N51,0))</f>
-        <v>2569.09333333334</v>
+        <v>0</v>
       </c>
       <c r="P51" s="12" t="n">
         <f aca="false">N51+O51</f>
-        <v>54711.3698653134</v>
+        <v>12081</v>
       </c>
       <c r="Q51" s="5" t="n">
         <f aca="false">IF(H51&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="5" t="n">
         <f aca="false">IF(M51&lt;=0.005,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" s="5" t="n">
         <f aca="false">IF(AND(Q51=1,R51=1),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" s="5" t="n">
         <f aca="false">IF(P51&gt;=$B$20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" s="5" t="n">
         <f aca="false">IF(P51+$B$18&gt;=$B$15-0.5,1,0)</f>
@@ -5859,36 +5631,36 @@
       </c>
       <c r="W51" s="12" t="n">
         <f aca="false">P51+$B$18</f>
-        <v>70972.1198653134</v>
+        <v>28341.75</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="34" t="n">
-        <v>46539</v>
+        <v>46447</v>
       </c>
       <c r="B52" s="21" t="n">
-        <f aca="false">IF(A52&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A52&gt;$B$40,$B$41,0)+IF(A52&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A52&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A52&gt;$B$43,$B$44,0)+IF(A52&gt;=$B$35,$B$37,0)+$B$32-IF(A52&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C52" s="12" t="n">
-        <f aca="false">IF(A52=$B$39,$B$26-$B$29,0)-IF(A52=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A52=$B$35,$B$37*$B$36,0)+0</f>
-        <v>0</v>
+        <f aca="false">IF(A52=$B$42,$B$26-$B$29,0)-IF(A52=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A52=$B$35,$B$37*$B$36,0)+0</f>
+        <v>51581.8416666667</v>
       </c>
       <c r="D52" s="12" t="n">
         <f aca="false">B52+C52</f>
-        <v>2569.09333333334</v>
+        <v>54150.935</v>
       </c>
       <c r="E52" s="12" t="n">
         <f aca="false">H51</f>
-        <v>0</v>
+        <v>7289.02765126074</v>
       </c>
       <c r="F52" s="12" t="n">
         <f aca="false">E52*$B$6/12</f>
-        <v>0</v>
+        <v>180.646401957079</v>
       </c>
       <c r="G52" s="12" t="n">
         <f aca="false">MIN(E52+F52,MAX(D52-K52,0))</f>
-        <v>0</v>
+        <v>7469.67405321782</v>
       </c>
       <c r="H52" s="12" t="n">
         <f aca="false">E52+F52-G52</f>
@@ -5896,19 +5668,19 @@
       </c>
       <c r="I52" s="12" t="n">
         <f aca="false">M51</f>
-        <v>0</v>
+        <v>5131.0427993352</v>
       </c>
       <c r="J52" s="12" t="n">
         <f aca="false">I52*$B$8/12</f>
-        <v>0</v>
+        <v>74.7849488003106</v>
       </c>
       <c r="K52" s="12" t="n">
         <f aca="false">MIN(I52+J52,J52+$B$9*I52)</f>
-        <v>0</v>
+        <v>126.095376793663</v>
       </c>
       <c r="L52" s="12" t="n">
         <f aca="false">MIN(I52+J52,MAX(D52-G52,0))</f>
-        <v>0</v>
+        <v>5205.82774813551</v>
       </c>
       <c r="M52" s="12" t="n">
         <f aca="false">I52+J52-L52</f>
@@ -5916,15 +5688,15 @@
       </c>
       <c r="N52" s="12" t="n">
         <f aca="false">P51</f>
-        <v>54711.3698653134</v>
+        <v>12081</v>
       </c>
       <c r="O52" s="12" t="n">
         <f aca="false">MIN(D52-G52-L52,MAX($B$15-$B$18-N52,0))</f>
-        <v>2569.09333333334</v>
+        <v>41475.4331986467</v>
       </c>
       <c r="P52" s="12" t="n">
         <f aca="false">N52+O52</f>
-        <v>57280.4631986467</v>
+        <v>53556.4331986467</v>
       </c>
       <c r="Q52" s="5" t="n">
         <f aca="false">IF(H52&lt;=0.005,1,0)</f>
@@ -5952,24 +5724,24 @@
       </c>
       <c r="W52" s="12" t="n">
         <f aca="false">P52+$B$18</f>
-        <v>73541.2131986467</v>
+        <v>69817.1831986467</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="34" t="n">
-        <v>46569</v>
+        <v>46478</v>
       </c>
       <c r="B53" s="21" t="n">
-        <f aca="false">IF(A53&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A53&gt;$B$40,$B$41,0)+IF(A53&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A53&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A53&gt;$B$43,$B$44,0)+IF(A53&gt;=$B$35,$B$37,0)+$B$32-IF(A53&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C53" s="12" t="n">
-        <f aca="false">IF(A53=$B$39,$B$26-$B$29,0)-IF(A53=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A53=$B$35,$B$37*$B$36,0)+0</f>
-        <v>0</v>
+        <f aca="false">IF(A53=$B$42,$B$26-$B$29,0)-IF(A53=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A53=$B$35,$B$37*$B$36,0)+0</f>
+        <v>-3983.25</v>
       </c>
       <c r="D53" s="12" t="n">
         <f aca="false">B53+C53</f>
-        <v>2569.09333333334</v>
+        <v>-1414.15666666667</v>
       </c>
       <c r="E53" s="12" t="n">
         <f aca="false">H52</f>
@@ -6009,15 +5781,15 @@
       </c>
       <c r="N53" s="12" t="n">
         <f aca="false">P52</f>
-        <v>57280.4631986467</v>
+        <v>53556.4331986467</v>
       </c>
       <c r="O53" s="12" t="n">
         <f aca="false">MIN(D53-G53-L53,MAX($B$15-$B$18-N53,0))</f>
-        <v>2569.09333333334</v>
+        <v>-1414.15666666667</v>
       </c>
       <c r="P53" s="12" t="n">
         <f aca="false">N53+O53</f>
-        <v>59849.55653198</v>
+        <v>52142.27653198</v>
       </c>
       <c r="Q53" s="5" t="n">
         <f aca="false">IF(H53&lt;=0.005,1,0)</f>
@@ -6045,19 +5817,19 @@
       </c>
       <c r="W53" s="12" t="n">
         <f aca="false">P53+$B$18</f>
-        <v>76110.30653198</v>
+        <v>68403.02653198</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="34" t="n">
-        <v>46600</v>
+        <v>46508</v>
       </c>
       <c r="B54" s="21" t="n">
-        <f aca="false">IF(A54&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A54&gt;$B$40,$B$41,0)+IF(A54&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A54&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A54&gt;$B$43,$B$44,0)+IF(A54&gt;=$B$35,$B$37,0)+$B$32-IF(A54&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C54" s="12" t="n">
-        <f aca="false">IF(A54=$B$39,$B$26-$B$29,0)-IF(A54=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A54=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A54=$B$42,$B$26-$B$29,0)-IF(A54=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A54=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D54" s="12" t="n">
@@ -6102,7 +5874,7 @@
       </c>
       <c r="N54" s="12" t="n">
         <f aca="false">P53</f>
-        <v>59849.55653198</v>
+        <v>52142.27653198</v>
       </c>
       <c r="O54" s="12" t="n">
         <f aca="false">MIN(D54-G54-L54,MAX($B$15-$B$18-N54,0))</f>
@@ -6110,7 +5882,7 @@
       </c>
       <c r="P54" s="12" t="n">
         <f aca="false">N54+O54</f>
-        <v>62418.6498653134</v>
+        <v>54711.3698653134</v>
       </c>
       <c r="Q54" s="5" t="n">
         <f aca="false">IF(H54&lt;=0.005,1,0)</f>
@@ -6138,19 +5910,19 @@
       </c>
       <c r="W54" s="12" t="n">
         <f aca="false">P54+$B$18</f>
-        <v>78679.3998653134</v>
+        <v>70972.1198653134</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="34" t="n">
-        <v>46631</v>
+        <v>46539</v>
       </c>
       <c r="B55" s="21" t="n">
-        <f aca="false">IF(A55&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A55&gt;$B$40,$B$41,0)+IF(A55&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A55&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A55&gt;$B$43,$B$44,0)+IF(A55&gt;=$B$35,$B$37,0)+$B$32-IF(A55&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C55" s="12" t="n">
-        <f aca="false">IF(A55=$B$39,$B$26-$B$29,0)-IF(A55=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A55=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A55=$B$42,$B$26-$B$29,0)-IF(A55=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A55=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D55" s="12" t="n">
@@ -6195,7 +5967,7 @@
       </c>
       <c r="N55" s="12" t="n">
         <f aca="false">P54</f>
-        <v>62418.6498653134</v>
+        <v>54711.3698653134</v>
       </c>
       <c r="O55" s="12" t="n">
         <f aca="false">MIN(D55-G55-L55,MAX($B$15-$B$18-N55,0))</f>
@@ -6203,7 +5975,7 @@
       </c>
       <c r="P55" s="12" t="n">
         <f aca="false">N55+O55</f>
-        <v>64987.7431986467</v>
+        <v>57280.4631986467</v>
       </c>
       <c r="Q55" s="5" t="n">
         <f aca="false">IF(H55&lt;=0.005,1,0)</f>
@@ -6231,19 +6003,19 @@
       </c>
       <c r="W55" s="12" t="n">
         <f aca="false">P55+$B$18</f>
-        <v>81248.4931986467</v>
+        <v>73541.2131986467</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="34" t="n">
-        <v>46661</v>
+        <v>46569</v>
       </c>
       <c r="B56" s="21" t="n">
-        <f aca="false">IF(A56&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A56&gt;$B$40,$B$41,0)+IF(A56&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A56&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A56&gt;$B$43,$B$44,0)+IF(A56&gt;=$B$35,$B$37,0)+$B$32-IF(A56&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C56" s="12" t="n">
-        <f aca="false">IF(A56=$B$39,$B$26-$B$29,0)-IF(A56=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A56=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A56=$B$42,$B$26-$B$29,0)-IF(A56=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A56=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D56" s="12" t="n">
@@ -6288,7 +6060,7 @@
       </c>
       <c r="N56" s="12" t="n">
         <f aca="false">P55</f>
-        <v>64987.7431986467</v>
+        <v>57280.4631986467</v>
       </c>
       <c r="O56" s="12" t="n">
         <f aca="false">MIN(D56-G56-L56,MAX($B$15-$B$18-N56,0))</f>
@@ -6296,7 +6068,7 @@
       </c>
       <c r="P56" s="12" t="n">
         <f aca="false">N56+O56</f>
-        <v>67556.83653198</v>
+        <v>59849.55653198</v>
       </c>
       <c r="Q56" s="5" t="n">
         <f aca="false">IF(H56&lt;=0.005,1,0)</f>
@@ -6324,19 +6096,19 @@
       </c>
       <c r="W56" s="12" t="n">
         <f aca="false">P56+$B$18</f>
-        <v>83817.58653198</v>
+        <v>76110.30653198</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="34" t="n">
-        <v>46692</v>
+        <v>46600</v>
       </c>
       <c r="B57" s="21" t="n">
-        <f aca="false">IF(A57&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A57&gt;$B$40,$B$41,0)+IF(A57&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A57&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A57&gt;$B$43,$B$44,0)+IF(A57&gt;=$B$35,$B$37,0)+$B$32-IF(A57&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C57" s="12" t="n">
-        <f aca="false">IF(A57=$B$39,$B$26-$B$29,0)-IF(A57=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A57=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A57=$B$42,$B$26-$B$29,0)-IF(A57=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A57=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D57" s="12" t="n">
@@ -6381,7 +6153,7 @@
       </c>
       <c r="N57" s="12" t="n">
         <f aca="false">P56</f>
-        <v>67556.83653198</v>
+        <v>59849.55653198</v>
       </c>
       <c r="O57" s="12" t="n">
         <f aca="false">MIN(D57-G57-L57,MAX($B$15-$B$18-N57,0))</f>
@@ -6389,7 +6161,7 @@
       </c>
       <c r="P57" s="12" t="n">
         <f aca="false">N57+O57</f>
-        <v>70125.9298653134</v>
+        <v>62418.6498653134</v>
       </c>
       <c r="Q57" s="5" t="n">
         <f aca="false">IF(H57&lt;=0.005,1,0)</f>
@@ -6417,19 +6189,19 @@
       </c>
       <c r="W57" s="12" t="n">
         <f aca="false">P57+$B$18</f>
-        <v>86386.6798653134</v>
+        <v>78679.3998653134</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="34" t="n">
-        <v>46722</v>
+        <v>46631</v>
       </c>
       <c r="B58" s="21" t="n">
-        <f aca="false">IF(A58&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A58&gt;$B$40,$B$41,0)+IF(A58&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A58&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A58&gt;$B$43,$B$44,0)+IF(A58&gt;=$B$35,$B$37,0)+$B$32-IF(A58&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C58" s="12" t="n">
-        <f aca="false">IF(A58=$B$39,$B$26-$B$29,0)-IF(A58=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A58=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A58=$B$42,$B$26-$B$29,0)-IF(A58=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A58=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D58" s="12" t="n">
@@ -6474,7 +6246,7 @@
       </c>
       <c r="N58" s="12" t="n">
         <f aca="false">P57</f>
-        <v>70125.9298653134</v>
+        <v>62418.6498653134</v>
       </c>
       <c r="O58" s="12" t="n">
         <f aca="false">MIN(D58-G58-L58,MAX($B$15-$B$18-N58,0))</f>
@@ -6482,7 +6254,7 @@
       </c>
       <c r="P58" s="12" t="n">
         <f aca="false">N58+O58</f>
-        <v>72695.0231986467</v>
+        <v>64987.7431986467</v>
       </c>
       <c r="Q58" s="5" t="n">
         <f aca="false">IF(H58&lt;=0.005,1,0)</f>
@@ -6510,19 +6282,19 @@
       </c>
       <c r="W58" s="12" t="n">
         <f aca="false">P58+$B$18</f>
-        <v>88955.7731986467</v>
+        <v>81248.4931986467</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="34" t="n">
-        <v>46753</v>
+        <v>46661</v>
       </c>
       <c r="B59" s="21" t="n">
-        <f aca="false">IF(A59&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A59&gt;$B$40,$B$41,0)+IF(A59&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A59&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A59&gt;$B$43,$B$44,0)+IF(A59&gt;=$B$35,$B$37,0)+$B$32-IF(A59&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C59" s="12" t="n">
-        <f aca="false">IF(A59=$B$39,$B$26-$B$29,0)-IF(A59=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A59=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A59=$B$42,$B$26-$B$29,0)-IF(A59=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A59=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D59" s="12" t="n">
@@ -6567,7 +6339,7 @@
       </c>
       <c r="N59" s="12" t="n">
         <f aca="false">P58</f>
-        <v>72695.0231986467</v>
+        <v>64987.7431986467</v>
       </c>
       <c r="O59" s="12" t="n">
         <f aca="false">MIN(D59-G59-L59,MAX($B$15-$B$18-N59,0))</f>
@@ -6575,7 +6347,7 @@
       </c>
       <c r="P59" s="12" t="n">
         <f aca="false">N59+O59</f>
-        <v>75264.1165319801</v>
+        <v>67556.83653198</v>
       </c>
       <c r="Q59" s="5" t="n">
         <f aca="false">IF(H59&lt;=0.005,1,0)</f>
@@ -6603,19 +6375,19 @@
       </c>
       <c r="W59" s="12" t="n">
         <f aca="false">P59+$B$18</f>
-        <v>91524.8665319801</v>
+        <v>83817.58653198</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="34" t="n">
-        <v>46784</v>
+        <v>46692</v>
       </c>
       <c r="B60" s="21" t="n">
-        <f aca="false">IF(A60&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A60&gt;$B$40,$B$41,0)+IF(A60&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A60&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A60&gt;$B$43,$B$44,0)+IF(A60&gt;=$B$35,$B$37,0)+$B$32-IF(A60&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C60" s="12" t="n">
-        <f aca="false">IF(A60=$B$39,$B$26-$B$29,0)-IF(A60=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A60=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A60=$B$42,$B$26-$B$29,0)-IF(A60=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A60=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D60" s="12" t="n">
@@ -6660,7 +6432,7 @@
       </c>
       <c r="N60" s="12" t="n">
         <f aca="false">P59</f>
-        <v>75264.1165319801</v>
+        <v>67556.83653198</v>
       </c>
       <c r="O60" s="12" t="n">
         <f aca="false">MIN(D60-G60-L60,MAX($B$15-$B$18-N60,0))</f>
@@ -6668,7 +6440,7 @@
       </c>
       <c r="P60" s="12" t="n">
         <f aca="false">N60+O60</f>
-        <v>77833.2098653134</v>
+        <v>70125.9298653134</v>
       </c>
       <c r="Q60" s="5" t="n">
         <f aca="false">IF(H60&lt;=0.005,1,0)</f>
@@ -6696,19 +6468,19 @@
       </c>
       <c r="W60" s="12" t="n">
         <f aca="false">P60+$B$18</f>
-        <v>94093.9598653134</v>
+        <v>86386.6798653134</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="34" t="n">
-        <v>46813</v>
+        <v>46722</v>
       </c>
       <c r="B61" s="21" t="n">
-        <f aca="false">IF(A61&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A61&gt;$B$40,$B$41,0)+IF(A61&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A61&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A61&gt;$B$43,$B$44,0)+IF(A61&gt;=$B$35,$B$37,0)+$B$32-IF(A61&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C61" s="12" t="n">
-        <f aca="false">IF(A61=$B$39,$B$26-$B$29,0)-IF(A61=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A61=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A61=$B$42,$B$26-$B$29,0)-IF(A61=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A61=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D61" s="12" t="n">
@@ -6753,7 +6525,7 @@
       </c>
       <c r="N61" s="12" t="n">
         <f aca="false">P60</f>
-        <v>77833.2098653134</v>
+        <v>70125.9298653134</v>
       </c>
       <c r="O61" s="12" t="n">
         <f aca="false">MIN(D61-G61-L61,MAX($B$15-$B$18-N61,0))</f>
@@ -6761,7 +6533,7 @@
       </c>
       <c r="P61" s="12" t="n">
         <f aca="false">N61+O61</f>
-        <v>80402.3031986467</v>
+        <v>72695.0231986467</v>
       </c>
       <c r="Q61" s="5" t="n">
         <f aca="false">IF(H61&lt;=0.005,1,0)</f>
@@ -6789,19 +6561,19 @@
       </c>
       <c r="W61" s="12" t="n">
         <f aca="false">P61+$B$18</f>
-        <v>96663.0531986467</v>
+        <v>88955.7731986467</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="34" t="n">
-        <v>46844</v>
+        <v>46753</v>
       </c>
       <c r="B62" s="21" t="n">
-        <f aca="false">IF(A62&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A62&gt;$B$40,$B$41,0)+IF(A62&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A62&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A62&gt;$B$43,$B$44,0)+IF(A62&gt;=$B$35,$B$37,0)+$B$32-IF(A62&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C62" s="12" t="n">
-        <f aca="false">IF(A62=$B$39,$B$26-$B$29,0)-IF(A62=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A62=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A62=$B$42,$B$26-$B$29,0)-IF(A62=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A62=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D62" s="12" t="n">
@@ -6846,7 +6618,7 @@
       </c>
       <c r="N62" s="12" t="n">
         <f aca="false">P61</f>
-        <v>80402.3031986467</v>
+        <v>72695.0231986467</v>
       </c>
       <c r="O62" s="12" t="n">
         <f aca="false">MIN(D62-G62-L62,MAX($B$15-$B$18-N62,0))</f>
@@ -6854,7 +6626,7 @@
       </c>
       <c r="P62" s="12" t="n">
         <f aca="false">N62+O62</f>
-        <v>82971.3965319801</v>
+        <v>75264.1165319801</v>
       </c>
       <c r="Q62" s="5" t="n">
         <f aca="false">IF(H62&lt;=0.005,1,0)</f>
@@ -6882,19 +6654,19 @@
       </c>
       <c r="W62" s="12" t="n">
         <f aca="false">P62+$B$18</f>
-        <v>99232.1465319801</v>
+        <v>91524.8665319801</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="34" t="n">
-        <v>46874</v>
+        <v>46784</v>
       </c>
       <c r="B63" s="21" t="n">
-        <f aca="false">IF(A63&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A63&gt;$B$40,$B$41,0)+IF(A63&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A63&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A63&gt;$B$43,$B$44,0)+IF(A63&gt;=$B$35,$B$37,0)+$B$32-IF(A63&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C63" s="12" t="n">
-        <f aca="false">IF(A63=$B$39,$B$26-$B$29,0)-IF(A63=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A63=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A63=$B$42,$B$26-$B$29,0)-IF(A63=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A63=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D63" s="12" t="n">
@@ -6939,15 +6711,15 @@
       </c>
       <c r="N63" s="12" t="n">
         <f aca="false">P62</f>
-        <v>82971.3965319801</v>
+        <v>75264.1165319801</v>
       </c>
       <c r="O63" s="12" t="n">
         <f aca="false">MIN(D63-G63-L63,MAX($B$15-$B$18-N63,0))</f>
-        <v>1609.85346801994</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P63" s="12" t="n">
         <f aca="false">N63+O63</f>
-        <v>84581.25</v>
+        <v>77833.2098653134</v>
       </c>
       <c r="Q63" s="5" t="n">
         <f aca="false">IF(H63&lt;=0.005,1,0)</f>
@@ -6967,27 +6739,27 @@
       </c>
       <c r="U63" s="5" t="n">
         <f aca="false">IF(P63+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V63" s="12" t="n">
         <f aca="false">MAX(D63-G63-L63,0)-MAX(O63,0)</f>
-        <v>959.239865313398</v>
+        <v>0</v>
       </c>
       <c r="W63" s="12" t="n">
         <f aca="false">P63+$B$18</f>
-        <v>100842</v>
+        <v>94093.9598653134</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="34" t="n">
-        <v>46905</v>
+        <v>46813</v>
       </c>
       <c r="B64" s="21" t="n">
-        <f aca="false">IF(A64&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A64&gt;$B$40,$B$41,0)+IF(A64&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A64&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A64&gt;$B$43,$B$44,0)+IF(A64&gt;=$B$35,$B$37,0)+$B$32-IF(A64&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C64" s="12" t="n">
-        <f aca="false">IF(A64=$B$39,$B$26-$B$29,0)-IF(A64=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A64=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A64=$B$42,$B$26-$B$29,0)-IF(A64=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A64=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D64" s="12" t="n">
@@ -7032,15 +6804,15 @@
       </c>
       <c r="N64" s="12" t="n">
         <f aca="false">P63</f>
-        <v>84581.25</v>
+        <v>77833.2098653134</v>
       </c>
       <c r="O64" s="12" t="n">
         <f aca="false">MIN(D64-G64-L64,MAX($B$15-$B$18-N64,0))</f>
-        <v>0</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P64" s="12" t="n">
         <f aca="false">N64+O64</f>
-        <v>84581.25</v>
+        <v>80402.3031986467</v>
       </c>
       <c r="Q64" s="5" t="n">
         <f aca="false">IF(H64&lt;=0.005,1,0)</f>
@@ -7060,27 +6832,27 @@
       </c>
       <c r="U64" s="5" t="n">
         <f aca="false">IF(P64+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64" s="12" t="n">
         <f aca="false">MAX(D64-G64-L64,0)-MAX(O64,0)</f>
-        <v>2569.09333333334</v>
+        <v>0</v>
       </c>
       <c r="W64" s="12" t="n">
         <f aca="false">P64+$B$18</f>
-        <v>100842</v>
+        <v>96663.0531986467</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="34" t="n">
-        <v>46935</v>
+        <v>46844</v>
       </c>
       <c r="B65" s="21" t="n">
-        <f aca="false">IF(A65&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A65&gt;$B$40,$B$41,0)+IF(A65&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A65&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A65&gt;$B$43,$B$44,0)+IF(A65&gt;=$B$35,$B$37,0)+$B$32-IF(A65&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C65" s="12" t="n">
-        <f aca="false">IF(A65=$B$39,$B$26-$B$29,0)-IF(A65=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A65=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A65=$B$42,$B$26-$B$29,0)-IF(A65=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A65=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D65" s="12" t="n">
@@ -7125,15 +6897,15 @@
       </c>
       <c r="N65" s="12" t="n">
         <f aca="false">P64</f>
-        <v>84581.25</v>
+        <v>80402.3031986467</v>
       </c>
       <c r="O65" s="12" t="n">
         <f aca="false">MIN(D65-G65-L65,MAX($B$15-$B$18-N65,0))</f>
-        <v>0</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="P65" s="12" t="n">
         <f aca="false">N65+O65</f>
-        <v>84581.25</v>
+        <v>82971.3965319801</v>
       </c>
       <c r="Q65" s="5" t="n">
         <f aca="false">IF(H65&lt;=0.005,1,0)</f>
@@ -7153,27 +6925,27 @@
       </c>
       <c r="U65" s="5" t="n">
         <f aca="false">IF(P65+$B$18&gt;=$B$15-0.5,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V65" s="12" t="n">
         <f aca="false">MAX(D65-G65-L65,0)-MAX(O65,0)</f>
-        <v>2569.09333333334</v>
+        <v>0</v>
       </c>
       <c r="W65" s="12" t="n">
         <f aca="false">P65+$B$18</f>
-        <v>100842</v>
+        <v>99232.1465319801</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="34" t="n">
-        <v>46966</v>
+        <v>46874</v>
       </c>
       <c r="B66" s="21" t="n">
-        <f aca="false">IF(A66&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A66&gt;$B$40,$B$41,0)+IF(A66&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A66&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A66&gt;$B$43,$B$44,0)+IF(A66&gt;=$B$35,$B$37,0)+$B$32-IF(A66&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C66" s="12" t="n">
-        <f aca="false">IF(A66=$B$39,$B$26-$B$29,0)-IF(A66=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A66=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A66=$B$42,$B$26-$B$29,0)-IF(A66=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A66=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D66" s="12" t="n">
@@ -7218,11 +6990,11 @@
       </c>
       <c r="N66" s="12" t="n">
         <f aca="false">P65</f>
-        <v>84581.25</v>
+        <v>82971.3965319801</v>
       </c>
       <c r="O66" s="12" t="n">
         <f aca="false">MIN(D66-G66-L66,MAX($B$15-$B$18-N66,0))</f>
-        <v>0</v>
+        <v>1609.85346801994</v>
       </c>
       <c r="P66" s="12" t="n">
         <f aca="false">N66+O66</f>
@@ -7250,7 +7022,7 @@
       </c>
       <c r="V66" s="12" t="n">
         <f aca="false">MAX(D66-G66-L66,0)-MAX(O66,0)</f>
-        <v>2569.09333333334</v>
+        <v>959.239865313398</v>
       </c>
       <c r="W66" s="12" t="n">
         <f aca="false">P66+$B$18</f>
@@ -7259,14 +7031,14 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="34" t="n">
-        <v>46997</v>
+        <v>46905</v>
       </c>
       <c r="B67" s="21" t="n">
-        <f aca="false">IF(A67&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A67&gt;$B$40,$B$41,0)+IF(A67&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A67&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A67&gt;$B$43,$B$44,0)+IF(A67&gt;=$B$35,$B$37,0)+$B$32-IF(A67&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C67" s="12" t="n">
-        <f aca="false">IF(A67=$B$39,$B$26-$B$29,0)-IF(A67=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A67=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A67=$B$42,$B$26-$B$29,0)-IF(A67=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A67=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D67" s="12" t="n">
@@ -7352,14 +7124,14 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="34" t="n">
-        <v>47027</v>
+        <v>46935</v>
       </c>
       <c r="B68" s="21" t="n">
-        <f aca="false">IF(A68&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A68&gt;$B$40,$B$41,0)+IF(A68&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A68&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A68&gt;$B$43,$B$44,0)+IF(A68&gt;=$B$35,$B$37,0)+$B$32-IF(A68&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C68" s="12" t="n">
-        <f aca="false">IF(A68=$B$39,$B$26-$B$29,0)-IF(A68=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A68=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A68=$B$42,$B$26-$B$29,0)-IF(A68=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A68=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D68" s="12" t="n">
@@ -7445,14 +7217,14 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="34" t="n">
-        <v>47058</v>
+        <v>46966</v>
       </c>
       <c r="B69" s="21" t="n">
-        <f aca="false">IF(A69&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A69&gt;$B$40,$B$41,0)+IF(A69&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A69&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A69&gt;$B$43,$B$44,0)+IF(A69&gt;=$B$35,$B$37,0)+$B$32-IF(A69&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C69" s="12" t="n">
-        <f aca="false">IF(A69=$B$39,$B$26-$B$29,0)-IF(A69=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A69=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A69=$B$42,$B$26-$B$29,0)-IF(A69=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A69=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D69" s="12" t="n">
@@ -7538,14 +7310,14 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="34" t="n">
-        <v>47088</v>
+        <v>46997</v>
       </c>
       <c r="B70" s="21" t="n">
-        <f aca="false">IF(A70&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A70&gt;$B$40,$B$41,0)+IF(A70&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A70&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A70&gt;$B$43,$B$44,0)+IF(A70&gt;=$B$35,$B$37,0)+$B$32-IF(A70&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C70" s="12" t="n">
-        <f aca="false">IF(A70=$B$39,$B$26-$B$29,0)-IF(A70=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A70=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A70=$B$42,$B$26-$B$29,0)-IF(A70=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A70=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D70" s="12" t="n">
@@ -7631,14 +7403,14 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="34" t="n">
-        <v>47119</v>
+        <v>47027</v>
       </c>
       <c r="B71" s="21" t="n">
-        <f aca="false">IF(A71&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A71&gt;$B$40,$B$41,0)+IF(A71&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A71&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A71&gt;$B$43,$B$44,0)+IF(A71&gt;=$B$35,$B$37,0)+$B$32-IF(A71&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2569.09333333334</v>
       </c>
       <c r="C71" s="12" t="n">
-        <f aca="false">IF(A71=$B$39,$B$26-$B$29,0)-IF(A71=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A71=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A71=$B$42,$B$26-$B$29,0)-IF(A71=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A71=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D71" s="12" t="n">
@@ -7724,19 +7496,19 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="34" t="n">
-        <v>47150</v>
+        <v>47058</v>
       </c>
       <c r="B72" s="21" t="n">
-        <f aca="false">IF(A72&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A72&gt;$B$40,$B$41,0)+IF(A72&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>2911.09333333334</v>
+        <f aca="false">IF(A72&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A72&gt;$B$43,$B$44,0)+IF(A72&gt;=$B$35,$B$37,0)+$B$32-IF(A72&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C72" s="12" t="n">
-        <f aca="false">IF(A72=$B$39,$B$26-$B$29,0)-IF(A72=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A72=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A72=$B$42,$B$26-$B$29,0)-IF(A72=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A72=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D72" s="12" t="n">
         <f aca="false">B72+C72</f>
-        <v>2911.09333333334</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E72" s="12" t="n">
         <f aca="false">H71</f>
@@ -7808,7 +7580,7 @@
       </c>
       <c r="V72" s="12" t="n">
         <f aca="false">MAX(D72-G72-L72,0)-MAX(O72,0)</f>
-        <v>2911.09333333334</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W72" s="12" t="n">
         <f aca="false">P72+$B$18</f>
@@ -7817,19 +7589,19 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="34" t="n">
-        <v>47178</v>
+        <v>47088</v>
       </c>
       <c r="B73" s="21" t="n">
-        <f aca="false">IF(A73&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A73&gt;$B$40,$B$41,0)+IF(A73&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>2911.09333333334</v>
+        <f aca="false">IF(A73&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A73&gt;$B$43,$B$44,0)+IF(A73&gt;=$B$35,$B$37,0)+$B$32-IF(A73&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C73" s="12" t="n">
-        <f aca="false">IF(A73=$B$39,$B$26-$B$29,0)-IF(A73=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A73=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A73=$B$42,$B$26-$B$29,0)-IF(A73=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A73=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D73" s="12" t="n">
         <f aca="false">B73+C73</f>
-        <v>2911.09333333334</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E73" s="12" t="n">
         <f aca="false">H72</f>
@@ -7901,7 +7673,7 @@
       </c>
       <c r="V73" s="12" t="n">
         <f aca="false">MAX(D73-G73-L73,0)-MAX(O73,0)</f>
-        <v>2911.09333333334</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W73" s="12" t="n">
         <f aca="false">P73+$B$18</f>
@@ -7910,19 +7682,19 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="34" t="n">
-        <v>47209</v>
+        <v>47119</v>
       </c>
       <c r="B74" s="21" t="n">
-        <f aca="false">IF(A74&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A74&gt;$B$40,$B$41,0)+IF(A74&gt;=$B$35,$B$37,0)+$B$32</f>
-        <v>2911.09333333334</v>
+        <f aca="false">IF(A74&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A74&gt;$B$43,$B$44,0)+IF(A74&gt;=$B$35,$B$37,0)+$B$32-IF(A74&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>2569.09333333334</v>
       </c>
       <c r="C74" s="12" t="n">
-        <f aca="false">IF(A74=$B$39,$B$26-$B$29,0)-IF(A74=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A74=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A74=$B$42,$B$26-$B$29,0)-IF(A74=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A74=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D74" s="12" t="n">
         <f aca="false">B74+C74</f>
-        <v>2911.09333333334</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="E74" s="12" t="n">
         <f aca="false">H73</f>
@@ -7994,7 +7766,7 @@
       </c>
       <c r="V74" s="12" t="n">
         <f aca="false">MAX(D74-G74-L74,0)-MAX(O74,0)</f>
-        <v>2911.09333333334</v>
+        <v>2569.09333333334</v>
       </c>
       <c r="W74" s="12" t="n">
         <f aca="false">P74+$B$18</f>
@@ -8003,14 +7775,14 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="34" t="n">
-        <v>47239</v>
+        <v>47150</v>
       </c>
       <c r="B75" s="21" t="n">
-        <f aca="false">IF(A75&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A75&gt;$B$40,$B$41,0)+IF(A75&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A75&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A75&gt;$B$43,$B$44,0)+IF(A75&gt;=$B$35,$B$37,0)+$B$32-IF(A75&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C75" s="12" t="n">
-        <f aca="false">IF(A75=$B$39,$B$26-$B$29,0)-IF(A75=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A75=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A75=$B$42,$B$26-$B$29,0)-IF(A75=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A75=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D75" s="12" t="n">
@@ -8096,14 +7868,14 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="34" t="n">
-        <v>47270</v>
+        <v>47178</v>
       </c>
       <c r="B76" s="21" t="n">
-        <f aca="false">IF(A76&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A76&gt;$B$40,$B$41,0)+IF(A76&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A76&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A76&gt;$B$43,$B$44,0)+IF(A76&gt;=$B$35,$B$37,0)+$B$32-IF(A76&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C76" s="12" t="n">
-        <f aca="false">IF(A76=$B$39,$B$26-$B$29,0)-IF(A76=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A76=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A76=$B$42,$B$26-$B$29,0)-IF(A76=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A76=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D76" s="12" t="n">
@@ -8189,14 +7961,14 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="34" t="n">
-        <v>47300</v>
+        <v>47209</v>
       </c>
       <c r="B77" s="21" t="n">
-        <f aca="false">IF(A77&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A77&gt;$B$40,$B$41,0)+IF(A77&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A77&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A77&gt;$B$43,$B$44,0)+IF(A77&gt;=$B$35,$B$37,0)+$B$32-IF(A77&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C77" s="12" t="n">
-        <f aca="false">IF(A77=$B$39,$B$26-$B$29,0)-IF(A77=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A77=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A77=$B$42,$B$26-$B$29,0)-IF(A77=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A77=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D77" s="12" t="n">
@@ -8282,14 +8054,14 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="34" t="n">
-        <v>47331</v>
+        <v>47239</v>
       </c>
       <c r="B78" s="21" t="n">
-        <f aca="false">IF(A78&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A78&gt;$B$40,$B$41,0)+IF(A78&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A78&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A78&gt;$B$43,$B$44,0)+IF(A78&gt;=$B$35,$B$37,0)+$B$32-IF(A78&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C78" s="12" t="n">
-        <f aca="false">IF(A78=$B$39,$B$26-$B$29,0)-IF(A78=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A78=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A78=$B$42,$B$26-$B$29,0)-IF(A78=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A78=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D78" s="12" t="n">
@@ -8375,14 +8147,14 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="34" t="n">
-        <v>47362</v>
+        <v>47270</v>
       </c>
       <c r="B79" s="21" t="n">
-        <f aca="false">IF(A79&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A79&gt;$B$40,$B$41,0)+IF(A79&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A79&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A79&gt;$B$43,$B$44,0)+IF(A79&gt;=$B$35,$B$37,0)+$B$32-IF(A79&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C79" s="12" t="n">
-        <f aca="false">IF(A79=$B$39,$B$26-$B$29,0)-IF(A79=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A79=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A79=$B$42,$B$26-$B$29,0)-IF(A79=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A79=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D79" s="12" t="n">
@@ -8468,14 +8240,14 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="34" t="n">
-        <v>47392</v>
+        <v>47300</v>
       </c>
       <c r="B80" s="21" t="n">
-        <f aca="false">IF(A80&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A80&gt;$B$40,$B$41,0)+IF(A80&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A80&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A80&gt;$B$43,$B$44,0)+IF(A80&gt;=$B$35,$B$37,0)+$B$32-IF(A80&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C80" s="12" t="n">
-        <f aca="false">IF(A80=$B$39,$B$26-$B$29,0)-IF(A80=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A80=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A80=$B$42,$B$26-$B$29,0)-IF(A80=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A80=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D80" s="12" t="n">
@@ -8561,14 +8333,14 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="34" t="n">
-        <v>47423</v>
+        <v>47331</v>
       </c>
       <c r="B81" s="21" t="n">
-        <f aca="false">IF(A81&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A81&gt;$B$40,$B$41,0)+IF(A81&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A81&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A81&gt;$B$43,$B$44,0)+IF(A81&gt;=$B$35,$B$37,0)+$B$32-IF(A81&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C81" s="12" t="n">
-        <f aca="false">IF(A81=$B$39,$B$26-$B$29,0)-IF(A81=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A81=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A81=$B$42,$B$26-$B$29,0)-IF(A81=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A81=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D81" s="12" t="n">
@@ -8654,14 +8426,14 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="34" t="n">
-        <v>47453</v>
+        <v>47362</v>
       </c>
       <c r="B82" s="21" t="n">
-        <f aca="false">IF(A82&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A82&gt;$B$40,$B$41,0)+IF(A82&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A82&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A82&gt;$B$43,$B$44,0)+IF(A82&gt;=$B$35,$B$37,0)+$B$32-IF(A82&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C82" s="12" t="n">
-        <f aca="false">IF(A82=$B$39,$B$26-$B$29,0)-IF(A82=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A82=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A82=$B$42,$B$26-$B$29,0)-IF(A82=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A82=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D82" s="12" t="n">
@@ -8747,14 +8519,14 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="34" t="n">
-        <v>47484</v>
+        <v>47392</v>
       </c>
       <c r="B83" s="21" t="n">
-        <f aca="false">IF(A83&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A83&gt;$B$40,$B$41,0)+IF(A83&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A83&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A83&gt;$B$43,$B$44,0)+IF(A83&gt;=$B$35,$B$37,0)+$B$32-IF(A83&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C83" s="12" t="n">
-        <f aca="false">IF(A83=$B$39,$B$26-$B$29,0)-IF(A83=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A83=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A83=$B$42,$B$26-$B$29,0)-IF(A83=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A83=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D83" s="12" t="n">
@@ -8840,14 +8612,14 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="34" t="n">
-        <v>47515</v>
+        <v>47423</v>
       </c>
       <c r="B84" s="21" t="n">
-        <f aca="false">IF(A84&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A84&gt;$B$40,$B$41,0)+IF(A84&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A84&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A84&gt;$B$43,$B$44,0)+IF(A84&gt;=$B$35,$B$37,0)+$B$32-IF(A84&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C84" s="12" t="n">
-        <f aca="false">IF(A84=$B$39,$B$26-$B$29,0)-IF(A84=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A84=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A84=$B$42,$B$26-$B$29,0)-IF(A84=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A84=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D84" s="12" t="n">
@@ -8933,14 +8705,14 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="34" t="n">
-        <v>47543</v>
+        <v>47453</v>
       </c>
       <c r="B85" s="21" t="n">
-        <f aca="false">IF(A85&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A85&gt;$B$40,$B$41,0)+IF(A85&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A85&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A85&gt;$B$43,$B$44,0)+IF(A85&gt;=$B$35,$B$37,0)+$B$32-IF(A85&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C85" s="12" t="n">
-        <f aca="false">IF(A85=$B$39,$B$26-$B$29,0)-IF(A85=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A85=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A85=$B$42,$B$26-$B$29,0)-IF(A85=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A85=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D85" s="12" t="n">
@@ -9026,14 +8798,14 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="34" t="n">
-        <v>47574</v>
+        <v>47484</v>
       </c>
       <c r="B86" s="21" t="n">
-        <f aca="false">IF(A86&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A86&gt;$B$40,$B$41,0)+IF(A86&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A86&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A86&gt;$B$43,$B$44,0)+IF(A86&gt;=$B$35,$B$37,0)+$B$32-IF(A86&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C86" s="12" t="n">
-        <f aca="false">IF(A86=$B$39,$B$26-$B$29,0)-IF(A86=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A86=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A86=$B$42,$B$26-$B$29,0)-IF(A86=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A86=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D86" s="12" t="n">
@@ -9119,14 +8891,14 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="34" t="n">
-        <v>47604</v>
+        <v>47515</v>
       </c>
       <c r="B87" s="21" t="n">
-        <f aca="false">IF(A87&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A87&gt;$B$40,$B$41,0)+IF(A87&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A87&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A87&gt;$B$43,$B$44,0)+IF(A87&gt;=$B$35,$B$37,0)+$B$32-IF(A87&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C87" s="12" t="n">
-        <f aca="false">IF(A87=$B$39,$B$26-$B$29,0)-IF(A87=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A87=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A87=$B$42,$B$26-$B$29,0)-IF(A87=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A87=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D87" s="12" t="n">
@@ -9212,14 +8984,14 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="34" t="n">
-        <v>47635</v>
+        <v>47543</v>
       </c>
       <c r="B88" s="21" t="n">
-        <f aca="false">IF(A88&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A88&gt;$B$40,$B$41,0)+IF(A88&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A88&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A88&gt;$B$43,$B$44,0)+IF(A88&gt;=$B$35,$B$37,0)+$B$32-IF(A88&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C88" s="12" t="n">
-        <f aca="false">IF(A88=$B$39,$B$26-$B$29,0)-IF(A88=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A88=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A88=$B$42,$B$26-$B$29,0)-IF(A88=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A88=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D88" s="12" t="n">
@@ -9305,14 +9077,14 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="34" t="n">
-        <v>47665</v>
+        <v>47574</v>
       </c>
       <c r="B89" s="21" t="n">
-        <f aca="false">IF(A89&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A89&gt;$B$40,$B$41,0)+IF(A89&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A89&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A89&gt;$B$43,$B$44,0)+IF(A89&gt;=$B$35,$B$37,0)+$B$32-IF(A89&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C89" s="12" t="n">
-        <f aca="false">IF(A89=$B$39,$B$26-$B$29,0)-IF(A89=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A89=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A89=$B$42,$B$26-$B$29,0)-IF(A89=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A89=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D89" s="12" t="n">
@@ -9398,14 +9170,14 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="34" t="n">
-        <v>47696</v>
+        <v>47604</v>
       </c>
       <c r="B90" s="21" t="n">
-        <f aca="false">IF(A90&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A90&gt;$B$40,$B$41,0)+IF(A90&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A90&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A90&gt;$B$43,$B$44,0)+IF(A90&gt;=$B$35,$B$37,0)+$B$32-IF(A90&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C90" s="12" t="n">
-        <f aca="false">IF(A90=$B$39,$B$26-$B$29,0)-IF(A90=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A90=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A90=$B$42,$B$26-$B$29,0)-IF(A90=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A90=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D90" s="12" t="n">
@@ -9491,14 +9263,14 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="34" t="n">
-        <v>47727</v>
+        <v>47635</v>
       </c>
       <c r="B91" s="21" t="n">
-        <f aca="false">IF(A91&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A91&gt;$B$40,$B$41,0)+IF(A91&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A91&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A91&gt;$B$43,$B$44,0)+IF(A91&gt;=$B$35,$B$37,0)+$B$32-IF(A91&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C91" s="12" t="n">
-        <f aca="false">IF(A91=$B$39,$B$26-$B$29,0)-IF(A91=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A91=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A91=$B$42,$B$26-$B$29,0)-IF(A91=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A91=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D91" s="12" t="n">
@@ -9584,14 +9356,14 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="34" t="n">
-        <v>47757</v>
+        <v>47665</v>
       </c>
       <c r="B92" s="21" t="n">
-        <f aca="false">IF(A92&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A92&gt;$B$40,$B$41,0)+IF(A92&gt;=$B$35,$B$37,0)+$B$32</f>
+        <f aca="false">IF(A92&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A92&gt;$B$43,$B$44,0)+IF(A92&gt;=$B$35,$B$37,0)+$B$32-IF(A92&gt;=$B$40,$B$39*(1-$B$41),0)</f>
         <v>2911.09333333334</v>
       </c>
       <c r="C92" s="12" t="n">
-        <f aca="false">IF(A92=$B$39,$B$26-$B$29,0)-IF(A92=DATE(YEAR($B$39),MONTH($B$39)+1,1),$B$28,0)+IF(A92=$B$35,$B$37*$B$36,0)+0</f>
+        <f aca="false">IF(A92=$B$42,$B$26-$B$29,0)-IF(A92=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A92=$B$35,$B$37*$B$36,0)+0</f>
         <v>0</v>
       </c>
       <c r="D92" s="12" t="n">
@@ -9672,6 +9444,285 @@
       </c>
       <c r="W92" s="12" t="n">
         <f aca="false">P92+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="34" t="n">
+        <v>47696</v>
+      </c>
+      <c r="B93" s="21" t="n">
+        <f aca="false">IF(A93&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A93&gt;$B$43,$B$44,0)+IF(A93&gt;=$B$35,$B$37,0)+$B$32-IF(A93&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="C93" s="12" t="n">
+        <f aca="false">IF(A93=$B$42,$B$26-$B$29,0)-IF(A93=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A93=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
+      </c>
+      <c r="D93" s="12" t="n">
+        <f aca="false">B93+C93</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="E93" s="12" t="n">
+        <f aca="false">H92</f>
+        <v>0</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <f aca="false">E93*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <f aca="false">MIN(E93+F93,MAX(D93-K93,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <f aca="false">E93+F93-G93</f>
+        <v>0</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <f aca="false">M92</f>
+        <v>0</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <f aca="false">I93*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <f aca="false">MIN(I93+J93,J93+$B$9*I93)</f>
+        <v>0</v>
+      </c>
+      <c r="L93" s="12" t="n">
+        <f aca="false">MIN(I93+J93,MAX(D93-G93,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M93" s="12" t="n">
+        <f aca="false">I93+J93-L93</f>
+        <v>0</v>
+      </c>
+      <c r="N93" s="12" t="n">
+        <f aca="false">P92</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O93" s="12" t="n">
+        <f aca="false">MIN(D93-G93-L93,MAX($B$15-$B$18-N93,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P93" s="12" t="n">
+        <f aca="false">N93+O93</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q93" s="5" t="n">
+        <f aca="false">IF(H93&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R93" s="5" t="n">
+        <f aca="false">IF(M93&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S93" s="5" t="n">
+        <f aca="false">IF(AND(Q93=1,R93=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T93" s="5" t="n">
+        <f aca="false">IF(P93&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U93" s="5" t="n">
+        <f aca="false">IF(P93+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V93" s="12" t="n">
+        <f aca="false">MAX(D93-G93-L93,0)-MAX(O93,0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="W93" s="12" t="n">
+        <f aca="false">P93+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="34" t="n">
+        <v>47727</v>
+      </c>
+      <c r="B94" s="21" t="n">
+        <f aca="false">IF(A94&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A94&gt;$B$43,$B$44,0)+IF(A94&gt;=$B$35,$B$37,0)+$B$32-IF(A94&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="C94" s="12" t="n">
+        <f aca="false">IF(A94=$B$42,$B$26-$B$29,0)-IF(A94=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A94=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="12" t="n">
+        <f aca="false">B94+C94</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="E94" s="12" t="n">
+        <f aca="false">H93</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <f aca="false">E94*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <f aca="false">MIN(E94+F94,MAX(D94-K94,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <f aca="false">E94+F94-G94</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <f aca="false">M93</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="12" t="n">
+        <f aca="false">I94*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <f aca="false">MIN(I94+J94,J94+$B$9*I94)</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <f aca="false">MIN(I94+J94,MAX(D94-G94,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M94" s="12" t="n">
+        <f aca="false">I94+J94-L94</f>
+        <v>0</v>
+      </c>
+      <c r="N94" s="12" t="n">
+        <f aca="false">P93</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O94" s="12" t="n">
+        <f aca="false">MIN(D94-G94-L94,MAX($B$15-$B$18-N94,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P94" s="12" t="n">
+        <f aca="false">N94+O94</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q94" s="5" t="n">
+        <f aca="false">IF(H94&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R94" s="5" t="n">
+        <f aca="false">IF(M94&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S94" s="5" t="n">
+        <f aca="false">IF(AND(Q94=1,R94=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T94" s="5" t="n">
+        <f aca="false">IF(P94&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U94" s="5" t="n">
+        <f aca="false">IF(P94+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V94" s="12" t="n">
+        <f aca="false">MAX(D94-G94-L94,0)-MAX(O94,0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="W94" s="12" t="n">
+        <f aca="false">P94+$B$18</f>
+        <v>100842</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="34" t="n">
+        <v>47757</v>
+      </c>
+      <c r="B95" s="21" t="n">
+        <f aca="false">IF(A95&lt;=$B$21,Budget!$F$70,Budget!$F$71)+IF(A95&gt;$B$43,$B$44,0)+IF(A95&gt;=$B$35,$B$37,0)+$B$32-IF(A95&gt;=$B$40,$B$39*(1-$B$41),0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="C95" s="12" t="n">
+        <f aca="false">IF(A95=$B$42,$B$26-$B$29,0)-IF(A95=DATE(YEAR($B$42),MONTH($B$42)+1,1),$B$28,0)+IF(A95=$B$35,$B$37*$B$36,0)+0</f>
+        <v>0</v>
+      </c>
+      <c r="D95" s="12" t="n">
+        <f aca="false">B95+C95</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="E95" s="12" t="n">
+        <f aca="false">H94</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <f aca="false">E95*$B$6/12</f>
+        <v>0</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <f aca="false">MIN(E95+F95,MAX(D95-K95,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <f aca="false">E95+F95-G95</f>
+        <v>0</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <f aca="false">M94</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <f aca="false">I95*$B$8/12</f>
+        <v>0</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <f aca="false">MIN(I95+J95,J95+$B$9*I95)</f>
+        <v>0</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <f aca="false">MIN(I95+J95,MAX(D95-G95,0))</f>
+        <v>0</v>
+      </c>
+      <c r="M95" s="12" t="n">
+        <f aca="false">I95+J95-L95</f>
+        <v>0</v>
+      </c>
+      <c r="N95" s="12" t="n">
+        <f aca="false">P94</f>
+        <v>84581.25</v>
+      </c>
+      <c r="O95" s="12" t="n">
+        <f aca="false">MIN(D95-G95-L95,MAX($B$15-$B$18-N95,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P95" s="12" t="n">
+        <f aca="false">N95+O95</f>
+        <v>84581.25</v>
+      </c>
+      <c r="Q95" s="5" t="n">
+        <f aca="false">IF(H95&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R95" s="5" t="n">
+        <f aca="false">IF(M95&lt;=0.005,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S95" s="5" t="n">
+        <f aca="false">IF(AND(Q95=1,R95=1),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T95" s="5" t="n">
+        <f aca="false">IF(P95&gt;=$B$20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U95" s="5" t="n">
+        <f aca="false">IF(P95+$B$18&gt;=$B$15-0.5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V95" s="12" t="n">
+        <f aca="false">MAX(D95-G95-L95,0)-MAX(O95,0)</f>
+        <v>2911.09333333334</v>
+      </c>
+      <c r="W95" s="12" t="n">
+        <f aca="false">P95+$B$18</f>
         <v>100842</v>
       </c>
     </row>
@@ -9702,12 +9753,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9715,48 +9766,48 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -9774,7 +9825,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>17767.46</v>
@@ -9821,7 +9872,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>6410.38</v>
@@ -9868,7 +9919,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>1459.54</v>
@@ -9915,7 +9966,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">SUM(B6:B8)</f>
@@ -9972,7 +10023,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -9990,7 +10041,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>4300</v>
@@ -10037,7 +10088,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B13" s="13" t="n">
         <v>32.71</v>
@@ -10084,7 +10135,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B14" s="13" t="n">
         <v>0</v>
@@ -10131,7 +10182,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>183.82</v>
@@ -10178,7 +10229,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B16" s="13" t="n">
         <v>500</v>
@@ -10225,7 +10276,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">SUM(B12:B16)</f>
@@ -10282,7 +10333,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -10300,7 +10351,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B20" s="13" t="n">
         <v>6857.93</v>
@@ -10394,7 +10445,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B22" s="13" t="n">
         <v>1057.39</v>
@@ -10441,7 +10492,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B23" s="13" t="n">
         <v>341.99</v>
@@ -10488,7 +10539,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B24" s="13" t="n">
         <v>0</v>
@@ -10535,7 +10586,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B25" s="13" t="n">
         <v>856.83</v>
@@ -10582,7 +10633,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B26" s="13" t="n">
         <v>286.67</v>
@@ -10629,7 +10680,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B27" s="13" t="n">
         <v>614</v>
@@ -10676,7 +10727,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B28" s="13" t="n">
         <v>323.39</v>
@@ -10723,7 +10774,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B29" s="13" t="n">
         <v>368.15</v>
@@ -10770,7 +10821,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B30" s="13" t="n">
         <v>400.62</v>
@@ -10817,7 +10868,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B31" s="13" t="n">
         <v>134.97</v>
@@ -10864,7 +10915,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B32" s="13" t="n">
         <v>178.9</v>
@@ -10911,7 +10962,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B33" s="13" t="n">
         <v>115.5</v>
@@ -10958,7 +11009,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B34" s="13" t="n">
         <v>760</v>
@@ -11005,7 +11056,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B35" s="13" t="n">
         <v>155</v>
@@ -11099,7 +11150,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B37" s="13" t="n">
         <v>473.56</v>
@@ -11146,7 +11197,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B38" s="13" t="n">
         <v>431.52</v>
@@ -11193,7 +11244,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B39" s="13" t="n">
         <v>359.9</v>
@@ -11240,7 +11291,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B40" s="13" t="n">
         <v>27.6</v>
@@ -11287,7 +11338,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B41" s="13" t="n">
         <v>557.68</v>
@@ -11334,7 +11385,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B42" s="13" t="n">
         <v>385.13</v>
@@ -11381,7 +11432,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B43" s="13" t="n">
         <v>209</v>
@@ -11428,7 +11479,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B44" s="13" t="n">
         <v>266.15</v>
@@ -11522,7 +11573,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B46" s="13" t="n">
         <v>469.36</v>
@@ -11616,7 +11667,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B48" s="13" t="n">
         <v>72.9</v>
@@ -11663,7 +11714,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B49" s="13" t="n">
         <v>0.5</v>
@@ -11710,7 +11761,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B50" s="13" t="n">
         <v>355.78</v>
@@ -11757,7 +11808,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B51" s="13" t="n">
         <v>97.3</v>
@@ -11804,7 +11855,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B52" s="13" t="n">
         <v>129.41</v>
@@ -11851,7 +11902,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B53" s="13" t="n">
         <v>465.78</v>
@@ -11898,7 +11949,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B54" s="13" t="n">
         <v>240</v>
@@ -11945,7 +11996,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B55" s="13" t="n">
         <v>729.5</v>
@@ -11992,7 +12043,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B56" s="13" t="n">
         <v>2.25</v>
@@ -12039,7 +12090,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B57" s="13" t="n">
         <v>0</v>
@@ -12086,7 +12137,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B58" s="13" t="n">
         <v>127.73</v>
@@ -12133,7 +12184,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B59" s="17" t="n">
         <f aca="false">SUM(B20:B58)</f>
@@ -12190,7 +12241,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B61" s="28" t="n">
         <f aca="false">B17+B59</f>
@@ -12247,7 +12298,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B62" s="28" t="n">
         <f aca="false">B9</f>
@@ -12304,7 +12355,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B63" s="9" t="n">
         <f aca="false">B62-B61</f>
@@ -12390,35 +12441,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>20</v>
@@ -12426,10 +12477,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>72.97</v>
@@ -12439,25 +12490,25 @@
         <v>875.64</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">IF(E5="Cut",D5,0)</f>
         <v>0</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>82.99</v>
@@ -12467,25 +12518,25 @@
         <v>995.88</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">IF(E6="Cut",D6,0)</f>
         <v>0</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>26.99</v>
@@ -12495,23 +12546,23 @@
         <v>323.88</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">IF(E7="Cut",D7,0)</f>
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>18.99</v>
@@ -12521,25 +12572,25 @@
         <v>227.88</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">IF(E8="Cut",D8,0)</f>
         <v>0</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>12.99</v>
@@ -12549,23 +12600,23 @@
         <v>155.88</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">IF(E9="Cut",D9,0)</f>
         <v>0</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>139</v>
@@ -12575,25 +12626,25 @@
         <v>139</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">IF(E10="Cut",D10,0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>4.99</v>
@@ -12603,25 +12654,25 @@
         <v>59.88</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">IF(E11="Cut",D11,0)</f>
         <v>0</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>6.36</v>
@@ -12631,25 +12682,25 @@
         <v>76.32</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">IF(E12="Cut",D12,0)</f>
         <v>0</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>11.99</v>
@@ -12659,25 +12710,25 @@
         <v>143.88</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">IF(E13="Cut",D13,0)</f>
         <v>0</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>8.99</v>
@@ -12687,25 +12738,25 @@
         <v>107.88</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">IF(E14="Cut",D14,0)</f>
         <v>0</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>25</v>
@@ -12715,25 +12766,25 @@
         <v>300</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F15" s="12" t="n">
         <f aca="false">IF(E15="Cut",D15,0)</f>
         <v>0</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>27.72</v>
@@ -12743,25 +12794,25 @@
         <v>332.64</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F16" s="12" t="n">
         <f aca="false">IF(E16="Cut",D16,0)</f>
         <v>0</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>99.99</v>
@@ -12771,23 +12822,23 @@
         <v>99.99</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F17" s="12" t="n">
         <f aca="false">IF(E17="Cut",D17,0)</f>
         <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>150</v>
@@ -12797,23 +12848,23 @@
         <v>150</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F18" s="12" t="n">
         <f aca="false">IF(E18="Cut",D18,0)</f>
         <v>0</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>20.7</v>
@@ -12823,25 +12874,25 @@
         <v>248.4</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F19" s="12" t="n">
         <f aca="false">IF(E19="Cut",D19,0)</f>
         <v>0</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>10</v>
@@ -12851,25 +12902,25 @@
         <v>120</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">IF(E20="Cut",D20,0)</f>
         <v>0</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>32.99</v>
@@ -12879,25 +12930,25 @@
         <v>395.88</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">IF(E21="Cut",D21,0)</f>
         <v>0</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>13.94</v>
@@ -12907,25 +12958,25 @@
         <v>167.28</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">IF(E22="Cut",D22,0)</f>
         <v>0</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>20.76</v>
@@ -12935,25 +12986,25 @@
         <v>249.12</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F23" s="12" t="n">
         <f aca="false">IF(E23="Cut",D23,0)</f>
         <v>0</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>10.63</v>
@@ -12963,23 +13014,23 @@
         <v>127.56</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F24" s="12" t="n">
         <f aca="false">IF(E24="Cut",D24,0)</f>
         <v>0</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>21.25</v>
@@ -12989,23 +13040,23 @@
         <v>255</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F25" s="12" t="n">
         <f aca="false">IF(E25="Cut",D25,0)</f>
         <v>0</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>381.44</v>
@@ -13015,25 +13066,25 @@
         <v>381.44</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F26" s="12" t="n">
         <f aca="false">IF(E26="Cut",D26,0)</f>
         <v>0</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>212.49</v>
@@ -13043,25 +13094,25 @@
         <v>212.49</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F27" s="12" t="n">
         <f aca="false">IF(E27="Cut",D27,0)</f>
         <v>0</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>114.75</v>
@@ -13071,25 +13122,25 @@
         <v>229.5</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F28" s="12" t="n">
         <f aca="false">IF(E28="Cut",D28,0)</f>
         <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>548</v>
@@ -13099,25 +13150,25 @@
         <v>548</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F29" s="12" t="n">
         <f aca="false">IF(E29="Cut",D29,0)</f>
         <v>0</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>32.95</v>
@@ -13127,25 +13178,25 @@
         <v>395.4</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F30" s="12" t="n">
         <f aca="false">IF(E30="Cut",D30,0)</f>
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>115.23</v>
@@ -13155,25 +13206,25 @@
         <v>1382.76</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F31" s="12" t="n">
         <f aca="false">IF(E31="Cut",D31,0)</f>
         <v>0</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>25</v>
@@ -13183,22 +13234,22 @@
         <v>300</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F32" s="12" t="n">
         <f aca="false">IF(E32="Cut",D32,0)</f>
         <v>0</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D33" s="17" t="n">
         <f aca="false">SUM(D5:D32)</f>
@@ -13211,7 +13262,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D34" s="12" t="n">
         <f aca="false">SUMIF(E5:E32,"Review",D5:D32)</f>
@@ -13220,7 +13271,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -13248,156 +13299,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="36" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="36" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
